--- a/ARCHER/Documentation/PCB/Sensor Characteristics.xlsx
+++ b/ARCHER/Documentation/PCB/Sensor Characteristics.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jason\Google Drive\Raketenbauteam\AG Elektronik\ARCHER\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\.git\ARCHER\Documentation\PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB2C72C-2B84-43B8-8D11-C6A9436AE3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CE9E1A-3911-4209-9A94-2B6C34F8C867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IMUs" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W16" authorId="0" shapeId="0" xr:uid="{A30B386B-0CFD-464B-A3DF-41E97E049C37}">
+    <comment ref="Y16" authorId="0" shapeId="0" xr:uid="{A30B386B-0CFD-464B-A3DF-41E97E049C37}">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T6" authorId="0" shapeId="0" xr:uid="{0021CFEA-32D7-4C8A-B33E-9A29A233A133}">
+    <comment ref="T6" authorId="0" shapeId="0" xr:uid="{0ED5BE3C-FA2E-473B-BD9C-CB05440E2559}">
       <text>
         <r>
           <rPr>
@@ -343,7 +343,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="337">
   <si>
     <t>ADXL345</t>
   </si>
@@ -775,15 +775,6 @@
   </si>
   <si>
     <t>MPL3115A2ST1</t>
-  </si>
-  <si>
-    <t>±1.6 mbar - ±1.0 bar</t>
-  </si>
-  <si>
-    <t>±0.5 psi - ±150 psi</t>
-  </si>
-  <si>
-    <t>±160 Pa - ±1 MPa</t>
   </si>
   <si>
     <t>Pressure Specs</t>
@@ -896,9 +887,6 @@
     <t>1.5 mbar</t>
   </si>
   <si>
-    <t>mbar</t>
-  </si>
-  <si>
     <t>10 mbar - 2000 mbar*</t>
   </si>
   <si>
@@ -976,9 +964,6 @@
     <t>±1 mbar/yr</t>
   </si>
   <si>
-    <t>0.024** (4096), 0.036 (2048), 0.054 (1024), 0.084 (512), 0.130 (256)</t>
-  </si>
-  <si>
     <t>12.5 (4096)***, 6.3 (2048), 3.2 (1024), 1.7 (512), 0.9 (256) μA</t>
   </si>
   <si>
@@ -1019,12 +1004,6 @@
   </si>
   <si>
     <t>265 μA (128)</t>
-  </si>
-  <si>
-    <t>20 kPa - 110 kPa</t>
-  </si>
-  <si>
-    <t>2.9 psi - 16 psi</t>
   </si>
   <si>
     <r>
@@ -1042,9 +1021,6 @@
     </r>
   </si>
   <si>
-    <t>0,2 bar - 1,1 bar*</t>
-  </si>
-  <si>
     <t>1x oversample</t>
   </si>
   <si>
@@ -1067,18 +1043,6 @@
   </si>
   <si>
     <t>&gt;1 Hz</t>
-  </si>
-  <si>
-    <t>Barometer mode</t>
-  </si>
-  <si>
-    <t>1.5 Pa</t>
-  </si>
-  <si>
-    <t>Altimeter mode</t>
-  </si>
-  <si>
-    <t>0.3 m</t>
   </si>
   <si>
     <t>Pressure Resolution</t>
@@ -1126,16 +1090,7 @@
     <t>12.5 (4096)****, 6.3 (2048), 3.2 (1024), 1.7 (512), 0.9 (256) μA</t>
   </si>
   <si>
-    <t>0.012** (4096), 0.018 (2048), 0.027 (1024), 0.042 (512), 0.065 (256)</t>
-  </si>
-  <si>
     <t>±2.5 mbar</t>
-  </si>
-  <si>
-    <t>&lt; 0.01°C for OSR &gt; 256</t>
-  </si>
-  <si>
-    <t>0.012 for OSR = 256</t>
   </si>
   <si>
     <t>3.0</t>
@@ -1301,18 +1256,6 @@
   </si>
   <si>
     <t>62.5 deg/s</t>
-  </si>
-  <si>
-    <t>For typical VDD = 1.8 V</t>
-  </si>
-  <si>
-    <t>0.504 mW</t>
-  </si>
-  <si>
-    <t>1.314 mW</t>
-  </si>
-  <si>
-    <t>13.5 uW</t>
   </si>
   <si>
     <t>2097.2 LSB/(deg/s)</t>
@@ -1479,30 +1422,9 @@
     <t>2.2 uA</t>
   </si>
   <si>
-    <t>0.756 mW</t>
-  </si>
-  <si>
-    <t>0.216 mW</t>
-  </si>
-  <si>
-    <t>0.648 mW</t>
-  </si>
-  <si>
     <t>67 uA</t>
   </si>
   <si>
-    <t>0.117 mW</t>
-  </si>
-  <si>
-    <t>0.396 mW</t>
-  </si>
-  <si>
-    <t>0.378 mW</t>
-  </si>
-  <si>
-    <t>0.00396 mW</t>
-  </si>
-  <si>
     <t>4000 deg/s</t>
   </si>
   <si>
@@ -1534,6 +1456,108 @@
   </si>
   <si>
     <t>512 LSB/g</t>
+  </si>
+  <si>
+    <t>±10 mg</t>
+  </si>
+  <si>
+    <t>±20 mg</t>
+  </si>
+  <si>
+    <t>For typical VDD = 3.3 V</t>
+  </si>
+  <si>
+    <t>0.924 mW</t>
+  </si>
+  <si>
+    <t>2.409 mW</t>
+  </si>
+  <si>
+    <t>2.904 mW</t>
+  </si>
+  <si>
+    <t>24.75 uW</t>
+  </si>
+  <si>
+    <t>1.386 mW</t>
+  </si>
+  <si>
+    <t>396 uW</t>
+  </si>
+  <si>
+    <t>1.188 mW</t>
+  </si>
+  <si>
+    <t>726 uW</t>
+  </si>
+  <si>
+    <t>221.1 uW</t>
+  </si>
+  <si>
+    <t>693 uW</t>
+  </si>
+  <si>
+    <t>7.26 uW</t>
+  </si>
+  <si>
+    <t>1.6 mbar - 1.0 bar</t>
+  </si>
+  <si>
+    <t>160 Pa - 100 kPa</t>
+  </si>
+  <si>
+    <t>0,2 bar - 1,2 bar*</t>
+  </si>
+  <si>
+    <t>20 kPa - 120 kPa</t>
+  </si>
+  <si>
+    <t>2.9 psi - 17.4 psi</t>
+  </si>
+  <si>
+    <t>0.02 psi - 14.5 psi</t>
+  </si>
+  <si>
+    <t>12 bit</t>
+  </si>
+  <si>
+    <t>20 bits</t>
+  </si>
+  <si>
+    <t>24 bits</t>
+  </si>
+  <si>
+    <t>0.002°C (4096), 0.003 (2048), 0.005 (1024), 0.008 (512), 0.012 (256)</t>
+  </si>
+  <si>
+    <t>Pa (OSR)</t>
+  </si>
+  <si>
+    <t>1.2 (4096), 1,8 (2048), 2.7 (1024), 4.2 (512), 6.5 (256)</t>
+  </si>
+  <si>
+    <t>2.4 (4096), 3.6 (2048), 5.4 (1024), 8.4 (512), 13.0 (256)</t>
+  </si>
+  <si>
+    <t>SPI (Max)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I2C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Max)</t>
+    </r>
+  </si>
+  <si>
+    <t>I2C (Max)</t>
   </si>
 </sst>
 </file>
@@ -2190,7 +2214,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2338,403 +2362,46 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="6" borderId="21" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -2742,30 +2409,12 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2778,9 +2427,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2789,30 +2435,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2822,72 +2447,450 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="38" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="28" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="29" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="21" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="38" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="21" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="16" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="28" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="29" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3205,179 +3208,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="2" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="222"/>
-      <c r="B1" s="209" t="s">
+      <c r="A1" s="89"/>
+      <c r="B1" s="157" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="209"/>
-      <c r="D1" s="209"/>
-      <c r="E1" s="209"/>
-      <c r="F1" s="209"/>
-      <c r="G1" s="213" t="s">
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="156" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="193"/>
-      <c r="K1" s="214" t="s">
-        <v>251</v>
-      </c>
-      <c r="L1" s="214"/>
-      <c r="M1" s="214"/>
-      <c r="N1" s="214"/>
-      <c r="O1" s="214"/>
-      <c r="P1" s="214"/>
-      <c r="Q1" s="214"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="218" t="s">
-        <v>289</v>
-      </c>
-      <c r="T1" s="219"/>
-      <c r="U1" s="219"/>
-      <c r="V1" s="219"/>
-      <c r="W1" s="219"/>
-      <c r="X1" s="219"/>
-      <c r="Y1" s="219"/>
-      <c r="Z1" s="219"/>
-      <c r="AA1" s="220"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="152" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="161" t="s">
+        <v>270</v>
+      </c>
+      <c r="T1" s="162"/>
+      <c r="U1" s="162"/>
+      <c r="V1" s="162"/>
+      <c r="W1" s="162"/>
+      <c r="X1" s="162"/>
+      <c r="Y1" s="162"/>
+      <c r="Z1" s="162"/>
+      <c r="AA1" s="163"/>
     </row>
     <row r="2" spans="1:27" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="223" t="s">
+      <c r="A2" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="211"/>
-      <c r="C2" s="211"/>
-      <c r="D2" s="211"/>
-      <c r="E2" s="211"/>
-      <c r="F2" s="211"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="211"/>
-      <c r="I2" s="211"/>
-      <c r="J2" s="212"/>
-      <c r="K2" s="217"/>
-      <c r="L2" s="217"/>
-      <c r="M2" s="217"/>
-      <c r="N2" s="217"/>
-      <c r="O2" s="211"/>
-      <c r="P2" s="211"/>
-      <c r="Q2" s="211"/>
-      <c r="R2" s="212"/>
-      <c r="S2" s="216"/>
-      <c r="T2" s="217"/>
-      <c r="U2" s="217"/>
-      <c r="V2" s="217"/>
-      <c r="W2" s="211"/>
-      <c r="X2" s="211"/>
-      <c r="Y2" s="211"/>
-      <c r="Z2" s="211"/>
-      <c r="AA2" s="212"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="88"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
+      <c r="R2" s="86"/>
+      <c r="S2" s="87"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
+      <c r="W2" s="85"/>
+      <c r="X2" s="85"/>
+      <c r="Y2" s="85"/>
+      <c r="Z2" s="85"/>
+      <c r="AA2" s="86"/>
     </row>
     <row r="3" spans="1:27" s="16" customFormat="1" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="224" t="s">
+      <c r="A3" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="165" t="s">
+      <c r="B3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="165" t="s">
+      <c r="C3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="165" t="s">
+      <c r="D3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="156" t="s">
+      <c r="E3" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="156"/>
-      <c r="G3" s="164" t="s">
+      <c r="F3" s="105"/>
+      <c r="G3" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="165" t="s">
+      <c r="H3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="165" t="s">
+      <c r="I3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J3" s="167" t="s">
+      <c r="J3" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="K3" s="173" t="s">
+      <c r="K3" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="173"/>
-      <c r="M3" s="173" t="s">
+      <c r="L3" s="122"/>
+      <c r="M3" s="122" t="s">
         <v>66</v>
       </c>
-      <c r="N3" s="173"/>
-      <c r="O3" s="173" t="s">
+      <c r="N3" s="122"/>
+      <c r="O3" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="P3" s="173"/>
-      <c r="Q3" s="173" t="s">
+      <c r="P3" s="122"/>
+      <c r="Q3" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="R3" s="78"/>
-      <c r="S3" s="71" t="s">
+      <c r="R3" s="143"/>
+      <c r="S3" s="164" t="s">
         <v>65</v>
       </c>
-      <c r="T3" s="173"/>
-      <c r="U3" s="173" t="s">
+      <c r="T3" s="122"/>
+      <c r="U3" s="122" t="s">
         <v>66</v>
       </c>
-      <c r="V3" s="173"/>
-      <c r="W3" s="173" t="s">
+      <c r="V3" s="122"/>
+      <c r="W3" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="X3" s="173"/>
-      <c r="Y3" s="173" t="s">
+      <c r="X3" s="122"/>
+      <c r="Y3" s="122" t="s">
         <v>68</v>
       </c>
-      <c r="Z3" s="173"/>
+      <c r="Z3" s="122"/>
       <c r="AA3" s="23" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="225" t="s">
+      <c r="A4" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="172" t="s">
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="156"/>
-      <c r="I4" s="156"/>
-      <c r="J4" s="175"/>
-      <c r="K4" s="173" t="s">
-        <v>252</v>
-      </c>
-      <c r="L4" s="70"/>
-      <c r="M4" s="70"/>
-      <c r="N4" s="70"/>
-      <c r="O4" s="70"/>
-      <c r="P4" s="70"/>
-      <c r="Q4" s="70"/>
-      <c r="R4" s="78"/>
-      <c r="S4" s="71" t="s">
-        <v>252</v>
-      </c>
-      <c r="T4" s="70"/>
-      <c r="U4" s="70"/>
-      <c r="V4" s="70"/>
-      <c r="W4" s="70"/>
-      <c r="X4" s="70"/>
-      <c r="Y4" s="70"/>
-      <c r="Z4" s="70"/>
-      <c r="AA4" s="78"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="122" t="s">
+        <v>237</v>
+      </c>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="143"/>
+      <c r="S4" s="164" t="s">
+        <v>237</v>
+      </c>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="W4" s="122"/>
+      <c r="X4" s="122"/>
+      <c r="Y4" s="122"/>
+      <c r="Z4" s="122"/>
+      <c r="AA4" s="143"/>
     </row>
     <row r="5" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="225" t="s">
+      <c r="A5" s="92" t="s">
         <v>71</v>
       </c>
       <c r="B5" s="12" t="s">
@@ -3389,11 +3392,11 @@
       <c r="D5" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="84" t="s">
+      <c r="E5" s="131" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="84"/>
-      <c r="G5" s="234" t="s">
+      <c r="F5" s="131"/>
+      <c r="G5" s="72" t="s">
         <v>29</v>
       </c>
       <c r="H5" s="12" t="s">
@@ -3402,127 +3405,127 @@
       <c r="I5" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="J5" s="235" t="s">
+      <c r="J5" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="173" t="s">
+      <c r="K5" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70" t="s">
+      <c r="L5" s="122"/>
+      <c r="M5" s="122" t="s">
         <v>89</v>
       </c>
-      <c r="N5" s="70"/>
-      <c r="O5" s="70" t="s">
+      <c r="N5" s="122"/>
+      <c r="O5" s="122" t="s">
         <v>88</v>
       </c>
-      <c r="P5" s="70"/>
-      <c r="Q5" s="70" t="s">
+      <c r="P5" s="122"/>
+      <c r="Q5" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="R5" s="78"/>
-      <c r="S5" s="71" t="s">
+      <c r="R5" s="143"/>
+      <c r="S5" s="164" t="s">
         <v>29</v>
       </c>
-      <c r="T5" s="70"/>
-      <c r="U5" s="70" t="s">
+      <c r="T5" s="122"/>
+      <c r="U5" s="122" t="s">
         <v>89</v>
       </c>
-      <c r="V5" s="70"/>
-      <c r="W5" s="70" t="s">
+      <c r="V5" s="122"/>
+      <c r="W5" s="122" t="s">
         <v>88</v>
       </c>
-      <c r="X5" s="70"/>
-      <c r="Y5" s="70" t="s">
+      <c r="X5" s="122"/>
+      <c r="Y5" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="Z5" s="70"/>
+      <c r="Z5" s="122"/>
       <c r="AA5" s="23" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="226" t="s">
+      <c r="A6" s="154" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="169" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="81" t="s">
+      <c r="C6" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81" t="s">
+      <c r="D6" s="107"/>
+      <c r="E6" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="176"/>
-      <c r="G6" s="168" t="s">
+      <c r="F6" s="107"/>
+      <c r="G6" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="169" t="s">
+      <c r="H6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="176" t="s">
+      <c r="I6" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="181"/>
-      <c r="K6" s="173" t="s">
-        <v>253</v>
-      </c>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="71" t="s">
-        <v>296</v>
-      </c>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
-      <c r="V6" s="70"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="70"/>
-      <c r="Y6" s="70"/>
-      <c r="Z6" s="70"/>
-      <c r="AA6" s="78"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="122" t="s">
+        <v>238</v>
+      </c>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="122"/>
+      <c r="O6" s="122"/>
+      <c r="P6" s="122"/>
+      <c r="Q6" s="122"/>
+      <c r="R6" s="143"/>
+      <c r="S6" s="164" t="s">
+        <v>277</v>
+      </c>
+      <c r="T6" s="122"/>
+      <c r="U6" s="122"/>
+      <c r="V6" s="122"/>
+      <c r="W6" s="122"/>
+      <c r="X6" s="122"/>
+      <c r="Y6" s="122"/>
+      <c r="Z6" s="122"/>
+      <c r="AA6" s="143"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="226"/>
-      <c r="B7" s="156" t="s">
+      <c r="A7" s="154"/>
+      <c r="B7" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="172" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="104" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="156"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="175"/>
-      <c r="K7" s="173"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="70"/>
-      <c r="Q7" s="70"/>
-      <c r="R7" s="78"/>
-      <c r="S7" s="71"/>
-      <c r="T7" s="70"/>
-      <c r="U7" s="70"/>
-      <c r="V7" s="70"/>
-      <c r="W7" s="70"/>
-      <c r="X7" s="70"/>
-      <c r="Y7" s="70"/>
-      <c r="Z7" s="70"/>
-      <c r="AA7" s="78"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="109"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="122"/>
+      <c r="M7" s="122"/>
+      <c r="N7" s="122"/>
+      <c r="O7" s="122"/>
+      <c r="P7" s="122"/>
+      <c r="Q7" s="122"/>
+      <c r="R7" s="143"/>
+      <c r="S7" s="164"/>
+      <c r="T7" s="122"/>
+      <c r="U7" s="122"/>
+      <c r="V7" s="122"/>
+      <c r="W7" s="122"/>
+      <c r="X7" s="122"/>
+      <c r="Y7" s="122"/>
+      <c r="Z7" s="122"/>
+      <c r="AA7" s="143"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="225" t="s">
+      <c r="A8" s="92" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="22"/>
@@ -3530,371 +3533,384 @@
       <c r="D8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="76"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="172" t="s">
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="156"/>
-      <c r="I8" s="156"/>
-      <c r="J8" s="175"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="109"/>
+      <c r="K8" s="238" t="s">
+        <v>308</v>
+      </c>
+      <c r="L8" s="122"/>
+      <c r="M8" s="122"/>
+      <c r="N8" s="122"/>
+      <c r="O8" s="122"/>
+      <c r="P8" s="122"/>
+      <c r="Q8" s="122"/>
+      <c r="R8" s="143"/>
+      <c r="S8" s="164" t="s">
+        <v>307</v>
+      </c>
+      <c r="T8" s="122"/>
+      <c r="U8" s="122"/>
+      <c r="V8" s="122"/>
+      <c r="W8" s="122"/>
+      <c r="X8" s="122"/>
+      <c r="Y8" s="122"/>
+      <c r="Z8" s="122"/>
+      <c r="AA8" s="143"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="227" t="s">
+      <c r="A9" s="155" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="76" t="s">
+      <c r="B9" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="76"/>
-      <c r="D9" s="76"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="172" t="s">
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="104" t="s">
         <v>114</v>
       </c>
-      <c r="H9" s="156"/>
-      <c r="I9" s="156"/>
-      <c r="J9" s="175"/>
-      <c r="K9" s="170" t="s">
-        <v>258</v>
-      </c>
-      <c r="L9" s="73"/>
-      <c r="M9" s="73"/>
-      <c r="N9" s="73"/>
-      <c r="O9" s="73" t="s">
-        <v>259</v>
-      </c>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="73"/>
-      <c r="R9" s="74"/>
-      <c r="S9" s="72" t="s">
-        <v>292</v>
-      </c>
-      <c r="T9" s="73"/>
-      <c r="U9" s="73"/>
-      <c r="V9" s="73"/>
-      <c r="W9" s="73"/>
-      <c r="X9" s="73"/>
-      <c r="Y9" s="73"/>
-      <c r="Z9" s="73"/>
-      <c r="AA9" s="74"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="109"/>
+      <c r="K9" s="103" t="s">
+        <v>243</v>
+      </c>
+      <c r="L9" s="103"/>
+      <c r="M9" s="103"/>
+      <c r="N9" s="103"/>
+      <c r="O9" s="103" t="s">
+        <v>244</v>
+      </c>
+      <c r="P9" s="103"/>
+      <c r="Q9" s="103"/>
+      <c r="R9" s="144"/>
+      <c r="S9" s="165" t="s">
+        <v>273</v>
+      </c>
+      <c r="T9" s="103"/>
+      <c r="U9" s="103"/>
+      <c r="V9" s="103"/>
+      <c r="W9" s="103"/>
+      <c r="X9" s="103"/>
+      <c r="Y9" s="103"/>
+      <c r="Z9" s="103"/>
+      <c r="AA9" s="144"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="227"/>
-      <c r="B10" s="76"/>
-      <c r="C10" s="76"/>
-      <c r="D10" s="76"/>
-      <c r="E10" s="76"/>
-      <c r="F10" s="156"/>
-      <c r="G10" s="172" t="s">
+      <c r="A10" s="155"/>
+      <c r="B10" s="105"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="104" t="s">
         <v>128</v>
       </c>
-      <c r="H10" s="156"/>
-      <c r="I10" s="156"/>
-      <c r="J10" s="175"/>
-      <c r="K10" s="173" t="s">
-        <v>260</v>
-      </c>
-      <c r="L10" s="70"/>
-      <c r="M10" s="70"/>
-      <c r="N10" s="70"/>
-      <c r="O10" s="70" t="s">
-        <v>261</v>
-      </c>
-      <c r="P10" s="70"/>
-      <c r="Q10" s="70"/>
-      <c r="R10" s="78"/>
-      <c r="S10" s="71" t="s">
-        <v>293</v>
-      </c>
-      <c r="T10" s="70"/>
-      <c r="U10" s="70"/>
-      <c r="V10" s="70"/>
-      <c r="W10" s="70"/>
-      <c r="X10" s="70"/>
-      <c r="Y10" s="70" t="s">
-        <v>294</v>
-      </c>
-      <c r="Z10" s="70"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="109"/>
+      <c r="K10" s="122" t="s">
+        <v>245</v>
+      </c>
+      <c r="L10" s="122"/>
+      <c r="M10" s="122"/>
+      <c r="N10" s="122"/>
+      <c r="O10" s="122" t="s">
+        <v>246</v>
+      </c>
+      <c r="P10" s="122"/>
+      <c r="Q10" s="122"/>
+      <c r="R10" s="143"/>
+      <c r="S10" s="164" t="s">
+        <v>274</v>
+      </c>
+      <c r="T10" s="122"/>
+      <c r="U10" s="122"/>
+      <c r="V10" s="122"/>
+      <c r="W10" s="122"/>
+      <c r="X10" s="122"/>
+      <c r="Y10" s="122" t="s">
+        <v>275</v>
+      </c>
+      <c r="Z10" s="122"/>
       <c r="AA10" s="23" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="228" t="s">
-        <v>326</v>
-      </c>
-      <c r="B11" s="221" t="s">
+      <c r="A11" s="151" t="s">
+        <v>300</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C11" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="103"/>
       <c r="F11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="168" t="s">
+      <c r="G11" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="176" t="s">
+      <c r="H11" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="176"/>
-      <c r="J11" s="177" t="s">
+      <c r="I11" s="107"/>
+      <c r="J11" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="170" t="s">
-        <v>254</v>
-      </c>
-      <c r="L11" s="73"/>
-      <c r="M11" s="73" t="s">
+      <c r="K11" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="L11" s="103"/>
+      <c r="M11" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="N11" s="73"/>
-      <c r="O11" s="73"/>
-      <c r="P11" s="73"/>
-      <c r="Q11" s="73" t="s">
-        <v>255</v>
-      </c>
-      <c r="R11" s="74"/>
-      <c r="S11" s="72" t="s">
-        <v>254</v>
-      </c>
-      <c r="T11" s="73"/>
-      <c r="U11" s="73" t="s">
+      <c r="N11" s="103"/>
+      <c r="O11" s="103"/>
+      <c r="P11" s="103"/>
+      <c r="Q11" s="103" t="s">
+        <v>240</v>
+      </c>
+      <c r="R11" s="144"/>
+      <c r="S11" s="165" t="s">
+        <v>239</v>
+      </c>
+      <c r="T11" s="103"/>
+      <c r="U11" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="V11" s="73"/>
-      <c r="W11" s="73"/>
-      <c r="X11" s="73"/>
-      <c r="Y11" s="73" t="s">
-        <v>255</v>
-      </c>
-      <c r="Z11" s="73"/>
-      <c r="AA11" s="74"/>
+      <c r="V11" s="103"/>
+      <c r="W11" s="103"/>
+      <c r="X11" s="103"/>
+      <c r="Y11" s="103" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z11" s="103"/>
+      <c r="AA11" s="144"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="228"/>
-      <c r="B12" s="165" t="s">
+      <c r="A12" s="151"/>
+      <c r="B12" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="105" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
       <c r="F12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="164" t="s">
+      <c r="G12" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="H12" s="156" t="s">
+      <c r="H12" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="156"/>
-      <c r="J12" s="167" t="s">
+      <c r="I12" s="105"/>
+      <c r="J12" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="K12" s="156" t="s">
+      <c r="K12" s="105" t="s">
         <v>91</v>
       </c>
-      <c r="L12" s="76"/>
-      <c r="M12" s="76" t="s">
+      <c r="L12" s="105"/>
+      <c r="M12" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="N12" s="76"/>
-      <c r="O12" s="76"/>
-      <c r="P12" s="76"/>
-      <c r="Q12" s="76" t="s">
+      <c r="N12" s="105"/>
+      <c r="O12" s="105"/>
+      <c r="P12" s="105"/>
+      <c r="Q12" s="105" t="s">
         <v>56</v>
       </c>
-      <c r="R12" s="77"/>
-      <c r="S12" s="75" t="s">
+      <c r="R12" s="149"/>
+      <c r="S12" s="113" t="s">
         <v>91</v>
       </c>
-      <c r="T12" s="76"/>
-      <c r="U12" s="76" t="s">
+      <c r="T12" s="105"/>
+      <c r="U12" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="V12" s="76"/>
-      <c r="W12" s="76"/>
-      <c r="X12" s="76"/>
-      <c r="Y12" s="76" t="s">
+      <c r="V12" s="105"/>
+      <c r="W12" s="105"/>
+      <c r="X12" s="105"/>
+      <c r="Y12" s="105" t="s">
         <v>56</v>
       </c>
-      <c r="Z12" s="76"/>
-      <c r="AA12" s="77"/>
+      <c r="Z12" s="105"/>
+      <c r="AA12" s="149"/>
     </row>
     <row r="13" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="229" t="s">
+      <c r="A13" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="165" t="s">
+      <c r="B13" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="76" t="s">
+      <c r="C13" s="105" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="76"/>
-      <c r="E13" s="76"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
       <c r="F13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="164" t="s">
+      <c r="G13" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="156" t="s">
+      <c r="H13" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="156"/>
-      <c r="J13" s="167" t="s">
+      <c r="I13" s="105"/>
+      <c r="J13" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="K13" s="156" t="s">
+      <c r="K13" s="105" t="s">
         <v>91</v>
       </c>
-      <c r="L13" s="76"/>
-      <c r="M13" s="76" t="s">
+      <c r="L13" s="105"/>
+      <c r="M13" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="N13" s="76"/>
-      <c r="O13" s="76"/>
-      <c r="P13" s="76"/>
-      <c r="Q13" s="76" t="s">
+      <c r="N13" s="105"/>
+      <c r="O13" s="105"/>
+      <c r="P13" s="105"/>
+      <c r="Q13" s="105" t="s">
         <v>56</v>
       </c>
-      <c r="R13" s="77"/>
-      <c r="S13" s="75" t="s">
-        <v>303</v>
-      </c>
-      <c r="T13" s="76"/>
-      <c r="U13" s="76" t="s">
+      <c r="R13" s="149"/>
+      <c r="S13" s="113" t="s">
+        <v>284</v>
+      </c>
+      <c r="T13" s="105"/>
+      <c r="U13" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="V13" s="76"/>
-      <c r="W13" s="76"/>
-      <c r="X13" s="76"/>
-      <c r="Y13" s="76" t="s">
+      <c r="V13" s="105"/>
+      <c r="W13" s="105"/>
+      <c r="X13" s="105"/>
+      <c r="Y13" s="105" t="s">
         <v>56</v>
       </c>
-      <c r="Z13" s="76"/>
-      <c r="AA13" s="77"/>
+      <c r="Z13" s="105"/>
+      <c r="AA13" s="149"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="228" t="s">
+      <c r="A14" s="151" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="176" t="s">
+      <c r="B14" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="81"/>
-      <c r="D14" s="81" t="s">
+      <c r="C14" s="107"/>
+      <c r="D14" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="180" t="s">
+      <c r="E14" s="107"/>
+      <c r="F14" s="107"/>
+      <c r="G14" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="176"/>
-      <c r="I14" s="176" t="s">
+      <c r="H14" s="107"/>
+      <c r="I14" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="181"/>
-      <c r="K14" s="170" t="s">
-        <v>254</v>
-      </c>
-      <c r="L14" s="73"/>
-      <c r="M14" s="73"/>
-      <c r="N14" s="73"/>
-      <c r="O14" s="73" t="s">
-        <v>255</v>
-      </c>
-      <c r="P14" s="73"/>
-      <c r="Q14" s="73"/>
-      <c r="R14" s="74"/>
-      <c r="S14" s="72" t="s">
-        <v>297</v>
-      </c>
-      <c r="T14" s="73"/>
-      <c r="U14" s="73"/>
-      <c r="V14" s="73"/>
-      <c r="W14" s="73" t="s">
-        <v>298</v>
-      </c>
-      <c r="X14" s="73"/>
-      <c r="Y14" s="73"/>
-      <c r="Z14" s="73"/>
+      <c r="J14" s="108"/>
+      <c r="K14" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="L14" s="103"/>
+      <c r="M14" s="103"/>
+      <c r="N14" s="103"/>
+      <c r="O14" s="103" t="s">
+        <v>240</v>
+      </c>
+      <c r="P14" s="103"/>
+      <c r="Q14" s="103"/>
+      <c r="R14" s="144"/>
+      <c r="S14" s="165" t="s">
+        <v>278</v>
+      </c>
+      <c r="T14" s="103"/>
+      <c r="U14" s="103"/>
+      <c r="V14" s="103"/>
+      <c r="W14" s="103" t="s">
+        <v>279</v>
+      </c>
+      <c r="X14" s="103"/>
+      <c r="Y14" s="103"/>
+      <c r="Z14" s="103"/>
       <c r="AA14" s="59"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="228"/>
-      <c r="B15" s="156" t="s">
+      <c r="A15" s="151"/>
+      <c r="B15" s="105" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="76"/>
-      <c r="D15" s="76" t="s">
+      <c r="C15" s="105"/>
+      <c r="D15" s="105" t="s">
         <v>95</v>
       </c>
-      <c r="E15" s="76"/>
-      <c r="F15" s="76"/>
-      <c r="G15" s="172" t="s">
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="104" t="s">
         <v>116</v>
       </c>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156" t="s">
+      <c r="H15" s="105"/>
+      <c r="I15" s="105" t="s">
         <v>117</v>
       </c>
-      <c r="J15" s="175"/>
-      <c r="K15" s="173" t="s">
-        <v>256</v>
-      </c>
-      <c r="L15" s="70"/>
-      <c r="M15" s="70"/>
-      <c r="N15" s="70"/>
-      <c r="O15" s="70" t="s">
-        <v>257</v>
-      </c>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="70"/>
-      <c r="R15" s="78"/>
-      <c r="S15" s="71" t="s">
-        <v>299</v>
-      </c>
-      <c r="T15" s="70"/>
-      <c r="U15" s="73" t="s">
-        <v>300</v>
-      </c>
-      <c r="V15" s="73"/>
-      <c r="W15" s="73" t="s">
-        <v>301</v>
-      </c>
-      <c r="X15" s="73"/>
-      <c r="Y15" s="73" t="s">
-        <v>302</v>
-      </c>
-      <c r="Z15" s="73"/>
+      <c r="J15" s="109"/>
+      <c r="K15" s="122" t="s">
+        <v>241</v>
+      </c>
+      <c r="L15" s="122"/>
+      <c r="M15" s="122"/>
+      <c r="N15" s="122"/>
+      <c r="O15" s="122" t="s">
+        <v>242</v>
+      </c>
+      <c r="P15" s="122"/>
+      <c r="Q15" s="122"/>
+      <c r="R15" s="143"/>
+      <c r="S15" s="164" t="s">
+        <v>280</v>
+      </c>
+      <c r="T15" s="122"/>
+      <c r="U15" s="103" t="s">
+        <v>281</v>
+      </c>
+      <c r="V15" s="103"/>
+      <c r="W15" s="103" t="s">
+        <v>282</v>
+      </c>
+      <c r="X15" s="103"/>
+      <c r="Y15" s="103" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z15" s="103"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="228" t="s">
+      <c r="A16" s="151" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="176" t="s">
+      <c r="B16" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="81"/>
+      <c r="C16" s="107"/>
       <c r="D16" s="5" t="s">
         <v>97</v>
       </c>
@@ -3904,64 +3920,64 @@
       <c r="F16" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="G16" s="168" t="s">
+      <c r="G16" s="67" t="s">
         <v>96</v>
       </c>
-      <c r="H16" s="169" t="s">
+      <c r="H16" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="I16" s="169" t="s">
+      <c r="I16" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="J16" s="177" t="s">
+      <c r="J16" s="70" t="s">
         <v>118</v>
       </c>
-      <c r="K16" s="170" t="s">
-        <v>262</v>
-      </c>
-      <c r="L16" s="73"/>
-      <c r="M16" s="73" t="s">
-        <v>263</v>
-      </c>
-      <c r="N16" s="73"/>
-      <c r="O16" s="73" t="s">
-        <v>264</v>
-      </c>
-      <c r="P16" s="73"/>
-      <c r="Q16" s="73" t="s">
-        <v>265</v>
-      </c>
-      <c r="R16" s="74"/>
-      <c r="S16" s="72" t="s">
-        <v>304</v>
-      </c>
-      <c r="T16" s="73"/>
+      <c r="K16" s="103" t="s">
+        <v>247</v>
+      </c>
+      <c r="L16" s="103"/>
+      <c r="M16" s="103" t="s">
+        <v>248</v>
+      </c>
+      <c r="N16" s="103"/>
+      <c r="O16" s="103" t="s">
+        <v>249</v>
+      </c>
+      <c r="P16" s="103"/>
+      <c r="Q16" s="103" t="s">
+        <v>250</v>
+      </c>
+      <c r="R16" s="144"/>
+      <c r="S16" s="165" t="s">
+        <v>285</v>
+      </c>
+      <c r="T16" s="103"/>
       <c r="U16" s="58" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="W16" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="X16" s="73" t="s">
-        <v>307</v>
-      </c>
-      <c r="Y16" s="73"/>
+        <v>287</v>
+      </c>
+      <c r="W16" s="103" t="s">
+        <v>288</v>
+      </c>
+      <c r="X16" s="103"/>
+      <c r="Y16" s="4" t="s">
+        <v>286</v>
+      </c>
       <c r="Z16" s="4" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="AA16" s="53" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A17" s="228"/>
-      <c r="B17" s="156" t="s">
+      <c r="A17" s="151"/>
+      <c r="B17" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="C17" s="76"/>
+      <c r="C17" s="105"/>
       <c r="D17" s="1" t="s">
         <v>101</v>
       </c>
@@ -3971,103 +3987,103 @@
       <c r="F17" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G17" s="164" t="s">
+      <c r="G17" s="65" t="s">
         <v>120</v>
       </c>
-      <c r="H17" s="165" t="s">
+      <c r="H17" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="I17" s="165" t="s">
+      <c r="I17" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J17" s="167" t="s">
+      <c r="J17" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="K17" s="173" t="s">
-        <v>270</v>
-      </c>
-      <c r="L17" s="70"/>
-      <c r="M17" s="70" t="s">
-        <v>266</v>
-      </c>
-      <c r="N17" s="70"/>
-      <c r="O17" s="70" t="s">
-        <v>267</v>
-      </c>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="70" t="s">
-        <v>268</v>
-      </c>
-      <c r="R17" s="78"/>
-      <c r="S17" s="71" t="s">
-        <v>308</v>
-      </c>
-      <c r="T17" s="70"/>
+      <c r="K17" s="122" t="s">
+        <v>255</v>
+      </c>
+      <c r="L17" s="122"/>
+      <c r="M17" s="122" t="s">
+        <v>251</v>
+      </c>
+      <c r="N17" s="122"/>
+      <c r="O17" s="122" t="s">
+        <v>252</v>
+      </c>
+      <c r="P17" s="122"/>
+      <c r="Q17" s="122" t="s">
+        <v>253</v>
+      </c>
+      <c r="R17" s="143"/>
+      <c r="S17" s="164" t="s">
+        <v>289</v>
+      </c>
+      <c r="T17" s="122"/>
       <c r="U17" s="57" t="s">
+        <v>290</v>
+      </c>
+      <c r="V17" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="W17" s="122" t="s">
+        <v>292</v>
+      </c>
+      <c r="X17" s="122"/>
+      <c r="Y17" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="Z17" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="AA17" s="23" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A18" s="151" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="107" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="107"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="107"/>
+      <c r="G18" s="106" t="s">
+        <v>123</v>
+      </c>
+      <c r="H18" s="107"/>
+      <c r="I18" s="107"/>
+      <c r="J18" s="108"/>
+      <c r="K18" s="103" t="s">
         <v>309</v>
       </c>
-      <c r="V17" s="22" t="s">
-        <v>310</v>
-      </c>
-      <c r="W17" s="22" t="s">
-        <v>317</v>
-      </c>
-      <c r="X17" s="70" t="s">
-        <v>311</v>
-      </c>
-      <c r="Y17" s="70"/>
-      <c r="Z17" s="22" t="s">
-        <v>312</v>
-      </c>
-      <c r="AA17" s="23" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" s="228" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" s="176" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="176"/>
-      <c r="G18" s="180" t="s">
-        <v>123</v>
-      </c>
-      <c r="H18" s="176"/>
-      <c r="I18" s="176"/>
-      <c r="J18" s="181"/>
-      <c r="K18" s="170" t="s">
-        <v>274</v>
-      </c>
-      <c r="L18" s="73"/>
-      <c r="M18" s="73"/>
-      <c r="N18" s="73"/>
-      <c r="O18" s="73"/>
-      <c r="P18" s="73"/>
-      <c r="Q18" s="73"/>
-      <c r="R18" s="74"/>
-      <c r="S18" s="72" t="s">
-        <v>274</v>
-      </c>
-      <c r="T18" s="73"/>
-      <c r="U18" s="73"/>
-      <c r="V18" s="73"/>
-      <c r="W18" s="73"/>
-      <c r="X18" s="73"/>
-      <c r="Y18" s="73"/>
-      <c r="Z18" s="73"/>
-      <c r="AA18" s="74"/>
+      <c r="L18" s="103"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="103"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="103"/>
+      <c r="Q18" s="103"/>
+      <c r="R18" s="144"/>
+      <c r="S18" s="165" t="s">
+        <v>309</v>
+      </c>
+      <c r="T18" s="103"/>
+      <c r="U18" s="103"/>
+      <c r="V18" s="103"/>
+      <c r="W18" s="103"/>
+      <c r="X18" s="103"/>
+      <c r="Y18" s="103"/>
+      <c r="Z18" s="103"/>
+      <c r="AA18" s="144"/>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A19" s="228"/>
-      <c r="B19" s="156" t="s">
+      <c r="A19" s="151"/>
+      <c r="B19" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="76"/>
+      <c r="C19" s="105"/>
       <c r="D19" s="1" t="s">
         <v>105</v>
       </c>
@@ -4077,138 +4093,138 @@
       <c r="F19" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G19" s="164" t="s">
+      <c r="G19" s="65" t="s">
         <v>124</v>
       </c>
-      <c r="H19" s="165" t="s">
+      <c r="H19" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I19" s="165" t="s">
+      <c r="I19" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="J19" s="167" t="s">
+      <c r="J19" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="K19" s="173" t="s">
-        <v>275</v>
-      </c>
-      <c r="L19" s="70"/>
-      <c r="M19" s="70" t="s">
-        <v>276</v>
-      </c>
-      <c r="N19" s="70"/>
-      <c r="O19" s="88">
-        <v>1584</v>
-      </c>
-      <c r="P19" s="70"/>
-      <c r="Q19" s="70" t="s">
-        <v>277</v>
-      </c>
-      <c r="R19" s="78"/>
-      <c r="S19" s="71" t="s">
+      <c r="K19" s="122" t="s">
+        <v>310</v>
+      </c>
+      <c r="L19" s="122"/>
+      <c r="M19" s="122" t="s">
+        <v>311</v>
+      </c>
+      <c r="N19" s="122"/>
+      <c r="O19" s="150" t="s">
+        <v>312</v>
+      </c>
+      <c r="P19" s="122"/>
+      <c r="Q19" s="122" t="s">
+        <v>313</v>
+      </c>
+      <c r="R19" s="143"/>
+      <c r="S19" s="164" t="s">
         <v>314</v>
       </c>
-      <c r="T19" s="70"/>
+      <c r="T19" s="122"/>
       <c r="U19" s="22" t="s">
         <v>315</v>
       </c>
       <c r="V19" s="22" t="s">
         <v>316</v>
       </c>
-      <c r="W19" s="55" t="s">
+      <c r="W19" s="122" t="s">
+        <v>317</v>
+      </c>
+      <c r="X19" s="122"/>
+      <c r="Y19" s="55" t="s">
         <v>318</v>
       </c>
-      <c r="X19" s="70" t="s">
+      <c r="Z19" s="22" t="s">
         <v>319</v>
       </c>
-      <c r="Y19" s="70"/>
-      <c r="Z19" s="22" t="s">
+      <c r="AA19" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="AA19" s="23" t="s">
-        <v>321</v>
-      </c>
     </row>
     <row r="20" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="225" t="s">
+      <c r="A20" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="156" t="s">
+      <c r="B20" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="76"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="172" t="s">
+      <c r="C20" s="105"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="H20" s="156"/>
-      <c r="I20" s="156"/>
-      <c r="J20" s="175"/>
-      <c r="K20" s="233" t="s">
-        <v>269</v>
-      </c>
-      <c r="L20" s="62"/>
-      <c r="M20" s="62"/>
-      <c r="N20" s="62"/>
-      <c r="O20" s="62"/>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="62"/>
-      <c r="R20" s="63"/>
-      <c r="S20" s="61" t="s">
-        <v>269</v>
-      </c>
-      <c r="T20" s="62"/>
-      <c r="U20" s="62"/>
-      <c r="V20" s="62"/>
-      <c r="W20" s="62"/>
-      <c r="X20" s="62"/>
-      <c r="Y20" s="62"/>
-      <c r="Z20" s="62"/>
-      <c r="AA20" s="63"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="109"/>
+      <c r="K20" s="145" t="s">
+        <v>254</v>
+      </c>
+      <c r="L20" s="145"/>
+      <c r="M20" s="145"/>
+      <c r="N20" s="145"/>
+      <c r="O20" s="145"/>
+      <c r="P20" s="145"/>
+      <c r="Q20" s="145"/>
+      <c r="R20" s="146"/>
+      <c r="S20" s="166" t="s">
+        <v>254</v>
+      </c>
+      <c r="T20" s="145"/>
+      <c r="U20" s="145"/>
+      <c r="V20" s="145"/>
+      <c r="W20" s="145"/>
+      <c r="X20" s="145"/>
+      <c r="Y20" s="145"/>
+      <c r="Z20" s="145"/>
+      <c r="AA20" s="146"/>
     </row>
     <row r="21" spans="1:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="225" t="s">
+      <c r="A21" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="156" t="s">
+      <c r="B21" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="76"/>
-      <c r="D21" s="76"/>
-      <c r="E21" s="76"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="236" t="s">
+      <c r="C21" s="105"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="158" t="s">
         <v>34</v>
       </c>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="237"/>
-      <c r="K21" s="65" t="s">
+      <c r="H21" s="159"/>
+      <c r="I21" s="159"/>
+      <c r="J21" s="160"/>
+      <c r="K21" s="147" t="s">
         <v>34</v>
       </c>
-      <c r="L21" s="65"/>
-      <c r="M21" s="65"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="65"/>
-      <c r="P21" s="65"/>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="66"/>
-      <c r="S21" s="64" t="s">
+      <c r="L21" s="147"/>
+      <c r="M21" s="147"/>
+      <c r="N21" s="147"/>
+      <c r="O21" s="147"/>
+      <c r="P21" s="147"/>
+      <c r="Q21" s="147"/>
+      <c r="R21" s="148"/>
+      <c r="S21" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="T21" s="65"/>
-      <c r="U21" s="65"/>
-      <c r="V21" s="65"/>
-      <c r="W21" s="65"/>
-      <c r="X21" s="65"/>
-      <c r="Y21" s="65"/>
-      <c r="Z21" s="65"/>
-      <c r="AA21" s="66"/>
+      <c r="T21" s="147"/>
+      <c r="U21" s="147"/>
+      <c r="V21" s="147"/>
+      <c r="W21" s="147"/>
+      <c r="X21" s="147"/>
+      <c r="Y21" s="147"/>
+      <c r="Z21" s="147"/>
+      <c r="AA21" s="148"/>
     </row>
     <row r="22" spans="1:27" s="18" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="230" t="s">
+      <c r="A22" s="94" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="17"/>
@@ -4216,10 +4232,10 @@
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
-      <c r="G22" s="238"/>
-      <c r="H22" s="205"/>
-      <c r="I22" s="205"/>
-      <c r="J22" s="239"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="98"/>
       <c r="O22" s="24"/>
       <c r="P22" s="24"/>
       <c r="Q22" s="24"/>
@@ -4231,10 +4247,10 @@
       <c r="AA22" s="25"/>
     </row>
     <row r="23" spans="1:27" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="225" t="s">
+      <c r="A23" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="165" t="s">
+      <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -4249,26 +4265,26 @@
       <c r="F23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G23" s="206" t="s">
+      <c r="G23" s="81" t="s">
         <v>108</v>
       </c>
-      <c r="H23" s="207" t="s">
+      <c r="H23" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="I23" s="207" t="s">
+      <c r="I23" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="J23" s="208" t="s">
+      <c r="J23" s="83" t="s">
         <v>37</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>36</v>
@@ -4286,13 +4302,13 @@
         <v>37</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="V23" s="1" t="s">
         <v>36</v>
@@ -4310,14 +4326,14 @@
         <v>37</v>
       </c>
       <c r="AA23" s="23" t="s">
-        <v>322</v>
+        <v>296</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="225" t="s">
+      <c r="A24" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="166" t="s">
+      <c r="B24" s="22" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -4332,200 +4348,200 @@
       <c r="F24" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="164" t="s">
+      <c r="G24" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="H24" s="165" t="s">
+      <c r="H24" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I24" s="165" t="s">
+      <c r="I24" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J24" s="167" t="s">
+      <c r="J24" s="66" t="s">
         <v>39</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="O24" s="22" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="P24" s="22" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="Q24" s="22" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="R24" s="23" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="W24" s="22" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="X24" s="22" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="Y24" s="22" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="Z24" s="22" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="AA24" s="23" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="229" t="s">
+      <c r="A25" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="156" t="s">
+      <c r="B25" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="76"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="156"/>
-      <c r="G25" s="172" t="s">
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="156"/>
-      <c r="I25" s="156"/>
-      <c r="J25" s="175"/>
-      <c r="K25" s="204" t="s">
-        <v>253</v>
-      </c>
-      <c r="L25" s="68"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="68"/>
-      <c r="P25" s="68"/>
-      <c r="Q25" s="68"/>
-      <c r="R25" s="69"/>
-      <c r="S25" s="67" t="s">
-        <v>296</v>
-      </c>
-      <c r="T25" s="68"/>
-      <c r="U25" s="68"/>
-      <c r="V25" s="68"/>
-      <c r="W25" s="68"/>
-      <c r="X25" s="68"/>
-      <c r="Y25" s="68"/>
-      <c r="Z25" s="68"/>
-      <c r="AA25" s="69"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="109"/>
+      <c r="K25" s="141" t="s">
+        <v>238</v>
+      </c>
+      <c r="L25" s="141"/>
+      <c r="M25" s="141"/>
+      <c r="N25" s="141"/>
+      <c r="O25" s="141"/>
+      <c r="P25" s="141"/>
+      <c r="Q25" s="141"/>
+      <c r="R25" s="142"/>
+      <c r="S25" s="168" t="s">
+        <v>277</v>
+      </c>
+      <c r="T25" s="141"/>
+      <c r="U25" s="141"/>
+      <c r="V25" s="141"/>
+      <c r="W25" s="141"/>
+      <c r="X25" s="141"/>
+      <c r="Y25" s="141"/>
+      <c r="Z25" s="141"/>
+      <c r="AA25" s="142"/>
     </row>
     <row r="26" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="231" t="s">
+      <c r="A26" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="156" t="s">
+      <c r="B26" s="105" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="156"/>
-      <c r="G26" s="172" t="s">
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="H26" s="156"/>
-      <c r="I26" s="156"/>
-      <c r="J26" s="175"/>
-      <c r="K26" s="204" t="s">
-        <v>286</v>
-      </c>
-      <c r="L26" s="68"/>
-      <c r="M26" s="68"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="68"/>
-      <c r="P26" s="68"/>
-      <c r="Q26" s="68"/>
-      <c r="R26" s="69"/>
-      <c r="S26" s="67" t="s">
-        <v>324</v>
-      </c>
-      <c r="T26" s="68"/>
-      <c r="U26" s="68"/>
-      <c r="V26" s="68"/>
-      <c r="W26" s="68"/>
-      <c r="X26" s="68"/>
-      <c r="Y26" s="68"/>
-      <c r="Z26" s="68"/>
-      <c r="AA26" s="69"/>
+      <c r="H26" s="105"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="109"/>
+      <c r="K26" s="141" t="s">
+        <v>267</v>
+      </c>
+      <c r="L26" s="141"/>
+      <c r="M26" s="141"/>
+      <c r="N26" s="141"/>
+      <c r="O26" s="141"/>
+      <c r="P26" s="141"/>
+      <c r="Q26" s="141"/>
+      <c r="R26" s="142"/>
+      <c r="S26" s="168" t="s">
+        <v>298</v>
+      </c>
+      <c r="T26" s="141"/>
+      <c r="U26" s="141"/>
+      <c r="V26" s="141"/>
+      <c r="W26" s="141"/>
+      <c r="X26" s="141"/>
+      <c r="Y26" s="141"/>
+      <c r="Z26" s="141"/>
+      <c r="AA26" s="142"/>
     </row>
     <row r="27" spans="1:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="232" t="s">
+      <c r="A27" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="156" t="s">
+      <c r="B27" s="105" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="76"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="156"/>
-      <c r="G27" s="182" t="s">
+      <c r="C27" s="105"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="110" t="s">
         <v>50</v>
       </c>
-      <c r="H27" s="183"/>
-      <c r="I27" s="183"/>
-      <c r="J27" s="184"/>
-      <c r="K27" s="204" t="s">
-        <v>287</v>
-      </c>
-      <c r="L27" s="68"/>
-      <c r="M27" s="68"/>
-      <c r="N27" s="68"/>
-      <c r="O27" s="68"/>
-      <c r="P27" s="68"/>
-      <c r="Q27" s="68"/>
-      <c r="R27" s="69"/>
-      <c r="S27" s="67" t="s">
-        <v>325</v>
-      </c>
-      <c r="T27" s="68"/>
-      <c r="U27" s="68"/>
-      <c r="V27" s="68"/>
-      <c r="W27" s="68"/>
-      <c r="X27" s="68"/>
-      <c r="Y27" s="68"/>
-      <c r="Z27" s="68"/>
-      <c r="AA27" s="69"/>
+      <c r="H27" s="111"/>
+      <c r="I27" s="111"/>
+      <c r="J27" s="112"/>
+      <c r="K27" s="141" t="s">
+        <v>268</v>
+      </c>
+      <c r="L27" s="141"/>
+      <c r="M27" s="141"/>
+      <c r="N27" s="141"/>
+      <c r="O27" s="141"/>
+      <c r="P27" s="141"/>
+      <c r="Q27" s="141"/>
+      <c r="R27" s="142"/>
+      <c r="S27" s="168" t="s">
+        <v>299</v>
+      </c>
+      <c r="T27" s="141"/>
+      <c r="U27" s="141"/>
+      <c r="V27" s="141"/>
+      <c r="W27" s="141"/>
+      <c r="X27" s="141"/>
+      <c r="Y27" s="141"/>
+      <c r="Z27" s="141"/>
+      <c r="AA27" s="142"/>
     </row>
     <row r="28" spans="1:27" s="18" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="230" t="s">
-        <v>288</v>
+      <c r="A28" s="94" t="s">
+        <v>269</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
-      <c r="G28" s="240"/>
-      <c r="H28" s="241"/>
-      <c r="I28" s="241"/>
-      <c r="J28" s="242"/>
+      <c r="G28" s="99"/>
+      <c r="H28" s="100"/>
+      <c r="I28" s="100"/>
+      <c r="J28" s="101"/>
       <c r="O28" s="24"/>
       <c r="P28" s="24"/>
       <c r="Q28" s="24"/>
@@ -4538,7 +4554,123 @@
     </row>
     <row r="29" spans="1:27" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="138">
+  <mergeCells count="140">
+    <mergeCell ref="K8:R8"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="S21:AA21"/>
+    <mergeCell ref="S25:AA25"/>
+    <mergeCell ref="S26:AA26"/>
+    <mergeCell ref="S27:AA27"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="S10:X10"/>
+    <mergeCell ref="Y10:Z10"/>
+    <mergeCell ref="S9:AA9"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="Y15:Z15"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="S18:AA18"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="U13:X13"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="S14:V14"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="S8:AA8"/>
+    <mergeCell ref="S6:AA7"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="U11:X11"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="U12:X12"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="S20:AA20"/>
+    <mergeCell ref="S1:AA1"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="S4:AA4"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="W14:Z14"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="K4:R4"/>
+    <mergeCell ref="K6:R7"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B9:F10"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="K18:R18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
     <mergeCell ref="K25:R25"/>
     <mergeCell ref="K26:R26"/>
     <mergeCell ref="K27:R27"/>
@@ -4563,120 +4695,6 @@
     <mergeCell ref="K20:R20"/>
     <mergeCell ref="K21:R21"/>
     <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="K18:R18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="K4:R4"/>
-    <mergeCell ref="K6:R7"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B9:F10"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="S1:AA1"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="S4:AA4"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="W14:Z14"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="S6:AA7"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="U11:X11"/>
-    <mergeCell ref="Y11:AA11"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="U12:X12"/>
-    <mergeCell ref="Y12:AA12"/>
-    <mergeCell ref="S20:AA20"/>
-    <mergeCell ref="S21:AA21"/>
-    <mergeCell ref="S25:AA25"/>
-    <mergeCell ref="S26:AA26"/>
-    <mergeCell ref="S27:AA27"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="S10:X10"/>
-    <mergeCell ref="Y10:Z10"/>
-    <mergeCell ref="S9:AA9"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="Y15:Z15"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="S18:AA18"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="U13:X13"/>
-    <mergeCell ref="Y13:AA13"/>
-    <mergeCell ref="S14:V14"/>
-    <mergeCell ref="S16:T16"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4701,45 +4719,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="191"/>
-      <c r="B1" s="192" t="s">
+      <c r="A1" s="74"/>
+      <c r="B1" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="157" t="s">
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="137" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="158"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="159"/>
-      <c r="J1" s="243" t="s">
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="244"/>
-      <c r="L1" s="244"/>
-      <c r="M1" s="245"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="117"/>
     </row>
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="194" t="s">
+      <c r="A2" s="75" t="s">
         <v>46</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="160"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="61"/>
       <c r="G2" s="21"/>
       <c r="H2" s="21"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="160"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="61"/>
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
-      <c r="M2" s="161"/>
+      <c r="M2" s="62"/>
     </row>
     <row r="3" spans="1:16" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="195" t="s">
+      <c r="A3" s="76" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="14" t="s">
@@ -4751,10 +4769,10 @@
       <c r="D3" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="163" t="s">
+      <c r="E3" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="162" t="s">
+      <c r="F3" s="63" t="s">
         <v>65</v>
       </c>
       <c r="G3" s="15" t="s">
@@ -4763,616 +4781,565 @@
       <c r="H3" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="163" t="s">
+      <c r="I3" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="162" t="s">
+      <c r="J3" s="63" t="s">
         <v>67</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>68</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="M3" s="163" t="s">
-        <v>331</v>
+        <v>271</v>
+      </c>
+      <c r="M3" s="64" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="196" t="s">
+      <c r="A4" s="77" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="165" t="s">
+      <c r="C4" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="165" t="s">
+      <c r="D4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="167" t="s">
+      <c r="E4" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="164" t="s">
+      <c r="F4" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="165" t="s">
+      <c r="G4" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H4" s="165" t="s">
+      <c r="H4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="167" t="s">
+      <c r="I4" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="247" t="s">
+      <c r="J4" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="M4" s="246"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="119"/>
+      <c r="M4" s="120"/>
     </row>
     <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="196" t="s">
+      <c r="A5" s="77" t="s">
         <v>71</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="165" t="s">
+      <c r="C5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="165" t="s">
+      <c r="D5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="167" t="s">
+      <c r="E5" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="164" t="s">
+      <c r="F5" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="165" t="s">
+      <c r="G5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="165" t="s">
+      <c r="H5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="167" t="s">
+      <c r="I5" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="164" t="s">
+      <c r="J5" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="K5" s="165" t="s">
+      <c r="K5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="166" t="s">
-        <v>291</v>
-      </c>
-      <c r="M5" s="167" t="s">
-        <v>332</v>
+      <c r="L5" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="M5" s="66" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="197" t="s">
+      <c r="A6" s="140" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="169" t="s">
+      <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="176" t="s">
+      <c r="D6" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="181"/>
-      <c r="F6" s="168" t="s">
+      <c r="E6" s="108"/>
+      <c r="F6" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="169" t="s">
+      <c r="G6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="176" t="s">
+      <c r="H6" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="181"/>
-      <c r="J6" s="168" t="s">
+      <c r="I6" s="108"/>
+      <c r="J6" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="K6" s="169" t="s">
+      <c r="K6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="170" t="s">
+      <c r="L6" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="M6" s="171"/>
+      <c r="M6" s="121"/>
       <c r="P6" s="56"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="197"/>
-      <c r="B7" s="83" t="s">
+      <c r="A7" s="140"/>
+      <c r="B7" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
-      <c r="E7" s="186"/>
-      <c r="F7" s="185" t="s">
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="186"/>
-      <c r="J7" s="172" t="s">
+      <c r="G7" s="131"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="156"/>
-      <c r="L7" s="173" t="s">
+      <c r="K7" s="105"/>
+      <c r="L7" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="M7" s="174"/>
+      <c r="M7" s="123"/>
     </row>
     <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="196" t="s">
+      <c r="A8" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="156"/>
-      <c r="D8" s="156" t="s">
+      <c r="C8" s="105"/>
+      <c r="D8" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="175"/>
-      <c r="F8" s="185" t="s">
+      <c r="E8" s="109"/>
+      <c r="F8" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="186"/>
-      <c r="J8" s="172" t="s">
+      <c r="G8" s="131"/>
+      <c r="H8" s="131"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="104" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="156"/>
-      <c r="L8" s="156"/>
-      <c r="M8" s="175"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="105"/>
+      <c r="M8" s="109"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="198" t="s">
+      <c r="A9" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="84"/>
-      <c r="D9" s="84" t="s">
+      <c r="C9" s="131"/>
+      <c r="D9" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="186"/>
-      <c r="F9" s="172" t="s">
+      <c r="E9" s="132"/>
+      <c r="F9" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="156"/>
-      <c r="H9" s="156"/>
-      <c r="I9" s="175"/>
-      <c r="J9" s="172" t="s">
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="109"/>
+      <c r="J9" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="156"/>
-      <c r="L9" s="156"/>
-      <c r="M9" s="175"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="109"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84"/>
-      <c r="E10" s="186"/>
-      <c r="F10" s="172"/>
-      <c r="G10" s="156"/>
-      <c r="H10" s="156"/>
-      <c r="I10" s="175"/>
-      <c r="J10" s="172"/>
-      <c r="K10" s="156"/>
-      <c r="L10" s="156"/>
-      <c r="M10" s="175"/>
+      <c r="A10" s="133"/>
+      <c r="B10" s="134"/>
+      <c r="C10" s="131"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="109"/>
+      <c r="J10" s="104"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="109"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="199" t="s">
-        <v>326</v>
+      <c r="A11" s="128" t="s">
+        <v>300</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="170" t="s">
+      <c r="C11" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="170"/>
-      <c r="E11" s="188" t="s">
+      <c r="D11" s="103"/>
+      <c r="E11" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="187" t="s">
+      <c r="F11" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="170" t="s">
+      <c r="G11" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="170"/>
-      <c r="I11" s="188" t="s">
+      <c r="H11" s="103"/>
+      <c r="I11" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="168" t="s">
+      <c r="J11" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="K11" s="176" t="s">
+      <c r="K11" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="L11" s="176"/>
-      <c r="M11" s="177" t="s">
+      <c r="L11" s="107"/>
+      <c r="M11" s="70" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="199"/>
+      <c r="A12" s="128"/>
       <c r="B12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="156" t="s">
+      <c r="C12" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="156"/>
-      <c r="E12" s="167" t="s">
+      <c r="D12" s="105"/>
+      <c r="E12" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="164" t="s">
+      <c r="F12" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="156" t="s">
+      <c r="G12" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="156"/>
-      <c r="I12" s="167" t="s">
+      <c r="H12" s="105"/>
+      <c r="I12" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="J12" s="164" t="s">
+      <c r="J12" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="K12" s="156" t="s">
+      <c r="K12" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="L12" s="156"/>
-      <c r="M12" s="178" t="s">
+      <c r="L12" s="105"/>
+      <c r="M12" s="69" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="200" t="s">
+      <c r="A13" s="78" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="156" t="s">
+      <c r="C13" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="156"/>
-      <c r="E13" s="167" t="s">
+      <c r="D13" s="105"/>
+      <c r="E13" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="164" t="s">
+      <c r="F13" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="156" t="s">
+      <c r="G13" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="H13" s="156"/>
-      <c r="I13" s="167" t="s">
+      <c r="H13" s="105"/>
+      <c r="I13" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="164" t="s">
+      <c r="J13" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="K13" s="156" t="s">
+      <c r="K13" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="156"/>
-      <c r="M13" s="178" t="s">
+      <c r="L13" s="105"/>
+      <c r="M13" s="69" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="201" t="s">
+      <c r="A14" s="124" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="80" t="s">
+      <c r="B14" s="129" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="176"/>
-      <c r="D14" s="176" t="s">
+      <c r="C14" s="107"/>
+      <c r="D14" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="181"/>
-      <c r="F14" s="180" t="s">
+      <c r="E14" s="108"/>
+      <c r="F14" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="176"/>
-      <c r="H14" s="176" t="s">
+      <c r="G14" s="107"/>
+      <c r="H14" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="181"/>
-      <c r="J14" s="168" t="s">
+      <c r="I14" s="108"/>
+      <c r="J14" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="176" t="s">
+      <c r="K14" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="L14" s="176"/>
-      <c r="M14" s="177" t="s">
+      <c r="L14" s="107"/>
+      <c r="M14" s="70" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="201"/>
-      <c r="B15" s="75" t="s">
+      <c r="A15" s="124"/>
+      <c r="B15" s="113" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="156"/>
-      <c r="D15" s="156" t="s">
+      <c r="C15" s="105"/>
+      <c r="D15" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="175"/>
-      <c r="F15" s="172" t="s">
+      <c r="E15" s="109"/>
+      <c r="F15" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="156"/>
-      <c r="H15" s="156" t="s">
+      <c r="G15" s="105"/>
+      <c r="H15" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="I15" s="175"/>
-      <c r="J15" s="164" t="s">
+      <c r="I15" s="109"/>
+      <c r="J15" s="65" t="s">
         <v>131</v>
       </c>
-      <c r="K15" s="156" t="s">
+      <c r="K15" s="105" t="s">
         <v>132</v>
       </c>
-      <c r="L15" s="156"/>
-      <c r="M15" s="178" t="s">
+      <c r="L15" s="105"/>
+      <c r="M15" s="69" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="201" t="s">
+      <c r="A16" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="82" t="s">
+      <c r="B16" s="125" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="190"/>
-      <c r="D16" s="169" t="s">
+      <c r="C16" s="126"/>
+      <c r="D16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="177" t="s">
+      <c r="E16" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="189" t="s">
+      <c r="F16" s="127" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="190"/>
-      <c r="H16" s="169" t="s">
+      <c r="G16" s="126"/>
+      <c r="H16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I16" s="177" t="s">
+      <c r="I16" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="J16" s="179" t="s">
+      <c r="J16" s="102" t="s">
         <v>134</v>
       </c>
-      <c r="K16" s="170"/>
-      <c r="L16" s="169" t="s">
+      <c r="K16" s="103"/>
+      <c r="L16" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="M16" s="177" t="s">
+      <c r="M16" s="70" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="201"/>
-      <c r="B17" s="75" t="s">
+      <c r="A17" s="124"/>
+      <c r="B17" s="113" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="156"/>
-      <c r="D17" s="165" t="s">
+      <c r="C17" s="105"/>
+      <c r="D17" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="167" t="s">
+      <c r="E17" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="F17" s="172" t="s">
+      <c r="F17" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="156"/>
-      <c r="H17" s="165" t="s">
+      <c r="G17" s="105"/>
+      <c r="H17" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="167" t="s">
+      <c r="I17" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="J17" s="172" t="s">
+      <c r="J17" s="104" t="s">
         <v>136</v>
       </c>
-      <c r="K17" s="156"/>
-      <c r="L17" s="165" t="s">
+      <c r="K17" s="105"/>
+      <c r="L17" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="M17" s="178" t="s">
+      <c r="M17" s="69" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="199" t="s">
+      <c r="A18" s="128" t="s">
         <v>84</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="170" t="s">
+      <c r="C18" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="170"/>
-      <c r="E18" s="188" t="s">
+      <c r="D18" s="103"/>
+      <c r="E18" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="187" t="s">
+      <c r="F18" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="G18" s="170" t="s">
+      <c r="G18" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="H18" s="170"/>
-      <c r="I18" s="188" t="s">
+      <c r="H18" s="103"/>
+      <c r="I18" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="180" t="s">
-        <v>327</v>
-      </c>
-      <c r="K18" s="176"/>
-      <c r="L18" s="176"/>
-      <c r="M18" s="181"/>
+      <c r="J18" s="106" t="s">
+        <v>301</v>
+      </c>
+      <c r="K18" s="107"/>
+      <c r="L18" s="107"/>
+      <c r="M18" s="108"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="199"/>
+      <c r="A19" s="128"/>
       <c r="B19" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="156" t="s">
+      <c r="C19" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="156"/>
-      <c r="E19" s="167" t="s">
+      <c r="D19" s="105"/>
+      <c r="E19" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="F19" s="164" t="s">
+      <c r="F19" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="156" t="s">
+      <c r="G19" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="H19" s="156"/>
-      <c r="I19" s="167" t="s">
+      <c r="H19" s="105"/>
+      <c r="I19" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="J19" s="172" t="s">
-        <v>330</v>
-      </c>
-      <c r="K19" s="156"/>
-      <c r="L19" s="165" t="s">
-        <v>329</v>
-      </c>
-      <c r="M19" s="178" t="s">
-        <v>328</v>
+      <c r="J19" s="104" t="s">
+        <v>304</v>
+      </c>
+      <c r="K19" s="105"/>
+      <c r="L19" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="M19" s="69" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="196" t="s">
+      <c r="A20" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="75" t="s">
+      <c r="B20" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="156"/>
-      <c r="D20" s="156"/>
-      <c r="E20" s="175"/>
-      <c r="F20" s="172" t="s">
+      <c r="C20" s="105"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="109"/>
+      <c r="F20" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="156"/>
-      <c r="H20" s="156"/>
-      <c r="I20" s="175"/>
-      <c r="J20" s="172" t="s">
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="109"/>
+      <c r="J20" s="104" t="s">
         <v>139</v>
       </c>
-      <c r="K20" s="156"/>
-      <c r="L20" s="156"/>
-      <c r="M20" s="175"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="105"/>
+      <c r="M20" s="109"/>
     </row>
     <row r="21" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="202" t="s">
+      <c r="A21" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="203" t="s">
+      <c r="B21" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="183"/>
-      <c r="D21" s="183"/>
-      <c r="E21" s="184"/>
-      <c r="F21" s="182" t="s">
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="112"/>
+      <c r="F21" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="183"/>
-      <c r="H21" s="183"/>
-      <c r="I21" s="184"/>
-      <c r="J21" s="182" t="s">
+      <c r="G21" s="111"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="110" t="s">
         <v>34</v>
       </c>
-      <c r="K21" s="183"/>
-      <c r="L21" s="183"/>
-      <c r="M21" s="184"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="112"/>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="J9:M10"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:I8"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:C10"/>
     <mergeCell ref="D9:E10"/>
@@ -5384,6 +5351,57 @@
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:I7"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J9:M10"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:M20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5414,1076 +5432,1074 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="2" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="107" t="s">
+      <c r="B1" s="232" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="109" t="s">
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="234" t="s">
         <v>141</v>
       </c>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="110" t="s">
+      <c r="I1" s="234"/>
+      <c r="J1" s="234"/>
+      <c r="K1" s="234"/>
+      <c r="L1" s="234"/>
+      <c r="M1" s="234"/>
+      <c r="N1" s="224" t="s">
         <v>143</v>
       </c>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="110"/>
-      <c r="R1" s="110"/>
-      <c r="S1" s="110"/>
-      <c r="T1" s="130" t="s">
-        <v>148</v>
-      </c>
-      <c r="U1" s="131"/>
-      <c r="V1" s="131"/>
-      <c r="W1" s="131"/>
-      <c r="X1" s="131"/>
-      <c r="Y1" s="132"/>
+      <c r="O1" s="224"/>
+      <c r="P1" s="224"/>
+      <c r="Q1" s="224"/>
+      <c r="R1" s="224"/>
+      <c r="S1" s="224"/>
+      <c r="T1" s="213" t="s">
+        <v>145</v>
+      </c>
+      <c r="U1" s="214"/>
+      <c r="V1" s="214"/>
+      <c r="W1" s="214"/>
+      <c r="X1" s="214"/>
+      <c r="Y1" s="215"/>
     </row>
     <row r="2" spans="1:26" s="3" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="126"/>
-      <c r="N2" s="111" t="s">
-        <v>220</v>
-      </c>
-      <c r="O2" s="112"/>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="126"/>
-      <c r="T2" s="111"/>
-      <c r="U2" s="112"/>
-      <c r="V2" s="112"/>
-      <c r="W2" s="112"/>
-      <c r="X2" s="112"/>
-      <c r="Y2" s="126"/>
+        <v>144</v>
+      </c>
+      <c r="B2" s="217"/>
+      <c r="C2" s="218"/>
+      <c r="D2" s="218"/>
+      <c r="E2" s="218"/>
+      <c r="F2" s="218"/>
+      <c r="G2" s="219"/>
+      <c r="H2" s="217"/>
+      <c r="I2" s="218"/>
+      <c r="J2" s="218"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="218"/>
+      <c r="M2" s="219"/>
+      <c r="N2" s="217" t="s">
+        <v>208</v>
+      </c>
+      <c r="O2" s="218"/>
+      <c r="P2" s="218"/>
+      <c r="Q2" s="218"/>
+      <c r="R2" s="218"/>
+      <c r="S2" s="219"/>
+      <c r="T2" s="217"/>
+      <c r="U2" s="218"/>
+      <c r="V2" s="218"/>
+      <c r="W2" s="218"/>
+      <c r="X2" s="218"/>
+      <c r="Y2" s="219"/>
     </row>
     <row r="3" spans="1:26" s="16" customFormat="1" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="124" t="s">
-        <v>144</v>
-      </c>
-      <c r="C3" s="125"/>
-      <c r="D3" s="101" t="s">
-        <v>146</v>
-      </c>
-      <c r="E3" s="101"/>
-      <c r="F3" s="101" t="s">
-        <v>145</v>
-      </c>
-      <c r="G3" s="102"/>
-      <c r="H3" s="100" t="s">
+      <c r="B3" s="230" t="s">
+        <v>321</v>
+      </c>
+      <c r="C3" s="231"/>
+      <c r="D3" s="170" t="s">
+        <v>322</v>
+      </c>
+      <c r="E3" s="170"/>
+      <c r="F3" s="170" t="s">
+        <v>326</v>
+      </c>
+      <c r="G3" s="171"/>
+      <c r="H3" s="216" t="s">
+        <v>212</v>
+      </c>
+      <c r="I3" s="170"/>
+      <c r="J3" s="170" t="s">
+        <v>209</v>
+      </c>
+      <c r="K3" s="170"/>
+      <c r="L3" s="170" t="s">
+        <v>210</v>
+      </c>
+      <c r="M3" s="171"/>
+      <c r="N3" s="216" t="s">
+        <v>323</v>
+      </c>
+      <c r="O3" s="170"/>
+      <c r="P3" s="170" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q3" s="170"/>
+      <c r="R3" s="170" t="s">
+        <v>325</v>
+      </c>
+      <c r="S3" s="171"/>
+      <c r="T3" s="220" t="s">
+        <v>166</v>
+      </c>
+      <c r="U3" s="209"/>
+      <c r="V3" s="209" t="s">
+        <v>149</v>
+      </c>
+      <c r="W3" s="209"/>
+      <c r="X3" s="209" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y3" s="210"/>
+    </row>
+    <row r="4" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="212" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="226" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" s="227"/>
+      <c r="D4" s="227"/>
+      <c r="E4" s="227"/>
+      <c r="F4" s="227"/>
+      <c r="G4" s="228"/>
+      <c r="H4" s="172" t="s">
+        <v>215</v>
+      </c>
+      <c r="I4" s="173"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="173"/>
+      <c r="L4" s="173"/>
+      <c r="M4" s="174"/>
+      <c r="N4" s="172" t="s">
+        <v>205</v>
+      </c>
+      <c r="O4" s="176"/>
+      <c r="P4" s="176"/>
+      <c r="Q4" s="176"/>
+      <c r="R4" s="176"/>
+      <c r="S4" s="179"/>
+      <c r="T4" s="205" t="s">
+        <v>14</v>
+      </c>
+      <c r="U4" s="185"/>
+      <c r="V4" s="185"/>
+      <c r="W4" s="185"/>
+      <c r="X4" s="203" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y4" s="186"/>
+    </row>
+    <row r="5" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="212"/>
+      <c r="B5" s="226"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="227"/>
+      <c r="E5" s="227"/>
+      <c r="F5" s="227"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="173"/>
+      <c r="J5" s="173"/>
+      <c r="K5" s="173"/>
+      <c r="L5" s="173"/>
+      <c r="M5" s="174"/>
+      <c r="N5" s="175"/>
+      <c r="O5" s="176"/>
+      <c r="P5" s="176"/>
+      <c r="Q5" s="176"/>
+      <c r="R5" s="176"/>
+      <c r="S5" s="179"/>
+      <c r="T5" s="201" t="s">
+        <v>164</v>
+      </c>
+      <c r="U5" s="185"/>
+      <c r="V5" s="185"/>
+      <c r="W5" s="185"/>
+      <c r="X5" s="185" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y5" s="186"/>
+    </row>
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="212" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" s="172" t="s">
         <v>224</v>
       </c>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101" t="s">
-        <v>221</v>
-      </c>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101" t="s">
-        <v>222</v>
-      </c>
-      <c r="M3" s="102"/>
-      <c r="N3" s="100" t="s">
-        <v>203</v>
-      </c>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q3" s="101"/>
-      <c r="R3" s="101" t="s">
-        <v>201</v>
-      </c>
-      <c r="S3" s="102"/>
-      <c r="T3" s="133" t="s">
-        <v>170</v>
-      </c>
-      <c r="U3" s="134"/>
-      <c r="V3" s="134" t="s">
-        <v>152</v>
-      </c>
-      <c r="W3" s="134"/>
-      <c r="X3" s="134" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y3" s="135"/>
-    </row>
-    <row r="4" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="87" t="s">
-        <v>151</v>
-      </c>
-      <c r="B4" s="119" t="s">
-        <v>238</v>
-      </c>
-      <c r="C4" s="120"/>
-      <c r="D4" s="120"/>
-      <c r="E4" s="120"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="89" t="s">
-        <v>228</v>
-      </c>
-      <c r="I4" s="90"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="91"/>
-      <c r="N4" s="89" t="s">
-        <v>217</v>
-      </c>
-      <c r="O4" s="113"/>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="103" t="s">
-        <v>14</v>
-      </c>
-      <c r="U4" s="105"/>
-      <c r="V4" s="105"/>
-      <c r="W4" s="105"/>
-      <c r="X4" s="94" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y4" s="106"/>
-    </row>
-    <row r="5" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="87"/>
-      <c r="B5" s="119"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="120"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="90"/>
-      <c r="L5" s="90"/>
-      <c r="M5" s="91"/>
-      <c r="N5" s="115"/>
-      <c r="O5" s="113"/>
-      <c r="P5" s="113"/>
-      <c r="Q5" s="113"/>
-      <c r="R5" s="113"/>
-      <c r="S5" s="114"/>
-      <c r="T5" s="99" t="s">
-        <v>167</v>
-      </c>
-      <c r="U5" s="105"/>
-      <c r="V5" s="105"/>
-      <c r="W5" s="105"/>
-      <c r="X5" s="105" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y5" s="106"/>
-    </row>
-    <row r="6" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="87" t="s">
-        <v>216</v>
-      </c>
-      <c r="B6" s="89" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="141" t="s">
-        <v>227</v>
-      </c>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="149" t="s">
-        <v>169</v>
-      </c>
-      <c r="N6" s="115" t="s">
-        <v>212</v>
-      </c>
-      <c r="O6" s="113"/>
-      <c r="P6" s="113"/>
-      <c r="Q6" s="113" t="s">
-        <v>214</v>
-      </c>
-      <c r="R6" s="113"/>
-      <c r="S6" s="114"/>
-      <c r="T6" s="141" t="s">
-        <v>185</v>
-      </c>
-      <c r="U6" s="122"/>
-      <c r="V6" s="122"/>
-      <c r="W6" s="122"/>
-      <c r="X6" s="122"/>
-      <c r="Y6" s="149" t="s">
-        <v>169</v>
-      </c>
+      <c r="C6" s="173"/>
+      <c r="D6" s="173"/>
+      <c r="E6" s="173"/>
+      <c r="F6" s="173"/>
+      <c r="G6" s="174"/>
+      <c r="H6" s="190" t="s">
+        <v>329</v>
+      </c>
+      <c r="I6" s="239"/>
+      <c r="J6" s="239"/>
+      <c r="K6" s="239"/>
+      <c r="L6" s="239"/>
+      <c r="M6" s="229"/>
+      <c r="N6" s="172" t="s">
+        <v>328</v>
+      </c>
+      <c r="O6" s="241"/>
+      <c r="P6" s="241"/>
+      <c r="Q6" s="241"/>
+      <c r="R6" s="241"/>
+      <c r="S6" s="174"/>
+      <c r="T6" s="190" t="s">
+        <v>329</v>
+      </c>
+      <c r="U6" s="239"/>
+      <c r="V6" s="239"/>
+      <c r="W6" s="239"/>
+      <c r="X6" s="239"/>
+      <c r="Y6" s="229"/>
       <c r="Z6" s="41"/>
     </row>
-    <row r="7" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="87"/>
-      <c r="B7" s="89"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="90"/>
-      <c r="F7" s="90"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="141"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="122"/>
-      <c r="K7" s="122"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="149"/>
-      <c r="N7" s="89" t="s">
-        <v>213</v>
-      </c>
-      <c r="O7" s="90"/>
-      <c r="P7" s="90"/>
-      <c r="Q7" s="90" t="s">
-        <v>215</v>
-      </c>
-      <c r="R7" s="90"/>
-      <c r="S7" s="91"/>
-      <c r="T7" s="141"/>
-      <c r="U7" s="122"/>
-      <c r="V7" s="122"/>
-      <c r="W7" s="122"/>
-      <c r="X7" s="122"/>
-      <c r="Y7" s="149"/>
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="212"/>
+      <c r="B7" s="172"/>
+      <c r="C7" s="173"/>
+      <c r="D7" s="173"/>
+      <c r="E7" s="173"/>
+      <c r="F7" s="173"/>
+      <c r="G7" s="174"/>
+      <c r="H7" s="190"/>
+      <c r="I7" s="239"/>
+      <c r="J7" s="239"/>
+      <c r="K7" s="239"/>
+      <c r="L7" s="239"/>
+      <c r="M7" s="229"/>
+      <c r="N7" s="172"/>
+      <c r="O7" s="241"/>
+      <c r="P7" s="241"/>
+      <c r="Q7" s="241"/>
+      <c r="R7" s="241"/>
+      <c r="S7" s="174"/>
+      <c r="T7" s="190"/>
+      <c r="U7" s="239"/>
+      <c r="V7" s="239"/>
+      <c r="W7" s="239"/>
+      <c r="X7" s="239"/>
+      <c r="Y7" s="229"/>
     </row>
     <row r="8" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B8" s="89" t="s">
-        <v>240</v>
-      </c>
-      <c r="C8" s="90"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="89" t="s">
-        <v>184</v>
-      </c>
-      <c r="I8" s="90"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="90"/>
-      <c r="L8" s="90"/>
-      <c r="M8" s="91"/>
-      <c r="N8" s="89" t="s">
-        <v>223</v>
-      </c>
-      <c r="O8" s="90"/>
-      <c r="P8" s="90"/>
-      <c r="Q8" s="90"/>
-      <c r="R8" s="90"/>
-      <c r="S8" s="91"/>
-      <c r="T8" s="104" t="s">
-        <v>184</v>
-      </c>
-      <c r="U8" s="105"/>
-      <c r="V8" s="105"/>
-      <c r="W8" s="105"/>
-      <c r="X8" s="105"/>
-      <c r="Y8" s="106"/>
+        <v>179</v>
+      </c>
+      <c r="B8" s="172" t="s">
+        <v>225</v>
+      </c>
+      <c r="C8" s="173"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="173"/>
+      <c r="F8" s="173"/>
+      <c r="G8" s="174"/>
+      <c r="H8" s="172" t="s">
+        <v>180</v>
+      </c>
+      <c r="I8" s="173"/>
+      <c r="J8" s="173"/>
+      <c r="K8" s="173"/>
+      <c r="L8" s="173"/>
+      <c r="M8" s="174"/>
+      <c r="N8" s="172" t="s">
+        <v>211</v>
+      </c>
+      <c r="O8" s="173"/>
+      <c r="P8" s="173"/>
+      <c r="Q8" s="173"/>
+      <c r="R8" s="173"/>
+      <c r="S8" s="174"/>
+      <c r="T8" s="184" t="s">
+        <v>180</v>
+      </c>
+      <c r="U8" s="185"/>
+      <c r="V8" s="185"/>
+      <c r="W8" s="185"/>
+      <c r="X8" s="185"/>
+      <c r="Y8" s="186"/>
     </row>
     <row r="9" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="173" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="173"/>
+      <c r="D9" s="173"/>
+      <c r="E9" s="173"/>
+      <c r="F9" s="173"/>
+      <c r="G9" s="174"/>
+      <c r="H9" s="172" t="s">
+        <v>152</v>
+      </c>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173" t="s">
         <v>154</v>
       </c>
-      <c r="B9" s="90" t="s">
-        <v>240</v>
-      </c>
-      <c r="C9" s="90"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="91"/>
-      <c r="H9" s="89" t="s">
-        <v>155</v>
-      </c>
-      <c r="I9" s="90"/>
-      <c r="J9" s="90" t="s">
-        <v>157</v>
-      </c>
-      <c r="K9" s="90"/>
-      <c r="L9" s="90" t="s">
-        <v>156</v>
-      </c>
-      <c r="M9" s="91"/>
-      <c r="N9" s="89" t="s">
-        <v>188</v>
-      </c>
-      <c r="O9" s="90"/>
-      <c r="P9" s="90" t="s">
+      <c r="K9" s="173"/>
+      <c r="L9" s="173" t="s">
+        <v>153</v>
+      </c>
+      <c r="M9" s="174"/>
+      <c r="N9" s="172" t="s">
+        <v>183</v>
+      </c>
+      <c r="O9" s="173"/>
+      <c r="P9" s="173" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q9" s="173"/>
+      <c r="R9" s="173" t="s">
+        <v>184</v>
+      </c>
+      <c r="S9" s="174"/>
+      <c r="T9" s="184" t="s">
+        <v>152</v>
+      </c>
+      <c r="U9" s="185"/>
+      <c r="V9" s="185" t="s">
+        <v>154</v>
+      </c>
+      <c r="W9" s="185"/>
+      <c r="X9" s="185" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y9" s="186"/>
+    </row>
+    <row r="10" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="183" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="191" t="s">
+        <v>225</v>
+      </c>
+      <c r="C10" s="191"/>
+      <c r="D10" s="191"/>
+      <c r="E10" s="191"/>
+      <c r="F10" s="191"/>
+      <c r="G10" s="229"/>
+      <c r="H10" s="172" t="s">
+        <v>332</v>
+      </c>
+      <c r="I10" s="241"/>
+      <c r="J10" s="241"/>
+      <c r="K10" s="241"/>
+      <c r="L10" s="241"/>
+      <c r="M10" s="174" t="s">
+        <v>331</v>
+      </c>
+      <c r="N10" s="175" t="s">
+        <v>196</v>
+      </c>
+      <c r="O10" s="173"/>
+      <c r="P10" s="173"/>
+      <c r="Q10" s="203" t="s">
+        <v>198</v>
+      </c>
+      <c r="R10" s="141"/>
+      <c r="S10" s="142"/>
+      <c r="T10" s="190" t="s">
+        <v>333</v>
+      </c>
+      <c r="U10" s="239"/>
+      <c r="V10" s="239"/>
+      <c r="W10" s="239"/>
+      <c r="X10" s="239"/>
+      <c r="Y10" s="192" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="183"/>
+      <c r="B11" s="191"/>
+      <c r="C11" s="191"/>
+      <c r="D11" s="191"/>
+      <c r="E11" s="191"/>
+      <c r="F11" s="191"/>
+      <c r="G11" s="229"/>
+      <c r="H11" s="172"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
+      <c r="M11" s="174"/>
+      <c r="N11" s="172" t="s">
+        <v>197</v>
+      </c>
+      <c r="O11" s="173"/>
+      <c r="P11" s="173"/>
+      <c r="Q11" s="173" t="s">
+        <v>199</v>
+      </c>
+      <c r="R11" s="173"/>
+      <c r="S11" s="174"/>
+      <c r="T11" s="190"/>
+      <c r="U11" s="239"/>
+      <c r="V11" s="239"/>
+      <c r="W11" s="239"/>
+      <c r="X11" s="239"/>
+      <c r="Y11" s="192"/>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="182" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="188" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" s="189"/>
+      <c r="D12" s="189" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="189"/>
+      <c r="F12" s="189" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="225"/>
+      <c r="H12" s="175" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="176"/>
+      <c r="J12" s="176" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" s="176"/>
+      <c r="L12" s="176" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="179"/>
+      <c r="N12" s="175" t="s">
+        <v>14</v>
+      </c>
+      <c r="O12" s="176"/>
+      <c r="P12" s="176" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q12" s="173"/>
+      <c r="R12" s="176" t="s">
+        <v>15</v>
+      </c>
+      <c r="S12" s="179"/>
+      <c r="T12" s="205" t="s">
+        <v>14</v>
+      </c>
+      <c r="U12" s="203"/>
+      <c r="V12" s="203" t="s">
+        <v>55</v>
+      </c>
+      <c r="W12" s="203"/>
+      <c r="X12" s="203" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y12" s="204"/>
+    </row>
+    <row r="13" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="182"/>
+      <c r="B13" s="172" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" s="173"/>
+      <c r="D13" s="173" t="s">
+        <v>217</v>
+      </c>
+      <c r="E13" s="173"/>
+      <c r="F13" s="173" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="174"/>
+      <c r="H13" s="172" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="173"/>
+      <c r="J13" s="173" t="s">
+        <v>92</v>
+      </c>
+      <c r="K13" s="173"/>
+      <c r="L13" s="173" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="174"/>
+      <c r="N13" s="172" t="s">
         <v>187</v>
       </c>
-      <c r="Q9" s="90"/>
-      <c r="R9" s="90" t="s">
-        <v>189</v>
-      </c>
-      <c r="S9" s="91"/>
-      <c r="T9" s="104" t="s">
-        <v>155</v>
-      </c>
-      <c r="U9" s="105"/>
-      <c r="V9" s="105" t="s">
-        <v>157</v>
-      </c>
-      <c r="W9" s="105"/>
-      <c r="X9" s="105" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y9" s="106"/>
-    </row>
-    <row r="10" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="150" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="122" t="s">
-        <v>240</v>
-      </c>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="122"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="123"/>
-      <c r="H10" s="89" t="s">
+      <c r="O13" s="173"/>
+      <c r="P13" s="173" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q13" s="173"/>
+      <c r="R13" s="173" t="s">
+        <v>56</v>
+      </c>
+      <c r="S13" s="174"/>
+      <c r="T13" s="201" t="s">
+        <v>60</v>
+      </c>
+      <c r="U13" s="185"/>
+      <c r="V13" s="185" t="s">
+        <v>92</v>
+      </c>
+      <c r="W13" s="185"/>
+      <c r="X13" s="185" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y13" s="186"/>
+    </row>
+    <row r="14" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="182" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" s="172" t="s">
+        <v>225</v>
+      </c>
+      <c r="C14" s="173"/>
+      <c r="D14" s="173"/>
+      <c r="E14" s="173"/>
+      <c r="F14" s="173"/>
+      <c r="G14" s="174"/>
+      <c r="H14" s="172" t="s">
         <v>140</v>
       </c>
-      <c r="I10" s="90"/>
-      <c r="J10" s="90"/>
-      <c r="K10" s="90"/>
-      <c r="L10" s="90"/>
-      <c r="M10" s="91"/>
-      <c r="N10" s="115" t="s">
-        <v>204</v>
-      </c>
-      <c r="O10" s="90"/>
-      <c r="P10" s="90"/>
-      <c r="Q10" s="94" t="s">
-        <v>206</v>
-      </c>
-      <c r="R10" s="68"/>
-      <c r="S10" s="69"/>
-      <c r="T10" s="141" t="s">
+      <c r="I14" s="173"/>
+      <c r="J14" s="173"/>
+      <c r="K14" s="173"/>
+      <c r="L14" s="173"/>
+      <c r="M14" s="174"/>
+      <c r="N14" s="175" t="s">
+        <v>14</v>
+      </c>
+      <c r="O14" s="173"/>
+      <c r="P14" s="176" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q14" s="173"/>
+      <c r="R14" s="176" t="s">
+        <v>15</v>
+      </c>
+      <c r="S14" s="174"/>
+      <c r="T14" s="196" t="s">
         <v>140</v>
       </c>
-      <c r="U10" s="122"/>
-      <c r="V10" s="122"/>
-      <c r="W10" s="122"/>
-      <c r="X10" s="122"/>
-      <c r="Y10" s="142"/>
-    </row>
-    <row r="11" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="150"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="89"/>
-      <c r="I11" s="90"/>
-      <c r="J11" s="90"/>
-      <c r="K11" s="90"/>
-      <c r="L11" s="90"/>
-      <c r="M11" s="91"/>
-      <c r="N11" s="89" t="s">
-        <v>205</v>
-      </c>
-      <c r="O11" s="90"/>
-      <c r="P11" s="90"/>
-      <c r="Q11" s="90" t="s">
-        <v>207</v>
-      </c>
-      <c r="R11" s="90"/>
-      <c r="S11" s="91"/>
-      <c r="T11" s="141"/>
-      <c r="U11" s="122"/>
-      <c r="V11" s="122"/>
-      <c r="W11" s="122"/>
-      <c r="X11" s="122"/>
-      <c r="Y11" s="142"/>
-    </row>
-    <row r="12" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="86" t="s">
-        <v>149</v>
-      </c>
-      <c r="B12" s="118" t="s">
-        <v>233</v>
-      </c>
-      <c r="C12" s="116"/>
-      <c r="D12" s="116" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="116"/>
-      <c r="F12" s="116" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="117"/>
-      <c r="H12" s="115" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="113"/>
-      <c r="J12" s="113" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="113"/>
-      <c r="L12" s="113" t="s">
-        <v>15</v>
-      </c>
-      <c r="M12" s="114"/>
-      <c r="N12" s="115" t="s">
-        <v>14</v>
-      </c>
-      <c r="O12" s="113"/>
-      <c r="P12" s="113" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q12" s="90"/>
-      <c r="R12" s="113" t="s">
-        <v>15</v>
-      </c>
-      <c r="S12" s="114"/>
-      <c r="T12" s="103" t="s">
-        <v>14</v>
-      </c>
-      <c r="U12" s="94"/>
-      <c r="V12" s="94" t="s">
-        <v>55</v>
-      </c>
-      <c r="W12" s="94"/>
-      <c r="X12" s="94" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y12" s="95"/>
-    </row>
-    <row r="13" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="86"/>
-      <c r="B13" s="89" t="s">
-        <v>231</v>
-      </c>
-      <c r="C13" s="90"/>
-      <c r="D13" s="90" t="s">
-        <v>232</v>
-      </c>
-      <c r="E13" s="90"/>
-      <c r="F13" s="90" t="s">
+      <c r="U14" s="197"/>
+      <c r="V14" s="197"/>
+      <c r="W14" s="197"/>
+      <c r="X14" s="197"/>
+      <c r="Y14" s="198"/>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="182"/>
+      <c r="B15" s="172"/>
+      <c r="C15" s="173"/>
+      <c r="D15" s="173"/>
+      <c r="E15" s="173"/>
+      <c r="F15" s="173"/>
+      <c r="G15" s="174"/>
+      <c r="H15" s="172"/>
+      <c r="I15" s="173"/>
+      <c r="J15" s="173"/>
+      <c r="K15" s="173"/>
+      <c r="L15" s="173"/>
+      <c r="M15" s="174"/>
+      <c r="N15" s="172" t="s">
+        <v>186</v>
+      </c>
+      <c r="O15" s="173"/>
+      <c r="P15" s="173" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q15" s="173"/>
+      <c r="R15" s="173" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="91"/>
-      <c r="H13" s="89" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13" s="90"/>
-      <c r="J13" s="90" t="s">
-        <v>92</v>
-      </c>
-      <c r="K13" s="90"/>
-      <c r="L13" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="M13" s="91"/>
-      <c r="N13" s="89" t="s">
-        <v>192</v>
-      </c>
-      <c r="O13" s="90"/>
-      <c r="P13" s="90" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q13" s="90"/>
-      <c r="R13" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="S13" s="91"/>
-      <c r="T13" s="99" t="s">
-        <v>60</v>
-      </c>
-      <c r="U13" s="105"/>
-      <c r="V13" s="105" t="s">
-        <v>92</v>
-      </c>
-      <c r="W13" s="105"/>
-      <c r="X13" s="105" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y13" s="106"/>
-    </row>
-    <row r="14" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="86" t="s">
-        <v>190</v>
-      </c>
-      <c r="B14" s="89" t="s">
-        <v>240</v>
-      </c>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="89" t="s">
-        <v>140</v>
-      </c>
-      <c r="I14" s="90"/>
-      <c r="J14" s="90"/>
-      <c r="K14" s="90"/>
-      <c r="L14" s="90"/>
-      <c r="M14" s="91"/>
-      <c r="N14" s="115" t="s">
-        <v>14</v>
-      </c>
-      <c r="O14" s="90"/>
-      <c r="P14" s="113" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q14" s="90"/>
-      <c r="R14" s="113" t="s">
-        <v>15</v>
-      </c>
-      <c r="S14" s="91"/>
-      <c r="T14" s="146" t="s">
-        <v>140</v>
-      </c>
-      <c r="U14" s="147"/>
-      <c r="V14" s="147"/>
-      <c r="W14" s="147"/>
-      <c r="X14" s="147"/>
-      <c r="Y14" s="148"/>
-    </row>
-    <row r="15" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="86"/>
-      <c r="B15" s="89"/>
-      <c r="C15" s="90"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="90"/>
-      <c r="K15" s="90"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="91"/>
-      <c r="N15" s="89" t="s">
-        <v>191</v>
-      </c>
-      <c r="O15" s="90"/>
-      <c r="P15" s="90" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q15" s="90"/>
-      <c r="R15" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="S15" s="91"/>
-      <c r="T15" s="146"/>
-      <c r="U15" s="147"/>
-      <c r="V15" s="147"/>
-      <c r="W15" s="147"/>
-      <c r="X15" s="147"/>
-      <c r="Y15" s="148"/>
+      <c r="S15" s="174"/>
+      <c r="T15" s="196"/>
+      <c r="U15" s="197"/>
+      <c r="V15" s="197"/>
+      <c r="W15" s="197"/>
+      <c r="X15" s="197"/>
+      <c r="Y15" s="198"/>
     </row>
     <row r="16" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="85" t="s">
+      <c r="A16" s="237" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="103" t="s">
-        <v>172</v>
-      </c>
-      <c r="C16" s="94"/>
-      <c r="D16" s="94"/>
-      <c r="E16" s="94" t="s">
-        <v>174</v>
-      </c>
-      <c r="F16" s="136"/>
-      <c r="G16" s="137"/>
-      <c r="H16" s="115" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="113"/>
-      <c r="J16" s="113" t="s">
-        <v>15</v>
-      </c>
-      <c r="K16" s="113"/>
-      <c r="L16" s="113"/>
-      <c r="M16" s="114"/>
-      <c r="N16" s="115" t="s">
-        <v>208</v>
-      </c>
-      <c r="O16" s="113"/>
-      <c r="P16" s="113"/>
-      <c r="Q16" s="113" t="s">
-        <v>210</v>
-      </c>
-      <c r="R16" s="113"/>
-      <c r="S16" s="114"/>
-      <c r="T16" s="103" t="s">
-        <v>172</v>
-      </c>
-      <c r="U16" s="94"/>
-      <c r="V16" s="94"/>
-      <c r="W16" s="94" t="s">
-        <v>174</v>
-      </c>
-      <c r="X16" s="136"/>
-      <c r="Y16" s="137"/>
+      <c r="B16" s="205" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="203"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="203" t="s">
+        <v>170</v>
+      </c>
+      <c r="F16" s="206"/>
+      <c r="G16" s="207"/>
+      <c r="H16" s="175" t="s">
+        <v>334</v>
+      </c>
+      <c r="I16" s="240"/>
+      <c r="J16" s="240"/>
+      <c r="K16" s="176" t="s">
+        <v>336</v>
+      </c>
+      <c r="L16" s="176"/>
+      <c r="M16" s="179"/>
+      <c r="N16" s="175" t="s">
+        <v>200</v>
+      </c>
+      <c r="O16" s="176"/>
+      <c r="P16" s="176"/>
+      <c r="Q16" s="176" t="s">
+        <v>202</v>
+      </c>
+      <c r="R16" s="176"/>
+      <c r="S16" s="179"/>
+      <c r="T16" s="205" t="s">
+        <v>168</v>
+      </c>
+      <c r="U16" s="203"/>
+      <c r="V16" s="203"/>
+      <c r="W16" s="203" t="s">
+        <v>335</v>
+      </c>
+      <c r="X16" s="206"/>
+      <c r="Y16" s="207"/>
     </row>
     <row r="17" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="85"/>
-      <c r="B17" s="104" t="s">
-        <v>241</v>
-      </c>
-      <c r="C17" s="105"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="105" t="s">
-        <v>175</v>
-      </c>
-      <c r="F17" s="105"/>
-      <c r="G17" s="106"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="90"/>
-      <c r="J17" s="90"/>
-      <c r="K17" s="90"/>
-      <c r="L17" s="90"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="89" t="s">
-        <v>209</v>
-      </c>
-      <c r="O17" s="90"/>
-      <c r="P17" s="90"/>
-      <c r="Q17" s="90" t="s">
-        <v>211</v>
-      </c>
-      <c r="R17" s="90"/>
-      <c r="S17" s="91"/>
-      <c r="T17" s="104" t="s">
-        <v>173</v>
-      </c>
-      <c r="U17" s="105"/>
-      <c r="V17" s="105"/>
-      <c r="W17" s="105" t="s">
-        <v>175</v>
-      </c>
-      <c r="X17" s="105"/>
-      <c r="Y17" s="106"/>
+      <c r="A17" s="237"/>
+      <c r="B17" s="184" t="s">
+        <v>226</v>
+      </c>
+      <c r="C17" s="185"/>
+      <c r="D17" s="185"/>
+      <c r="E17" s="185" t="s">
+        <v>171</v>
+      </c>
+      <c r="F17" s="185"/>
+      <c r="G17" s="186"/>
+      <c r="H17" s="172" t="s">
+        <v>169</v>
+      </c>
+      <c r="I17" s="241"/>
+      <c r="J17" s="241"/>
+      <c r="K17" s="173" t="s">
+        <v>171</v>
+      </c>
+      <c r="L17" s="173"/>
+      <c r="M17" s="174"/>
+      <c r="N17" s="172" t="s">
+        <v>201</v>
+      </c>
+      <c r="O17" s="173"/>
+      <c r="P17" s="173"/>
+      <c r="Q17" s="173" t="s">
+        <v>203</v>
+      </c>
+      <c r="R17" s="173"/>
+      <c r="S17" s="174"/>
+      <c r="T17" s="184" t="s">
+        <v>169</v>
+      </c>
+      <c r="U17" s="185"/>
+      <c r="V17" s="185"/>
+      <c r="W17" s="185" t="s">
+        <v>171</v>
+      </c>
+      <c r="X17" s="185"/>
+      <c r="Y17" s="186"/>
     </row>
     <row r="18" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="85" t="s">
+      <c r="A18" s="237" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="115" t="s">
-        <v>234</v>
-      </c>
-      <c r="C18" s="113"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="113" t="s">
-        <v>235</v>
-      </c>
-      <c r="F18" s="113"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="103" t="s">
-        <v>225</v>
-      </c>
-      <c r="I18" s="94"/>
-      <c r="J18" s="94"/>
-      <c r="K18" s="94"/>
+      <c r="B18" s="175" t="s">
+        <v>219</v>
+      </c>
+      <c r="C18" s="176"/>
+      <c r="D18" s="176"/>
+      <c r="E18" s="176" t="s">
+        <v>220</v>
+      </c>
+      <c r="F18" s="176"/>
+      <c r="G18" s="179"/>
+      <c r="H18" s="205" t="s">
+        <v>213</v>
+      </c>
+      <c r="I18" s="203"/>
+      <c r="J18" s="203"/>
+      <c r="K18" s="203"/>
       <c r="L18" s="37" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="M18" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="N18" s="118" t="s">
-        <v>202</v>
-      </c>
-      <c r="O18" s="116"/>
-      <c r="P18" s="116"/>
-      <c r="Q18" s="116"/>
+      <c r="N18" s="188" t="s">
+        <v>195</v>
+      </c>
+      <c r="O18" s="189"/>
+      <c r="P18" s="189"/>
+      <c r="Q18" s="189"/>
       <c r="R18" s="34" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="S18" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="T18" s="103" t="s">
-        <v>164</v>
-      </c>
-      <c r="U18" s="94"/>
-      <c r="V18" s="94"/>
-      <c r="W18" s="94"/>
+      <c r="T18" s="205" t="s">
+        <v>161</v>
+      </c>
+      <c r="U18" s="203"/>
+      <c r="V18" s="203"/>
+      <c r="W18" s="203"/>
       <c r="X18" s="37" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Y18" s="38" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="85"/>
-      <c r="B19" s="89" t="s">
-        <v>236</v>
-      </c>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90" t="s">
-        <v>237</v>
-      </c>
-      <c r="F19" s="90"/>
-      <c r="G19" s="91"/>
-      <c r="H19" s="104" t="s">
-        <v>226</v>
-      </c>
-      <c r="I19" s="105"/>
-      <c r="J19" s="105"/>
-      <c r="K19" s="105"/>
+      <c r="A19" s="237"/>
+      <c r="B19" s="172" t="s">
+        <v>221</v>
+      </c>
+      <c r="C19" s="173"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="173" t="s">
+        <v>222</v>
+      </c>
+      <c r="F19" s="173"/>
+      <c r="G19" s="174"/>
+      <c r="H19" s="184" t="s">
+        <v>214</v>
+      </c>
+      <c r="I19" s="185"/>
+      <c r="J19" s="185"/>
+      <c r="K19" s="185"/>
       <c r="L19" s="27" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M19" s="28" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="N19" s="50" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="O19" s="52" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="P19" s="31" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="Q19" s="31"/>
       <c r="R19" s="31" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="S19" s="36" t="s">
-        <v>194</v>
-      </c>
-      <c r="T19" s="104" t="s">
-        <v>186</v>
-      </c>
-      <c r="U19" s="105"/>
-      <c r="V19" s="105"/>
-      <c r="W19" s="105"/>
+        <v>189</v>
+      </c>
+      <c r="T19" s="184" t="s">
+        <v>181</v>
+      </c>
+      <c r="U19" s="185"/>
+      <c r="V19" s="185"/>
+      <c r="W19" s="185"/>
       <c r="X19" s="27" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Y19" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z19" s="41"/>
+    </row>
+    <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="182" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="172" t="s">
+        <v>228</v>
+      </c>
+      <c r="C20" s="173"/>
+      <c r="D20" s="173"/>
+      <c r="E20" s="173"/>
+      <c r="F20" s="173"/>
+      <c r="G20" s="174"/>
+      <c r="H20" s="172" t="s">
+        <v>228</v>
+      </c>
+      <c r="I20" s="173"/>
+      <c r="J20" s="173"/>
+      <c r="K20" s="173"/>
+      <c r="L20" s="173"/>
+      <c r="M20" s="174"/>
+      <c r="N20" s="172" t="s">
+        <v>228</v>
+      </c>
+      <c r="O20" s="176"/>
+      <c r="P20" s="176"/>
+      <c r="Q20" s="176"/>
+      <c r="R20" s="176"/>
+      <c r="S20" s="179"/>
+      <c r="T20" s="190" t="s">
+        <v>228</v>
+      </c>
+      <c r="U20" s="191"/>
+      <c r="V20" s="191"/>
+      <c r="W20" s="191"/>
+      <c r="X20" s="191"/>
+      <c r="Y20" s="192"/>
+      <c r="Z20" s="41"/>
+    </row>
+    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="182"/>
+      <c r="B21" s="172"/>
+      <c r="C21" s="173"/>
+      <c r="D21" s="173"/>
+      <c r="E21" s="173"/>
+      <c r="F21" s="173"/>
+      <c r="G21" s="174"/>
+      <c r="H21" s="172"/>
+      <c r="I21" s="173"/>
+      <c r="J21" s="173"/>
+      <c r="K21" s="173"/>
+      <c r="L21" s="173"/>
+      <c r="M21" s="174"/>
+      <c r="N21" s="175"/>
+      <c r="O21" s="176"/>
+      <c r="P21" s="176"/>
+      <c r="Q21" s="176"/>
+      <c r="R21" s="176"/>
+      <c r="S21" s="179"/>
+      <c r="T21" s="190"/>
+      <c r="U21" s="191"/>
+      <c r="V21" s="191"/>
+      <c r="W21" s="191"/>
+      <c r="X21" s="191"/>
+      <c r="Y21" s="192"/>
+    </row>
+    <row r="22" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="212" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="205" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="203"/>
+      <c r="D22" s="203"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="203" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="236"/>
+      <c r="H22" s="205" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="203"/>
+      <c r="J22" s="203" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" s="203"/>
+      <c r="L22" s="203" t="s">
+        <v>15</v>
+      </c>
+      <c r="M22" s="186"/>
+      <c r="N22" s="175" t="s">
+        <v>14</v>
+      </c>
+      <c r="O22" s="173"/>
+      <c r="P22" s="173"/>
+      <c r="Q22" s="173"/>
+      <c r="R22" s="176" t="s">
+        <v>15</v>
+      </c>
+      <c r="S22" s="174"/>
+      <c r="T22" s="205" t="s">
+        <v>14</v>
+      </c>
+      <c r="U22" s="203"/>
+      <c r="V22" s="203" t="s">
+        <v>55</v>
+      </c>
+      <c r="W22" s="203"/>
+      <c r="X22" s="203" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y22" s="186"/>
+    </row>
+    <row r="23" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="212"/>
+      <c r="B23" s="201" t="s">
+        <v>227</v>
+      </c>
+      <c r="C23" s="202"/>
+      <c r="D23" s="202"/>
+      <c r="E23" s="202"/>
+      <c r="F23" s="202" t="s">
+        <v>157</v>
+      </c>
+      <c r="G23" s="235"/>
+      <c r="H23" s="201" t="s">
+        <v>155</v>
+      </c>
+      <c r="I23" s="202"/>
+      <c r="J23" s="202" t="s">
+        <v>156</v>
+      </c>
+      <c r="K23" s="185"/>
+      <c r="L23" s="202" t="s">
+        <v>157</v>
+      </c>
+      <c r="M23" s="186"/>
+      <c r="N23" s="177" t="s">
+        <v>155</v>
+      </c>
+      <c r="O23" s="173"/>
+      <c r="P23" s="173"/>
+      <c r="Q23" s="173"/>
+      <c r="R23" s="178" t="s">
+        <v>157</v>
+      </c>
+      <c r="S23" s="174"/>
+      <c r="T23" s="201" t="s">
+        <v>155</v>
+      </c>
+      <c r="U23" s="202"/>
+      <c r="V23" s="202" t="s">
+        <v>156</v>
+      </c>
+      <c r="W23" s="185"/>
+      <c r="X23" s="202" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y23" s="186"/>
+    </row>
+    <row r="24" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="212" t="s">
+        <v>229</v>
+      </c>
+      <c r="B24" s="199" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="202"/>
+      <c r="D24" s="202"/>
+      <c r="E24" s="202"/>
+      <c r="F24" s="202"/>
+      <c r="G24" s="235"/>
+      <c r="H24" s="199" t="s">
         <v>161</v>
       </c>
-      <c r="Z19" s="41"/>
-    </row>
-    <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="86" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" s="89" t="s">
-        <v>243</v>
-      </c>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="89" t="s">
-        <v>243</v>
-      </c>
-      <c r="I20" s="90"/>
-      <c r="J20" s="90"/>
-      <c r="K20" s="90"/>
-      <c r="L20" s="90"/>
-      <c r="M20" s="91"/>
-      <c r="N20" s="89" t="s">
-        <v>243</v>
-      </c>
-      <c r="O20" s="113"/>
-      <c r="P20" s="113"/>
-      <c r="Q20" s="113"/>
-      <c r="R20" s="113"/>
-      <c r="S20" s="114"/>
-      <c r="T20" s="141" t="s">
-        <v>243</v>
-      </c>
-      <c r="U20" s="122"/>
-      <c r="V20" s="122"/>
-      <c r="W20" s="122"/>
-      <c r="X20" s="122"/>
-      <c r="Y20" s="142"/>
-      <c r="Z20" s="41"/>
-    </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="86"/>
-      <c r="B21" s="89"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="90"/>
-      <c r="J21" s="90"/>
-      <c r="K21" s="90"/>
-      <c r="L21" s="90"/>
-      <c r="M21" s="91"/>
-      <c r="N21" s="115"/>
-      <c r="O21" s="113"/>
-      <c r="P21" s="113"/>
-      <c r="Q21" s="113"/>
-      <c r="R21" s="113"/>
-      <c r="S21" s="114"/>
-      <c r="T21" s="141"/>
-      <c r="U21" s="122"/>
-      <c r="V21" s="122"/>
-      <c r="W21" s="122"/>
-      <c r="X21" s="122"/>
-      <c r="Y21" s="142"/>
-    </row>
-    <row r="22" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="87" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="103" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="94"/>
-      <c r="D22" s="94"/>
-      <c r="E22" s="94"/>
-      <c r="F22" s="94" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="98"/>
-      <c r="H22" s="103" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="94"/>
-      <c r="J22" s="94" t="s">
-        <v>55</v>
-      </c>
-      <c r="K22" s="94"/>
-      <c r="L22" s="94" t="s">
-        <v>15</v>
-      </c>
-      <c r="M22" s="106"/>
-      <c r="N22" s="115" t="s">
-        <v>14</v>
-      </c>
-      <c r="O22" s="90"/>
-      <c r="P22" s="90"/>
-      <c r="Q22" s="90"/>
-      <c r="R22" s="113" t="s">
-        <v>15</v>
-      </c>
-      <c r="S22" s="91"/>
-      <c r="T22" s="103" t="s">
-        <v>14</v>
-      </c>
-      <c r="U22" s="94"/>
-      <c r="V22" s="94" t="s">
-        <v>55</v>
-      </c>
-      <c r="W22" s="94"/>
-      <c r="X22" s="94" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y22" s="106"/>
-    </row>
-    <row r="23" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="87"/>
-      <c r="B23" s="99" t="s">
-        <v>242</v>
-      </c>
-      <c r="C23" s="96"/>
-      <c r="D23" s="96"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96" t="s">
-        <v>160</v>
-      </c>
-      <c r="G23" s="97"/>
-      <c r="H23" s="99" t="s">
-        <v>158</v>
-      </c>
-      <c r="I23" s="96"/>
-      <c r="J23" s="96" t="s">
-        <v>159</v>
-      </c>
-      <c r="K23" s="105"/>
-      <c r="L23" s="96" t="s">
-        <v>160</v>
-      </c>
-      <c r="M23" s="106"/>
-      <c r="N23" s="152" t="s">
-        <v>158</v>
-      </c>
-      <c r="O23" s="90"/>
-      <c r="P23" s="90"/>
-      <c r="Q23" s="90"/>
-      <c r="R23" s="153" t="s">
-        <v>160</v>
-      </c>
-      <c r="S23" s="91"/>
-      <c r="T23" s="99" t="s">
-        <v>158</v>
-      </c>
-      <c r="U23" s="96"/>
-      <c r="V23" s="96" t="s">
-        <v>159</v>
-      </c>
-      <c r="W23" s="105"/>
-      <c r="X23" s="96" t="s">
-        <v>160</v>
-      </c>
-      <c r="Y23" s="106"/>
-    </row>
-    <row r="24" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="87" t="s">
-        <v>244</v>
-      </c>
-      <c r="B24" s="92" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="97"/>
-      <c r="H24" s="92" t="s">
-        <v>164</v>
-      </c>
-      <c r="I24" s="93"/>
-      <c r="J24" s="93"/>
-      <c r="K24" s="94" t="s">
+      <c r="I24" s="200"/>
+      <c r="J24" s="200"/>
+      <c r="K24" s="203" t="s">
         <v>81</v>
       </c>
-      <c r="L24" s="94"/>
-      <c r="M24" s="98"/>
-      <c r="N24" s="154" t="s">
-        <v>248</v>
-      </c>
-      <c r="O24" s="153"/>
-      <c r="P24" s="153"/>
-      <c r="Q24" s="113" t="s">
+      <c r="L24" s="203"/>
+      <c r="M24" s="236"/>
+      <c r="N24" s="180" t="s">
+        <v>233</v>
+      </c>
+      <c r="O24" s="178"/>
+      <c r="P24" s="178"/>
+      <c r="Q24" s="176" t="s">
         <v>81</v>
       </c>
-      <c r="R24" s="90"/>
-      <c r="S24" s="91"/>
-      <c r="T24" s="92" t="s">
-        <v>164</v>
-      </c>
-      <c r="U24" s="96"/>
-      <c r="V24" s="96"/>
-      <c r="W24" s="94" t="s">
+      <c r="R24" s="173"/>
+      <c r="S24" s="174"/>
+      <c r="T24" s="199" t="s">
+        <v>161</v>
+      </c>
+      <c r="U24" s="202"/>
+      <c r="V24" s="202"/>
+      <c r="W24" s="203" t="s">
         <v>81</v>
       </c>
-      <c r="X24" s="105"/>
-      <c r="Y24" s="106"/>
+      <c r="X24" s="185"/>
+      <c r="Y24" s="186"/>
     </row>
     <row r="25" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="87"/>
-      <c r="B25" s="99" t="s">
-        <v>245</v>
-      </c>
-      <c r="C25" s="96"/>
-      <c r="D25" s="96"/>
-      <c r="E25" s="96"/>
-      <c r="F25" s="96"/>
-      <c r="G25" s="97"/>
-      <c r="H25" s="99" t="s">
-        <v>246</v>
-      </c>
-      <c r="I25" s="96"/>
-      <c r="J25" s="96"/>
-      <c r="K25" s="96" t="s">
-        <v>247</v>
-      </c>
-      <c r="L25" s="96"/>
-      <c r="M25" s="97"/>
-      <c r="N25" s="152" t="s">
-        <v>249</v>
-      </c>
-      <c r="O25" s="153"/>
-      <c r="P25" s="153"/>
-      <c r="Q25" s="153" t="s">
-        <v>250</v>
-      </c>
-      <c r="R25" s="153"/>
-      <c r="S25" s="155"/>
-      <c r="T25" s="99" t="s">
-        <v>246</v>
-      </c>
-      <c r="U25" s="96"/>
-      <c r="V25" s="96"/>
-      <c r="W25" s="96" t="s">
-        <v>247</v>
-      </c>
-      <c r="X25" s="96"/>
-      <c r="Y25" s="139"/>
+      <c r="A25" s="212"/>
+      <c r="B25" s="201" t="s">
+        <v>230</v>
+      </c>
+      <c r="C25" s="202"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="202"/>
+      <c r="G25" s="235"/>
+      <c r="H25" s="201" t="s">
+        <v>231</v>
+      </c>
+      <c r="I25" s="202"/>
+      <c r="J25" s="202"/>
+      <c r="K25" s="202" t="s">
+        <v>232</v>
+      </c>
+      <c r="L25" s="202"/>
+      <c r="M25" s="235"/>
+      <c r="N25" s="177" t="s">
+        <v>234</v>
+      </c>
+      <c r="O25" s="178"/>
+      <c r="P25" s="178"/>
+      <c r="Q25" s="178" t="s">
+        <v>235</v>
+      </c>
+      <c r="R25" s="178"/>
+      <c r="S25" s="181"/>
+      <c r="T25" s="201" t="s">
+        <v>231</v>
+      </c>
+      <c r="U25" s="202"/>
+      <c r="V25" s="202"/>
+      <c r="W25" s="202" t="s">
+        <v>232</v>
+      </c>
+      <c r="X25" s="202"/>
+      <c r="Y25" s="211"/>
     </row>
     <row r="26" spans="1:26" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="89" t="s">
+      <c r="B26" s="172" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="90"/>
-      <c r="H26" s="127" t="s">
+      <c r="C26" s="173"/>
+      <c r="D26" s="173"/>
+      <c r="E26" s="173"/>
+      <c r="F26" s="173"/>
+      <c r="G26" s="173"/>
+      <c r="H26" s="221" t="s">
         <v>34</v>
       </c>
-      <c r="I26" s="128"/>
-      <c r="J26" s="128"/>
-      <c r="K26" s="128"/>
-      <c r="L26" s="128"/>
-      <c r="M26" s="129"/>
-      <c r="N26" s="127" t="s">
+      <c r="I26" s="222"/>
+      <c r="J26" s="222"/>
+      <c r="K26" s="222"/>
+      <c r="L26" s="222"/>
+      <c r="M26" s="223"/>
+      <c r="N26" s="221" t="s">
         <v>140</v>
       </c>
-      <c r="O26" s="128"/>
-      <c r="P26" s="128"/>
-      <c r="Q26" s="128"/>
-      <c r="R26" s="128"/>
-      <c r="S26" s="129"/>
-      <c r="T26" s="143" t="s">
+      <c r="O26" s="222"/>
+      <c r="P26" s="222"/>
+      <c r="Q26" s="222"/>
+      <c r="R26" s="222"/>
+      <c r="S26" s="223"/>
+      <c r="T26" s="193" t="s">
         <v>140</v>
       </c>
-      <c r="U26" s="144"/>
-      <c r="V26" s="144"/>
-      <c r="W26" s="144"/>
-      <c r="X26" s="144"/>
-      <c r="Y26" s="145"/>
+      <c r="U26" s="194"/>
+      <c r="V26" s="194"/>
+      <c r="W26" s="194"/>
+      <c r="X26" s="194"/>
+      <c r="Y26" s="195"/>
     </row>
     <row r="27" spans="1:26" s="18" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="43" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B27" s="44"/>
       <c r="C27" s="45"/>
@@ -6514,14 +6530,14 @@
       <c r="A28" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="100" t="s">
-        <v>240</v>
-      </c>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="102"/>
+      <c r="B28" s="216" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" s="170"/>
+      <c r="D28" s="170"/>
+      <c r="E28" s="170"/>
+      <c r="F28" s="170"/>
+      <c r="G28" s="171"/>
       <c r="H28" s="30" t="s">
         <v>108</v>
       </c>
@@ -6536,170 +6552,170 @@
       <c r="M28" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="N28" s="151" t="s">
-        <v>218</v>
-      </c>
-      <c r="O28" s="101"/>
-      <c r="P28" s="101"/>
-      <c r="Q28" s="101"/>
-      <c r="R28" s="101"/>
-      <c r="S28" s="102"/>
-      <c r="T28" s="138" t="s">
-        <v>150</v>
-      </c>
-      <c r="U28" s="134"/>
-      <c r="V28" s="134"/>
-      <c r="W28" s="134"/>
-      <c r="X28" s="134"/>
-      <c r="Y28" s="135"/>
+      <c r="N28" s="169" t="s">
+        <v>206</v>
+      </c>
+      <c r="O28" s="170"/>
+      <c r="P28" s="170"/>
+      <c r="Q28" s="170"/>
+      <c r="R28" s="170"/>
+      <c r="S28" s="171"/>
+      <c r="T28" s="208" t="s">
+        <v>147</v>
+      </c>
+      <c r="U28" s="209"/>
+      <c r="V28" s="209"/>
+      <c r="W28" s="209"/>
+      <c r="X28" s="209"/>
+      <c r="Y28" s="210"/>
     </row>
     <row r="29" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="87" t="s">
+      <c r="A29" s="212" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29" s="172"/>
+      <c r="C29" s="173"/>
+      <c r="D29" s="173"/>
+      <c r="E29" s="173"/>
+      <c r="F29" s="173"/>
+      <c r="G29" s="174"/>
+      <c r="H29" s="199" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="200"/>
+      <c r="J29" s="200" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" s="203"/>
+      <c r="L29" s="203" t="s">
+        <v>15</v>
+      </c>
+      <c r="M29" s="204"/>
+      <c r="N29" s="172" t="s">
+        <v>207</v>
+      </c>
+      <c r="O29" s="173"/>
+      <c r="P29" s="173"/>
+      <c r="Q29" s="173"/>
+      <c r="R29" s="173"/>
+      <c r="S29" s="174"/>
+      <c r="T29" s="199" t="s">
+        <v>14</v>
+      </c>
+      <c r="U29" s="200"/>
+      <c r="V29" s="200" t="s">
+        <v>177</v>
+      </c>
+      <c r="W29" s="203"/>
+      <c r="X29" s="203" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y29" s="204"/>
+    </row>
+    <row r="30" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="212"/>
+      <c r="B30" s="172"/>
+      <c r="C30" s="173"/>
+      <c r="D30" s="173"/>
+      <c r="E30" s="173"/>
+      <c r="F30" s="173"/>
+      <c r="G30" s="174"/>
+      <c r="H30" s="201" t="s">
+        <v>175</v>
+      </c>
+      <c r="I30" s="202"/>
+      <c r="J30" s="185" t="s">
         <v>178</v>
       </c>
-      <c r="B29" s="89"/>
-      <c r="C29" s="90"/>
-      <c r="D29" s="90"/>
-      <c r="E29" s="90"/>
-      <c r="F29" s="90"/>
-      <c r="G29" s="91"/>
-      <c r="H29" s="92" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93" t="s">
-        <v>181</v>
-      </c>
-      <c r="K29" s="94"/>
-      <c r="L29" s="94" t="s">
-        <v>15</v>
-      </c>
-      <c r="M29" s="95"/>
-      <c r="N29" s="89" t="s">
-        <v>219</v>
-      </c>
-      <c r="O29" s="90"/>
-      <c r="P29" s="90"/>
-      <c r="Q29" s="90"/>
-      <c r="R29" s="90"/>
-      <c r="S29" s="91"/>
-      <c r="T29" s="92" t="s">
-        <v>14</v>
-      </c>
-      <c r="U29" s="93"/>
-      <c r="V29" s="93" t="s">
-        <v>181</v>
-      </c>
-      <c r="W29" s="94"/>
-      <c r="X29" s="94" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y29" s="95"/>
-    </row>
-    <row r="30" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="87"/>
-      <c r="B30" s="89"/>
-      <c r="C30" s="90"/>
-      <c r="D30" s="90"/>
-      <c r="E30" s="90"/>
-      <c r="F30" s="90"/>
-      <c r="G30" s="91"/>
-      <c r="H30" s="99" t="s">
-        <v>179</v>
-      </c>
-      <c r="I30" s="96"/>
-      <c r="J30" s="105" t="s">
-        <v>182</v>
-      </c>
-      <c r="K30" s="105"/>
-      <c r="L30" s="96" t="s">
-        <v>180</v>
-      </c>
-      <c r="M30" s="106"/>
-      <c r="N30" s="89"/>
-      <c r="O30" s="90"/>
-      <c r="P30" s="90"/>
-      <c r="Q30" s="90"/>
-      <c r="R30" s="90"/>
-      <c r="S30" s="91"/>
-      <c r="T30" s="99" t="s">
-        <v>179</v>
-      </c>
-      <c r="U30" s="96"/>
-      <c r="V30" s="105" t="s">
-        <v>182</v>
-      </c>
-      <c r="W30" s="105"/>
-      <c r="X30" s="96" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y30" s="106"/>
+      <c r="K30" s="185"/>
+      <c r="L30" s="202" t="s">
+        <v>176</v>
+      </c>
+      <c r="M30" s="186"/>
+      <c r="N30" s="172"/>
+      <c r="O30" s="173"/>
+      <c r="P30" s="173"/>
+      <c r="Q30" s="173"/>
+      <c r="R30" s="173"/>
+      <c r="S30" s="174"/>
+      <c r="T30" s="201" t="s">
+        <v>175</v>
+      </c>
+      <c r="U30" s="202"/>
+      <c r="V30" s="185" t="s">
+        <v>178</v>
+      </c>
+      <c r="W30" s="185"/>
+      <c r="X30" s="202" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y30" s="186"/>
     </row>
     <row r="31" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B31" s="89"/>
-      <c r="C31" s="90"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="90"/>
-      <c r="F31" s="90"/>
-      <c r="G31" s="91"/>
-      <c r="H31" s="89" t="s">
-        <v>229</v>
-      </c>
-      <c r="I31" s="90"/>
-      <c r="J31" s="90"/>
-      <c r="K31" s="90"/>
-      <c r="L31" s="90" t="s">
-        <v>230</v>
-      </c>
-      <c r="M31" s="91"/>
-      <c r="N31" s="89" t="s">
-        <v>140</v>
-      </c>
-      <c r="O31" s="90"/>
-      <c r="P31" s="90"/>
-      <c r="Q31" s="90"/>
-      <c r="R31" s="90"/>
-      <c r="S31" s="91"/>
-      <c r="T31" s="104" t="s">
-        <v>177</v>
-      </c>
-      <c r="U31" s="105"/>
-      <c r="V31" s="105"/>
-      <c r="W31" s="105"/>
-      <c r="X31" s="105"/>
-      <c r="Y31" s="106"/>
+        <v>172</v>
+      </c>
+      <c r="B31" s="172"/>
+      <c r="C31" s="173"/>
+      <c r="D31" s="173"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="173"/>
+      <c r="G31" s="174"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="51"/>
+      <c r="N31" s="172" t="s">
+        <v>327</v>
+      </c>
+      <c r="O31" s="173"/>
+      <c r="P31" s="173"/>
+      <c r="Q31" s="173"/>
+      <c r="R31" s="173"/>
+      <c r="S31" s="174"/>
+      <c r="T31" s="184" t="s">
+        <v>173</v>
+      </c>
+      <c r="U31" s="185"/>
+      <c r="V31" s="185"/>
+      <c r="W31" s="185"/>
+      <c r="X31" s="185"/>
+      <c r="Y31" s="186"/>
     </row>
     <row r="32" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B32" s="89"/>
-      <c r="C32" s="90"/>
-      <c r="D32" s="90"/>
-      <c r="E32" s="90"/>
-      <c r="F32" s="90"/>
-      <c r="G32" s="91"/>
-      <c r="H32" s="89"/>
-      <c r="I32" s="90"/>
-      <c r="J32" s="90"/>
-      <c r="K32" s="90"/>
-      <c r="L32" s="90"/>
-      <c r="M32" s="91"/>
+      <c r="B32" s="172"/>
+      <c r="C32" s="173"/>
+      <c r="D32" s="173"/>
+      <c r="E32" s="173"/>
+      <c r="F32" s="173"/>
+      <c r="G32" s="174"/>
+      <c r="H32" s="172" t="s">
+        <v>330</v>
+      </c>
+      <c r="I32" s="241"/>
+      <c r="J32" s="241"/>
+      <c r="K32" s="241"/>
+      <c r="L32" s="241"/>
+      <c r="M32" s="174"/>
       <c r="N32" s="50"/>
       <c r="O32" s="52"/>
       <c r="P32" s="52"/>
       <c r="Q32" s="52"/>
       <c r="R32" s="52"/>
       <c r="S32" s="51"/>
-      <c r="T32" s="32"/>
-      <c r="U32" s="32"/>
-      <c r="V32" s="32"/>
-      <c r="W32" s="32"/>
-      <c r="X32" s="32"/>
-      <c r="Y32" s="33"/>
+      <c r="T32" s="172" t="s">
+        <v>330</v>
+      </c>
+      <c r="U32" s="241"/>
+      <c r="V32" s="241"/>
+      <c r="W32" s="241"/>
+      <c r="X32" s="241"/>
+      <c r="Y32" s="174"/>
     </row>
     <row r="33" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="32"/>
@@ -6811,7 +6827,7 @@
     </row>
     <row r="37" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="42" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B37" s="39"/>
       <c r="C37" s="32"/>
@@ -6819,108 +6835,157 @@
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
       <c r="G37" s="32"/>
-      <c r="H37" s="104" t="s">
-        <v>166</v>
-      </c>
-      <c r="I37" s="105"/>
-      <c r="J37" s="105"/>
-      <c r="K37" s="105"/>
-      <c r="L37" s="105"/>
-      <c r="M37" s="106"/>
-      <c r="N37" s="104"/>
-      <c r="O37" s="105"/>
-      <c r="P37" s="105"/>
-      <c r="Q37" s="105"/>
-      <c r="R37" s="105"/>
-      <c r="S37" s="140"/>
-      <c r="T37" s="104" t="s">
-        <v>166</v>
-      </c>
-      <c r="U37" s="105"/>
-      <c r="V37" s="105"/>
-      <c r="W37" s="105"/>
-      <c r="X37" s="105"/>
-      <c r="Y37" s="106"/>
+      <c r="H37" s="184" t="s">
+        <v>163</v>
+      </c>
+      <c r="I37" s="185"/>
+      <c r="J37" s="185"/>
+      <c r="K37" s="185"/>
+      <c r="L37" s="185"/>
+      <c r="M37" s="186"/>
+      <c r="N37" s="184"/>
+      <c r="O37" s="185"/>
+      <c r="P37" s="185"/>
+      <c r="Q37" s="185"/>
+      <c r="R37" s="185"/>
+      <c r="S37" s="187"/>
+      <c r="T37" s="184" t="s">
+        <v>163</v>
+      </c>
+      <c r="U37" s="185"/>
+      <c r="V37" s="185"/>
+      <c r="W37" s="185"/>
+      <c r="X37" s="185"/>
+      <c r="Y37" s="186"/>
     </row>
     <row r="38" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="42" t="s">
-        <v>195</v>
-      </c>
-      <c r="N38" s="104" t="s">
-        <v>196</v>
-      </c>
-      <c r="O38" s="68"/>
-      <c r="P38" s="68"/>
-      <c r="Q38" s="68"/>
-      <c r="R38" s="68"/>
-      <c r="S38" s="69"/>
+        <v>190</v>
+      </c>
+      <c r="N38" s="184" t="s">
+        <v>191</v>
+      </c>
+      <c r="O38" s="141"/>
+      <c r="P38" s="141"/>
+      <c r="Q38" s="141"/>
+      <c r="R38" s="141"/>
+      <c r="S38" s="142"/>
     </row>
   </sheetData>
-  <mergeCells count="205">
-    <mergeCell ref="N28:S28"/>
-    <mergeCell ref="N29:S30"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="N20:S21"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="Q17:S17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B14:G15"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="H14:M15"/>
-    <mergeCell ref="N37:S37"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="N31:S31"/>
-    <mergeCell ref="N38:S38"/>
-    <mergeCell ref="N18:Q18"/>
-    <mergeCell ref="T10:Y11"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="T20:Y21"/>
-    <mergeCell ref="T8:Y8"/>
-    <mergeCell ref="T26:Y26"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="T14:Y15"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="X29:Y29"/>
-    <mergeCell ref="X30:Y30"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="W16:Y16"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="W17:Y17"/>
-    <mergeCell ref="T28:Y28"/>
-    <mergeCell ref="T24:V24"/>
-    <mergeCell ref="W24:Y24"/>
-    <mergeCell ref="T25:V25"/>
-    <mergeCell ref="W25:Y25"/>
+  <mergeCells count="201">
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="H6:M7"/>
+    <mergeCell ref="N6:S7"/>
+    <mergeCell ref="T6:Y7"/>
+    <mergeCell ref="T32:Y32"/>
+    <mergeCell ref="H10:L11"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="T10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="H20:M21"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="B28:G32"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="H4:M5"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B4:G5"/>
+    <mergeCell ref="B6:G7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:G11"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="B20:G21"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="T1:Y1"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="N2:S2"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="N4:S5"/>
     <mergeCell ref="T31:Y31"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="T18:W18"/>
@@ -6945,123 +7010,70 @@
     <mergeCell ref="X12:Y12"/>
     <mergeCell ref="X13:Y13"/>
     <mergeCell ref="A29:A30"/>
-    <mergeCell ref="T1:Y1"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="X5:Y5"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="N2:S2"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="N4:S5"/>
-    <mergeCell ref="T6:X7"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="X29:Y29"/>
+    <mergeCell ref="X30:Y30"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="W16:Y16"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="W17:Y17"/>
+    <mergeCell ref="T28:Y28"/>
+    <mergeCell ref="T24:V24"/>
+    <mergeCell ref="W24:Y24"/>
+    <mergeCell ref="T25:V25"/>
+    <mergeCell ref="W25:Y25"/>
+    <mergeCell ref="N37:S37"/>
+    <mergeCell ref="N8:S8"/>
+    <mergeCell ref="N31:S31"/>
+    <mergeCell ref="N38:S38"/>
+    <mergeCell ref="N18:Q18"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="T20:Y21"/>
+    <mergeCell ref="T8:Y8"/>
+    <mergeCell ref="T26:Y26"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="T14:Y15"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B14:G15"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="H14:M15"/>
+    <mergeCell ref="N28:S28"/>
+    <mergeCell ref="N29:S30"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="N20:S21"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="Q25:S25"/>
     <mergeCell ref="N26:S26"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="H10:M11"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="B20:G21"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="N1:S1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B4:G5"/>
-    <mergeCell ref="B6:G7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B10:G11"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="H6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="H4:M5"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="H20:M21"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="B28:G32"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/ARCHER/Documentation/PCB/Sensor Characteristics.xlsx
+++ b/ARCHER/Documentation/PCB/Sensor Characteristics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\.git\ARCHER\Documentation\PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CE9E1A-3911-4209-9A94-2B6C34F8C867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20D9DC5-A41E-4AAE-9D57-55D922E132A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -238,6 +238,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="N16" authorId="0" shapeId="0" xr:uid="{3BEEC590-492D-4593-980E-B135B2434D16}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Jason Gläser:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Depending on capacitor size
+f_scl 1: 400 pF
+f_scl 2: 20 pF</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H18" authorId="0" shapeId="0" xr:uid="{F2DFCE55-C851-4DC9-A1EA-9560EC74B3BC}">
       <text>
         <r>
@@ -343,7 +369,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="341">
   <si>
     <t>ADXL345</t>
   </si>
@@ -940,9 +966,6 @@
     <t>Resolution</t>
   </si>
   <si>
-    <t>&lt;0.01°C</t>
-  </si>
-  <si>
     <t>Accuracy</t>
   </si>
   <si>
@@ -1033,18 +1056,6 @@
     <t>1.5 Pa RMS</t>
   </si>
   <si>
-    <t>One-shot mode</t>
-  </si>
-  <si>
-    <t>100 Hz</t>
-  </si>
-  <si>
-    <t>FIFO-Mode</t>
-  </si>
-  <si>
-    <t>&gt;1 Hz</t>
-  </si>
-  <si>
     <t>Pressure Resolution</t>
   </si>
   <si>
@@ -1151,9 +1162,6 @@
   </si>
   <si>
     <t>-20°C</t>
-  </si>
-  <si>
-    <t>TBD</t>
   </si>
   <si>
     <r>
@@ -1518,9 +1526,6 @@
     <t>0.02 psi - 14.5 psi</t>
   </si>
   <si>
-    <t>12 bit</t>
-  </si>
-  <si>
     <t>20 bits</t>
   </si>
   <si>
@@ -1558,6 +1563,39 @@
   </si>
   <si>
     <t>I2C (Max)</t>
+  </si>
+  <si>
+    <t>I2C f_SCL 1</t>
+  </si>
+  <si>
+    <t>I2C f_SCL 2</t>
+  </si>
+  <si>
+    <t>4 MHz</t>
+  </si>
+  <si>
+    <t>10.23 mW</t>
+  </si>
+  <si>
+    <t>12.87 mW</t>
+  </si>
+  <si>
+    <t>4.62 mW</t>
+  </si>
+  <si>
+    <t>41.25 uW</t>
+  </si>
+  <si>
+    <t>0.462 uW</t>
+  </si>
+  <si>
+    <t>6.6 mW</t>
+  </si>
+  <si>
+    <t>6.6 uW</t>
+  </si>
+  <si>
+    <t>844,8 uW</t>
   </si>
 </sst>
 </file>
@@ -2214,7 +2252,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2287,9 +2325,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3208,75 +3243,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="2" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="89"/>
-      <c r="B1" s="157" t="s">
+      <c r="A1" s="88"/>
+      <c r="B1" s="156" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="156" t="s">
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="152" t="s">
-        <v>236</v>
-      </c>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="153"/>
-      <c r="S1" s="161" t="s">
-        <v>270</v>
-      </c>
-      <c r="T1" s="162"/>
-      <c r="U1" s="162"/>
-      <c r="V1" s="162"/>
-      <c r="W1" s="162"/>
-      <c r="X1" s="162"/>
-      <c r="Y1" s="162"/>
-      <c r="Z1" s="162"/>
-      <c r="AA1" s="163"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="151" t="s">
+        <v>230</v>
+      </c>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="160" t="s">
+        <v>264</v>
+      </c>
+      <c r="T1" s="161"/>
+      <c r="U1" s="161"/>
+      <c r="V1" s="161"/>
+      <c r="W1" s="161"/>
+      <c r="X1" s="161"/>
+      <c r="Y1" s="161"/>
+      <c r="Z1" s="161"/>
+      <c r="AA1" s="162"/>
     </row>
     <row r="2" spans="1:27" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="86"/>
-      <c r="S2" s="87"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
-      <c r="W2" s="85"/>
-      <c r="X2" s="85"/>
-      <c r="Y2" s="85"/>
-      <c r="Z2" s="85"/>
-      <c r="AA2" s="86"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="87"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="85"/>
+      <c r="S2" s="86"/>
+      <c r="T2" s="87"/>
+      <c r="U2" s="87"/>
+      <c r="V2" s="87"/>
+      <c r="W2" s="84"/>
+      <c r="X2" s="84"/>
+      <c r="Y2" s="84"/>
+      <c r="Z2" s="84"/>
+      <c r="AA2" s="85"/>
     </row>
     <row r="3" spans="1:27" s="16" customFormat="1" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="91" t="s">
+      <c r="A3" s="90" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -3288,11 +3323,11 @@
       <c r="D3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="105" t="s">
+      <c r="E3" s="104" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="105"/>
-      <c r="G3" s="65" t="s">
+      <c r="F3" s="104"/>
+      <c r="G3" s="64" t="s">
         <v>65</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -3301,86 +3336,86 @@
       <c r="I3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J3" s="66" t="s">
+      <c r="J3" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="L3" s="122"/>
-      <c r="M3" s="122" t="s">
+      <c r="L3" s="121"/>
+      <c r="M3" s="121" t="s">
         <v>66</v>
       </c>
-      <c r="N3" s="122"/>
-      <c r="O3" s="122" t="s">
+      <c r="N3" s="121"/>
+      <c r="O3" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="P3" s="122"/>
-      <c r="Q3" s="122" t="s">
+      <c r="P3" s="121"/>
+      <c r="Q3" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="R3" s="143"/>
-      <c r="S3" s="164" t="s">
+      <c r="R3" s="142"/>
+      <c r="S3" s="163" t="s">
         <v>65</v>
       </c>
-      <c r="T3" s="122"/>
-      <c r="U3" s="122" t="s">
+      <c r="T3" s="121"/>
+      <c r="U3" s="121" t="s">
         <v>66</v>
       </c>
-      <c r="V3" s="122"/>
-      <c r="W3" s="122" t="s">
+      <c r="V3" s="121"/>
+      <c r="W3" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="X3" s="122"/>
-      <c r="Y3" s="122" t="s">
+      <c r="X3" s="121"/>
+      <c r="Y3" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="Z3" s="122"/>
+      <c r="Z3" s="121"/>
       <c r="AA3" s="23" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="104" t="s">
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="122" t="s">
-        <v>237</v>
-      </c>
-      <c r="L4" s="122"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="122"/>
-      <c r="O4" s="122"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="143"/>
-      <c r="S4" s="164" t="s">
-        <v>237</v>
-      </c>
-      <c r="T4" s="122"/>
-      <c r="U4" s="122"/>
-      <c r="V4" s="122"/>
-      <c r="W4" s="122"/>
-      <c r="X4" s="122"/>
-      <c r="Y4" s="122"/>
-      <c r="Z4" s="122"/>
-      <c r="AA4" s="143"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="121" t="s">
+        <v>231</v>
+      </c>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="121"/>
+      <c r="O4" s="121"/>
+      <c r="P4" s="121"/>
+      <c r="Q4" s="121"/>
+      <c r="R4" s="142"/>
+      <c r="S4" s="163" t="s">
+        <v>231</v>
+      </c>
+      <c r="T4" s="121"/>
+      <c r="U4" s="121"/>
+      <c r="V4" s="121"/>
+      <c r="W4" s="121"/>
+      <c r="X4" s="121"/>
+      <c r="Y4" s="121"/>
+      <c r="Z4" s="121"/>
+      <c r="AA4" s="142"/>
     </row>
     <row r="5" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="91" t="s">
         <v>71</v>
       </c>
       <c r="B5" s="12" t="s">
@@ -3392,11 +3427,11 @@
       <c r="D5" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="131" t="s">
+      <c r="E5" s="130" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="131"/>
-      <c r="G5" s="72" t="s">
+      <c r="F5" s="130"/>
+      <c r="G5" s="71" t="s">
         <v>29</v>
       </c>
       <c r="H5" s="12" t="s">
@@ -3405,127 +3440,127 @@
       <c r="I5" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="J5" s="73" t="s">
+      <c r="J5" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="122" t="s">
+      <c r="K5" s="121" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="122"/>
-      <c r="M5" s="122" t="s">
+      <c r="L5" s="121"/>
+      <c r="M5" s="121" t="s">
         <v>89</v>
       </c>
-      <c r="N5" s="122"/>
-      <c r="O5" s="122" t="s">
+      <c r="N5" s="121"/>
+      <c r="O5" s="121" t="s">
         <v>88</v>
       </c>
-      <c r="P5" s="122"/>
-      <c r="Q5" s="122" t="s">
+      <c r="P5" s="121"/>
+      <c r="Q5" s="121" t="s">
         <v>30</v>
       </c>
-      <c r="R5" s="143"/>
-      <c r="S5" s="164" t="s">
+      <c r="R5" s="142"/>
+      <c r="S5" s="163" t="s">
         <v>29</v>
       </c>
-      <c r="T5" s="122"/>
-      <c r="U5" s="122" t="s">
+      <c r="T5" s="121"/>
+      <c r="U5" s="121" t="s">
         <v>89</v>
       </c>
-      <c r="V5" s="122"/>
-      <c r="W5" s="122" t="s">
+      <c r="V5" s="121"/>
+      <c r="W5" s="121" t="s">
         <v>88</v>
       </c>
-      <c r="X5" s="122"/>
-      <c r="Y5" s="122" t="s">
+      <c r="X5" s="121"/>
+      <c r="Y5" s="121" t="s">
         <v>30</v>
       </c>
-      <c r="Z5" s="122"/>
+      <c r="Z5" s="121"/>
       <c r="AA5" s="23" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="154" t="s">
+      <c r="A6" s="153" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="107" t="s">
+      <c r="C6" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107" t="s">
+      <c r="D6" s="106"/>
+      <c r="E6" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="107"/>
-      <c r="G6" s="67" t="s">
+      <c r="F6" s="106"/>
+      <c r="G6" s="66" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="107" t="s">
+      <c r="I6" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="108"/>
-      <c r="K6" s="122" t="s">
-        <v>238</v>
-      </c>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
-      <c r="N6" s="122"/>
-      <c r="O6" s="122"/>
-      <c r="P6" s="122"/>
-      <c r="Q6" s="122"/>
-      <c r="R6" s="143"/>
-      <c r="S6" s="164" t="s">
-        <v>277</v>
-      </c>
-      <c r="T6" s="122"/>
-      <c r="U6" s="122"/>
-      <c r="V6" s="122"/>
-      <c r="W6" s="122"/>
-      <c r="X6" s="122"/>
-      <c r="Y6" s="122"/>
-      <c r="Z6" s="122"/>
-      <c r="AA6" s="143"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="121" t="s">
+        <v>232</v>
+      </c>
+      <c r="L6" s="121"/>
+      <c r="M6" s="121"/>
+      <c r="N6" s="121"/>
+      <c r="O6" s="121"/>
+      <c r="P6" s="121"/>
+      <c r="Q6" s="121"/>
+      <c r="R6" s="142"/>
+      <c r="S6" s="163" t="s">
+        <v>271</v>
+      </c>
+      <c r="T6" s="121"/>
+      <c r="U6" s="121"/>
+      <c r="V6" s="121"/>
+      <c r="W6" s="121"/>
+      <c r="X6" s="121"/>
+      <c r="Y6" s="121"/>
+      <c r="Z6" s="121"/>
+      <c r="AA6" s="142"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="154"/>
-      <c r="B7" s="105" t="s">
+      <c r="A7" s="153"/>
+      <c r="B7" s="104" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="104" t="s">
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="103" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="109"/>
-      <c r="K7" s="122"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="122"/>
-      <c r="N7" s="122"/>
-      <c r="O7" s="122"/>
-      <c r="P7" s="122"/>
-      <c r="Q7" s="122"/>
-      <c r="R7" s="143"/>
-      <c r="S7" s="164"/>
-      <c r="T7" s="122"/>
-      <c r="U7" s="122"/>
-      <c r="V7" s="122"/>
-      <c r="W7" s="122"/>
-      <c r="X7" s="122"/>
-      <c r="Y7" s="122"/>
-      <c r="Z7" s="122"/>
-      <c r="AA7" s="143"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="108"/>
+      <c r="K7" s="121"/>
+      <c r="L7" s="121"/>
+      <c r="M7" s="121"/>
+      <c r="N7" s="121"/>
+      <c r="O7" s="121"/>
+      <c r="P7" s="121"/>
+      <c r="Q7" s="121"/>
+      <c r="R7" s="142"/>
+      <c r="S7" s="163"/>
+      <c r="T7" s="121"/>
+      <c r="U7" s="121"/>
+      <c r="V7" s="121"/>
+      <c r="W7" s="121"/>
+      <c r="X7" s="121"/>
+      <c r="Y7" s="121"/>
+      <c r="Z7" s="121"/>
+      <c r="AA7" s="142"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="92" t="s">
+      <c r="A8" s="91" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="22"/>
@@ -3533,384 +3568,384 @@
       <c r="D8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="104" t="s">
+      <c r="E8" s="104"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="109"/>
-      <c r="K8" s="238" t="s">
-        <v>308</v>
-      </c>
-      <c r="L8" s="122"/>
-      <c r="M8" s="122"/>
-      <c r="N8" s="122"/>
-      <c r="O8" s="122"/>
-      <c r="P8" s="122"/>
-      <c r="Q8" s="122"/>
-      <c r="R8" s="143"/>
-      <c r="S8" s="164" t="s">
-        <v>307</v>
-      </c>
-      <c r="T8" s="122"/>
-      <c r="U8" s="122"/>
-      <c r="V8" s="122"/>
-      <c r="W8" s="122"/>
-      <c r="X8" s="122"/>
-      <c r="Y8" s="122"/>
-      <c r="Z8" s="122"/>
-      <c r="AA8" s="143"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="108"/>
+      <c r="K8" s="237" t="s">
+        <v>302</v>
+      </c>
+      <c r="L8" s="121"/>
+      <c r="M8" s="121"/>
+      <c r="N8" s="121"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="121"/>
+      <c r="R8" s="142"/>
+      <c r="S8" s="163" t="s">
+        <v>301</v>
+      </c>
+      <c r="T8" s="121"/>
+      <c r="U8" s="121"/>
+      <c r="V8" s="121"/>
+      <c r="W8" s="121"/>
+      <c r="X8" s="121"/>
+      <c r="Y8" s="121"/>
+      <c r="Z8" s="121"/>
+      <c r="AA8" s="142"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="155" t="s">
+      <c r="A9" s="154" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="105" t="s">
+      <c r="B9" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="105"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="104" t="s">
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="103" t="s">
         <v>114</v>
       </c>
-      <c r="H9" s="105"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="109"/>
-      <c r="K9" s="103" t="s">
-        <v>243</v>
-      </c>
-      <c r="L9" s="103"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="103"/>
-      <c r="O9" s="103" t="s">
-        <v>244</v>
-      </c>
-      <c r="P9" s="103"/>
-      <c r="Q9" s="103"/>
-      <c r="R9" s="144"/>
-      <c r="S9" s="165" t="s">
-        <v>273</v>
-      </c>
-      <c r="T9" s="103"/>
-      <c r="U9" s="103"/>
-      <c r="V9" s="103"/>
-      <c r="W9" s="103"/>
-      <c r="X9" s="103"/>
-      <c r="Y9" s="103"/>
-      <c r="Z9" s="103"/>
-      <c r="AA9" s="144"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="108"/>
+      <c r="K9" s="102" t="s">
+        <v>237</v>
+      </c>
+      <c r="L9" s="102"/>
+      <c r="M9" s="102"/>
+      <c r="N9" s="102"/>
+      <c r="O9" s="102" t="s">
+        <v>238</v>
+      </c>
+      <c r="P9" s="102"/>
+      <c r="Q9" s="102"/>
+      <c r="R9" s="143"/>
+      <c r="S9" s="164" t="s">
+        <v>267</v>
+      </c>
+      <c r="T9" s="102"/>
+      <c r="U9" s="102"/>
+      <c r="V9" s="102"/>
+      <c r="W9" s="102"/>
+      <c r="X9" s="102"/>
+      <c r="Y9" s="102"/>
+      <c r="Z9" s="102"/>
+      <c r="AA9" s="143"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="155"/>
-      <c r="B10" s="105"/>
-      <c r="C10" s="105"/>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="105"/>
-      <c r="G10" s="104" t="s">
+      <c r="A10" s="154"/>
+      <c r="B10" s="104"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="104"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="103" t="s">
         <v>128</v>
       </c>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="109"/>
-      <c r="K10" s="122" t="s">
-        <v>245</v>
-      </c>
-      <c r="L10" s="122"/>
-      <c r="M10" s="122"/>
-      <c r="N10" s="122"/>
-      <c r="O10" s="122" t="s">
-        <v>246</v>
-      </c>
-      <c r="P10" s="122"/>
-      <c r="Q10" s="122"/>
-      <c r="R10" s="143"/>
-      <c r="S10" s="164" t="s">
-        <v>274</v>
-      </c>
-      <c r="T10" s="122"/>
-      <c r="U10" s="122"/>
-      <c r="V10" s="122"/>
-      <c r="W10" s="122"/>
-      <c r="X10" s="122"/>
-      <c r="Y10" s="122" t="s">
-        <v>275</v>
-      </c>
-      <c r="Z10" s="122"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="121" t="s">
+        <v>239</v>
+      </c>
+      <c r="L10" s="121"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="121" t="s">
+        <v>240</v>
+      </c>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="121"/>
+      <c r="R10" s="142"/>
+      <c r="S10" s="163" t="s">
+        <v>268</v>
+      </c>
+      <c r="T10" s="121"/>
+      <c r="U10" s="121"/>
+      <c r="V10" s="121"/>
+      <c r="W10" s="121"/>
+      <c r="X10" s="121"/>
+      <c r="Y10" s="121" t="s">
+        <v>269</v>
+      </c>
+      <c r="Z10" s="121"/>
       <c r="AA10" s="23" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="151" t="s">
-        <v>300</v>
+      <c r="A11" s="150" t="s">
+        <v>294</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="103" t="s">
+      <c r="C11" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
       <c r="F11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="67" t="s">
+      <c r="G11" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="107" t="s">
+      <c r="H11" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="107"/>
-      <c r="J11" s="70" t="s">
+      <c r="I11" s="106"/>
+      <c r="J11" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="103" t="s">
-        <v>239</v>
-      </c>
-      <c r="L11" s="103"/>
-      <c r="M11" s="103" t="s">
+      <c r="K11" s="102" t="s">
+        <v>233</v>
+      </c>
+      <c r="L11" s="102"/>
+      <c r="M11" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="N11" s="103"/>
-      <c r="O11" s="103"/>
-      <c r="P11" s="103"/>
-      <c r="Q11" s="103" t="s">
-        <v>240</v>
-      </c>
-      <c r="R11" s="144"/>
-      <c r="S11" s="165" t="s">
-        <v>239</v>
-      </c>
-      <c r="T11" s="103"/>
-      <c r="U11" s="103" t="s">
+      <c r="N11" s="102"/>
+      <c r="O11" s="102"/>
+      <c r="P11" s="102"/>
+      <c r="Q11" s="102" t="s">
+        <v>234</v>
+      </c>
+      <c r="R11" s="143"/>
+      <c r="S11" s="164" t="s">
+        <v>233</v>
+      </c>
+      <c r="T11" s="102"/>
+      <c r="U11" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="V11" s="103"/>
-      <c r="W11" s="103"/>
-      <c r="X11" s="103"/>
-      <c r="Y11" s="103" t="s">
-        <v>240</v>
-      </c>
-      <c r="Z11" s="103"/>
-      <c r="AA11" s="144"/>
+      <c r="V11" s="102"/>
+      <c r="W11" s="102"/>
+      <c r="X11" s="102"/>
+      <c r="Y11" s="102" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z11" s="102"/>
+      <c r="AA11" s="143"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="151"/>
+      <c r="A12" s="150"/>
       <c r="B12" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="105" t="s">
+      <c r="C12" s="104" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="105"/>
-      <c r="E12" s="105"/>
+      <c r="D12" s="104"/>
+      <c r="E12" s="104"/>
       <c r="F12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="65" t="s">
+      <c r="G12" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="H12" s="105" t="s">
+      <c r="H12" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="105"/>
-      <c r="J12" s="66" t="s">
+      <c r="I12" s="104"/>
+      <c r="J12" s="65" t="s">
         <v>115</v>
       </c>
-      <c r="K12" s="105" t="s">
+      <c r="K12" s="104" t="s">
         <v>91</v>
       </c>
-      <c r="L12" s="105"/>
-      <c r="M12" s="105" t="s">
+      <c r="L12" s="104"/>
+      <c r="M12" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="N12" s="105"/>
-      <c r="O12" s="105"/>
-      <c r="P12" s="105"/>
-      <c r="Q12" s="105" t="s">
+      <c r="N12" s="104"/>
+      <c r="O12" s="104"/>
+      <c r="P12" s="104"/>
+      <c r="Q12" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="R12" s="149"/>
-      <c r="S12" s="113" t="s">
+      <c r="R12" s="148"/>
+      <c r="S12" s="112" t="s">
         <v>91</v>
       </c>
-      <c r="T12" s="105"/>
-      <c r="U12" s="105" t="s">
+      <c r="T12" s="104"/>
+      <c r="U12" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="V12" s="105"/>
-      <c r="W12" s="105"/>
-      <c r="X12" s="105"/>
-      <c r="Y12" s="105" t="s">
+      <c r="V12" s="104"/>
+      <c r="W12" s="104"/>
+      <c r="X12" s="104"/>
+      <c r="Y12" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="Z12" s="105"/>
-      <c r="AA12" s="149"/>
+      <c r="Z12" s="104"/>
+      <c r="AA12" s="148"/>
     </row>
     <row r="13" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="93" t="s">
+      <c r="A13" s="92" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="105" t="s">
+      <c r="C13" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="105"/>
-      <c r="E13" s="105"/>
+      <c r="D13" s="104"/>
+      <c r="E13" s="104"/>
       <c r="F13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="65" t="s">
+      <c r="G13" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="105" t="s">
+      <c r="H13" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="105"/>
-      <c r="J13" s="66" t="s">
+      <c r="I13" s="104"/>
+      <c r="J13" s="65" t="s">
         <v>115</v>
       </c>
-      <c r="K13" s="105" t="s">
+      <c r="K13" s="104" t="s">
         <v>91</v>
       </c>
-      <c r="L13" s="105"/>
-      <c r="M13" s="105" t="s">
+      <c r="L13" s="104"/>
+      <c r="M13" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="N13" s="105"/>
-      <c r="O13" s="105"/>
-      <c r="P13" s="105"/>
-      <c r="Q13" s="105" t="s">
+      <c r="N13" s="104"/>
+      <c r="O13" s="104"/>
+      <c r="P13" s="104"/>
+      <c r="Q13" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="R13" s="149"/>
-      <c r="S13" s="113" t="s">
-        <v>284</v>
-      </c>
-      <c r="T13" s="105"/>
-      <c r="U13" s="105" t="s">
+      <c r="R13" s="148"/>
+      <c r="S13" s="112" t="s">
+        <v>278</v>
+      </c>
+      <c r="T13" s="104"/>
+      <c r="U13" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="V13" s="105"/>
-      <c r="W13" s="105"/>
-      <c r="X13" s="105"/>
-      <c r="Y13" s="105" t="s">
+      <c r="V13" s="104"/>
+      <c r="W13" s="104"/>
+      <c r="X13" s="104"/>
+      <c r="Y13" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="Z13" s="105"/>
-      <c r="AA13" s="149"/>
+      <c r="Z13" s="104"/>
+      <c r="AA13" s="148"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="151" t="s">
+      <c r="A14" s="150" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="107" t="s">
+      <c r="B14" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="107"/>
-      <c r="D14" s="107" t="s">
+      <c r="C14" s="106"/>
+      <c r="D14" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="107"/>
-      <c r="F14" s="107"/>
-      <c r="G14" s="106" t="s">
+      <c r="E14" s="106"/>
+      <c r="F14" s="106"/>
+      <c r="G14" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="107"/>
-      <c r="I14" s="107" t="s">
+      <c r="H14" s="106"/>
+      <c r="I14" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="108"/>
-      <c r="K14" s="103" t="s">
-        <v>239</v>
-      </c>
-      <c r="L14" s="103"/>
-      <c r="M14" s="103"/>
-      <c r="N14" s="103"/>
-      <c r="O14" s="103" t="s">
-        <v>240</v>
-      </c>
-      <c r="P14" s="103"/>
-      <c r="Q14" s="103"/>
-      <c r="R14" s="144"/>
-      <c r="S14" s="165" t="s">
-        <v>278</v>
-      </c>
-      <c r="T14" s="103"/>
-      <c r="U14" s="103"/>
-      <c r="V14" s="103"/>
-      <c r="W14" s="103" t="s">
-        <v>279</v>
-      </c>
-      <c r="X14" s="103"/>
-      <c r="Y14" s="103"/>
-      <c r="Z14" s="103"/>
-      <c r="AA14" s="59"/>
+      <c r="J14" s="107"/>
+      <c r="K14" s="102" t="s">
+        <v>233</v>
+      </c>
+      <c r="L14" s="102"/>
+      <c r="M14" s="102"/>
+      <c r="N14" s="102"/>
+      <c r="O14" s="102" t="s">
+        <v>234</v>
+      </c>
+      <c r="P14" s="102"/>
+      <c r="Q14" s="102"/>
+      <c r="R14" s="143"/>
+      <c r="S14" s="164" t="s">
+        <v>272</v>
+      </c>
+      <c r="T14" s="102"/>
+      <c r="U14" s="102"/>
+      <c r="V14" s="102"/>
+      <c r="W14" s="102" t="s">
+        <v>273</v>
+      </c>
+      <c r="X14" s="102"/>
+      <c r="Y14" s="102"/>
+      <c r="Z14" s="102"/>
+      <c r="AA14" s="58"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="151"/>
-      <c r="B15" s="105" t="s">
+      <c r="A15" s="150"/>
+      <c r="B15" s="104" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="105"/>
-      <c r="D15" s="105" t="s">
+      <c r="C15" s="104"/>
+      <c r="D15" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="E15" s="105"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="104" t="s">
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="103" t="s">
         <v>116</v>
       </c>
-      <c r="H15" s="105"/>
-      <c r="I15" s="105" t="s">
+      <c r="H15" s="104"/>
+      <c r="I15" s="104" t="s">
         <v>117</v>
       </c>
-      <c r="J15" s="109"/>
-      <c r="K15" s="122" t="s">
-        <v>241</v>
-      </c>
-      <c r="L15" s="122"/>
-      <c r="M15" s="122"/>
-      <c r="N15" s="122"/>
-      <c r="O15" s="122" t="s">
-        <v>242</v>
-      </c>
-      <c r="P15" s="122"/>
-      <c r="Q15" s="122"/>
-      <c r="R15" s="143"/>
-      <c r="S15" s="164" t="s">
-        <v>280</v>
-      </c>
-      <c r="T15" s="122"/>
-      <c r="U15" s="103" t="s">
-        <v>281</v>
-      </c>
-      <c r="V15" s="103"/>
-      <c r="W15" s="103" t="s">
-        <v>282</v>
-      </c>
-      <c r="X15" s="103"/>
-      <c r="Y15" s="103" t="s">
-        <v>283</v>
-      </c>
-      <c r="Z15" s="103"/>
+      <c r="J15" s="108"/>
+      <c r="K15" s="121" t="s">
+        <v>235</v>
+      </c>
+      <c r="L15" s="121"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121" t="s">
+        <v>236</v>
+      </c>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="121"/>
+      <c r="R15" s="142"/>
+      <c r="S15" s="163" t="s">
+        <v>274</v>
+      </c>
+      <c r="T15" s="121"/>
+      <c r="U15" s="102" t="s">
+        <v>275</v>
+      </c>
+      <c r="V15" s="102"/>
+      <c r="W15" s="102" t="s">
+        <v>276</v>
+      </c>
+      <c r="X15" s="102"/>
+      <c r="Y15" s="102" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z15" s="102"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="151" t="s">
+      <c r="A16" s="150" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="107" t="s">
+      <c r="B16" s="106" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="107"/>
+      <c r="C16" s="106"/>
       <c r="D16" s="5" t="s">
         <v>97</v>
       </c>
@@ -3920,7 +3955,7 @@
       <c r="F16" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="G16" s="67" t="s">
+      <c r="G16" s="66" t="s">
         <v>96</v>
       </c>
       <c r="H16" s="5" t="s">
@@ -3929,55 +3964,55 @@
       <c r="I16" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="J16" s="70" t="s">
+      <c r="J16" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="K16" s="103" t="s">
-        <v>247</v>
-      </c>
-      <c r="L16" s="103"/>
-      <c r="M16" s="103" t="s">
-        <v>248</v>
-      </c>
-      <c r="N16" s="103"/>
-      <c r="O16" s="103" t="s">
-        <v>249</v>
-      </c>
-      <c r="P16" s="103"/>
-      <c r="Q16" s="103" t="s">
-        <v>250</v>
-      </c>
-      <c r="R16" s="144"/>
-      <c r="S16" s="165" t="s">
-        <v>285</v>
-      </c>
-      <c r="T16" s="103"/>
-      <c r="U16" s="58" t="s">
-        <v>286</v>
+      <c r="K16" s="102" t="s">
+        <v>241</v>
+      </c>
+      <c r="L16" s="102"/>
+      <c r="M16" s="102" t="s">
+        <v>242</v>
+      </c>
+      <c r="N16" s="102"/>
+      <c r="O16" s="102" t="s">
+        <v>243</v>
+      </c>
+      <c r="P16" s="102"/>
+      <c r="Q16" s="102" t="s">
+        <v>244</v>
+      </c>
+      <c r="R16" s="143"/>
+      <c r="S16" s="164" t="s">
+        <v>279</v>
+      </c>
+      <c r="T16" s="102"/>
+      <c r="U16" s="57" t="s">
+        <v>280</v>
       </c>
       <c r="V16" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="W16" s="103" t="s">
-        <v>288</v>
-      </c>
-      <c r="X16" s="103"/>
+        <v>281</v>
+      </c>
+      <c r="W16" s="102" t="s">
+        <v>282</v>
+      </c>
+      <c r="X16" s="102"/>
       <c r="Y16" s="4" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="AA16" s="53" t="s">
-        <v>250</v>
+        <v>281</v>
+      </c>
+      <c r="AA16" s="52" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A17" s="151"/>
-      <c r="B17" s="105" t="s">
+      <c r="A17" s="150"/>
+      <c r="B17" s="104" t="s">
         <v>102</v>
       </c>
-      <c r="C17" s="105"/>
+      <c r="C17" s="104"/>
       <c r="D17" s="1" t="s">
         <v>101</v>
       </c>
@@ -3987,7 +4022,7 @@
       <c r="F17" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G17" s="65" t="s">
+      <c r="G17" s="64" t="s">
         <v>120</v>
       </c>
       <c r="H17" s="1" t="s">
@@ -3996,94 +4031,94 @@
       <c r="I17" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J17" s="66" t="s">
+      <c r="J17" s="65" t="s">
         <v>122</v>
       </c>
-      <c r="K17" s="122" t="s">
-        <v>255</v>
-      </c>
-      <c r="L17" s="122"/>
-      <c r="M17" s="122" t="s">
-        <v>251</v>
-      </c>
-      <c r="N17" s="122"/>
-      <c r="O17" s="122" t="s">
-        <v>252</v>
-      </c>
-      <c r="P17" s="122"/>
-      <c r="Q17" s="122" t="s">
-        <v>253</v>
-      </c>
-      <c r="R17" s="143"/>
-      <c r="S17" s="164" t="s">
+      <c r="K17" s="121" t="s">
+        <v>249</v>
+      </c>
+      <c r="L17" s="121"/>
+      <c r="M17" s="121" t="s">
+        <v>245</v>
+      </c>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121" t="s">
+        <v>246</v>
+      </c>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="121" t="s">
+        <v>247</v>
+      </c>
+      <c r="R17" s="142"/>
+      <c r="S17" s="163" t="s">
+        <v>283</v>
+      </c>
+      <c r="T17" s="121"/>
+      <c r="U17" s="56" t="s">
+        <v>284</v>
+      </c>
+      <c r="V17" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="W17" s="121" t="s">
+        <v>286</v>
+      </c>
+      <c r="X17" s="121"/>
+      <c r="Y17" s="22" t="s">
         <v>289</v>
       </c>
-      <c r="T17" s="122"/>
-      <c r="U17" s="57" t="s">
-        <v>290</v>
-      </c>
-      <c r="V17" s="22" t="s">
-        <v>291</v>
-      </c>
-      <c r="W17" s="122" t="s">
-        <v>292</v>
-      </c>
-      <c r="X17" s="122"/>
-      <c r="Y17" s="22" t="s">
-        <v>295</v>
-      </c>
       <c r="Z17" s="22" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="AA17" s="23" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" s="151" t="s">
+      <c r="A18" s="150" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="107" t="s">
+      <c r="B18" s="106" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="107"/>
-      <c r="D18" s="107"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="107"/>
-      <c r="G18" s="106" t="s">
+      <c r="C18" s="106"/>
+      <c r="D18" s="106"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="105" t="s">
         <v>123</v>
       </c>
-      <c r="H18" s="107"/>
-      <c r="I18" s="107"/>
-      <c r="J18" s="108"/>
-      <c r="K18" s="103" t="s">
-        <v>309</v>
-      </c>
-      <c r="L18" s="103"/>
-      <c r="M18" s="103"/>
-      <c r="N18" s="103"/>
-      <c r="O18" s="103"/>
-      <c r="P18" s="103"/>
-      <c r="Q18" s="103"/>
-      <c r="R18" s="144"/>
-      <c r="S18" s="165" t="s">
-        <v>309</v>
-      </c>
-      <c r="T18" s="103"/>
-      <c r="U18" s="103"/>
-      <c r="V18" s="103"/>
-      <c r="W18" s="103"/>
-      <c r="X18" s="103"/>
-      <c r="Y18" s="103"/>
-      <c r="Z18" s="103"/>
-      <c r="AA18" s="144"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="107"/>
+      <c r="K18" s="102" t="s">
+        <v>303</v>
+      </c>
+      <c r="L18" s="102"/>
+      <c r="M18" s="102"/>
+      <c r="N18" s="102"/>
+      <c r="O18" s="102"/>
+      <c r="P18" s="102"/>
+      <c r="Q18" s="102"/>
+      <c r="R18" s="143"/>
+      <c r="S18" s="164" t="s">
+        <v>303</v>
+      </c>
+      <c r="T18" s="102"/>
+      <c r="U18" s="102"/>
+      <c r="V18" s="102"/>
+      <c r="W18" s="102"/>
+      <c r="X18" s="102"/>
+      <c r="Y18" s="102"/>
+      <c r="Z18" s="102"/>
+      <c r="AA18" s="143"/>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A19" s="151"/>
-      <c r="B19" s="105" t="s">
+      <c r="A19" s="150"/>
+      <c r="B19" s="104" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="105"/>
+      <c r="C19" s="104"/>
       <c r="D19" s="1" t="s">
         <v>105</v>
       </c>
@@ -4093,7 +4128,7 @@
       <c r="F19" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G19" s="65" t="s">
+      <c r="G19" s="64" t="s">
         <v>124</v>
       </c>
       <c r="H19" s="1" t="s">
@@ -4102,129 +4137,129 @@
       <c r="I19" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="J19" s="66" t="s">
+      <c r="J19" s="65" t="s">
         <v>127</v>
       </c>
-      <c r="K19" s="122" t="s">
+      <c r="K19" s="121" t="s">
+        <v>304</v>
+      </c>
+      <c r="L19" s="121"/>
+      <c r="M19" s="121" t="s">
+        <v>305</v>
+      </c>
+      <c r="N19" s="121"/>
+      <c r="O19" s="149" t="s">
+        <v>306</v>
+      </c>
+      <c r="P19" s="121"/>
+      <c r="Q19" s="121" t="s">
+        <v>307</v>
+      </c>
+      <c r="R19" s="142"/>
+      <c r="S19" s="163" t="s">
+        <v>308</v>
+      </c>
+      <c r="T19" s="121"/>
+      <c r="U19" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="V19" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="L19" s="122"/>
-      <c r="M19" s="122" t="s">
+      <c r="W19" s="121" t="s">
         <v>311</v>
       </c>
-      <c r="N19" s="122"/>
-      <c r="O19" s="150" t="s">
+      <c r="X19" s="121"/>
+      <c r="Y19" s="54" t="s">
         <v>312</v>
       </c>
-      <c r="P19" s="122"/>
-      <c r="Q19" s="122" t="s">
+      <c r="Z19" s="22" t="s">
         <v>313</v>
       </c>
-      <c r="R19" s="143"/>
-      <c r="S19" s="164" t="s">
+      <c r="AA19" s="23" t="s">
         <v>314</v>
       </c>
-      <c r="T19" s="122"/>
-      <c r="U19" s="22" t="s">
-        <v>315</v>
-      </c>
-      <c r="V19" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="W19" s="122" t="s">
-        <v>317</v>
-      </c>
-      <c r="X19" s="122"/>
-      <c r="Y19" s="55" t="s">
-        <v>318</v>
-      </c>
-      <c r="Z19" s="22" t="s">
-        <v>319</v>
-      </c>
-      <c r="AA19" s="23" t="s">
-        <v>320</v>
-      </c>
     </row>
     <row r="20" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="92" t="s">
+      <c r="A20" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="105" t="s">
+      <c r="B20" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="105"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="104" t="s">
+      <c r="C20" s="104"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="103" t="s">
         <v>83</v>
       </c>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="145" t="s">
-        <v>254</v>
-      </c>
-      <c r="L20" s="145"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="145"/>
-      <c r="O20" s="145"/>
-      <c r="P20" s="145"/>
-      <c r="Q20" s="145"/>
-      <c r="R20" s="146"/>
-      <c r="S20" s="166" t="s">
-        <v>254</v>
-      </c>
-      <c r="T20" s="145"/>
-      <c r="U20" s="145"/>
-      <c r="V20" s="145"/>
-      <c r="W20" s="145"/>
-      <c r="X20" s="145"/>
-      <c r="Y20" s="145"/>
-      <c r="Z20" s="145"/>
-      <c r="AA20" s="146"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="108"/>
+      <c r="K20" s="144" t="s">
+        <v>248</v>
+      </c>
+      <c r="L20" s="144"/>
+      <c r="M20" s="144"/>
+      <c r="N20" s="144"/>
+      <c r="O20" s="144"/>
+      <c r="P20" s="144"/>
+      <c r="Q20" s="144"/>
+      <c r="R20" s="145"/>
+      <c r="S20" s="165" t="s">
+        <v>248</v>
+      </c>
+      <c r="T20" s="144"/>
+      <c r="U20" s="144"/>
+      <c r="V20" s="144"/>
+      <c r="W20" s="144"/>
+      <c r="X20" s="144"/>
+      <c r="Y20" s="144"/>
+      <c r="Z20" s="144"/>
+      <c r="AA20" s="145"/>
     </row>
     <row r="21" spans="1:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="92" t="s">
+      <c r="A21" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="105" t="s">
+      <c r="B21" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="105"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="105"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="158" t="s">
+      <c r="C21" s="104"/>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="157" t="s">
         <v>34</v>
       </c>
-      <c r="H21" s="159"/>
-      <c r="I21" s="159"/>
-      <c r="J21" s="160"/>
-      <c r="K21" s="147" t="s">
+      <c r="H21" s="158"/>
+      <c r="I21" s="158"/>
+      <c r="J21" s="159"/>
+      <c r="K21" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="L21" s="147"/>
-      <c r="M21" s="147"/>
-      <c r="N21" s="147"/>
-      <c r="O21" s="147"/>
-      <c r="P21" s="147"/>
-      <c r="Q21" s="147"/>
-      <c r="R21" s="148"/>
-      <c r="S21" s="167" t="s">
+      <c r="L21" s="146"/>
+      <c r="M21" s="146"/>
+      <c r="N21" s="146"/>
+      <c r="O21" s="146"/>
+      <c r="P21" s="146"/>
+      <c r="Q21" s="146"/>
+      <c r="R21" s="147"/>
+      <c r="S21" s="166" t="s">
         <v>34</v>
       </c>
-      <c r="T21" s="147"/>
-      <c r="U21" s="147"/>
-      <c r="V21" s="147"/>
-      <c r="W21" s="147"/>
-      <c r="X21" s="147"/>
-      <c r="Y21" s="147"/>
-      <c r="Z21" s="147"/>
-      <c r="AA21" s="148"/>
+      <c r="T21" s="146"/>
+      <c r="U21" s="146"/>
+      <c r="V21" s="146"/>
+      <c r="W21" s="146"/>
+      <c r="X21" s="146"/>
+      <c r="Y21" s="146"/>
+      <c r="Z21" s="146"/>
+      <c r="AA21" s="147"/>
     </row>
     <row r="22" spans="1:27" s="18" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="94" t="s">
+      <c r="A22" s="93" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="17"/>
@@ -4232,10 +4267,10 @@
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
-      <c r="G22" s="97"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
-      <c r="J22" s="98"/>
+      <c r="G22" s="96"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="97"/>
       <c r="O22" s="24"/>
       <c r="P22" s="24"/>
       <c r="Q22" s="24"/>
@@ -4243,11 +4278,11 @@
       <c r="W22" s="24"/>
       <c r="X22" s="24"/>
       <c r="Y22" s="24"/>
-      <c r="Z22" s="60"/>
+      <c r="Z22" s="59"/>
       <c r="AA22" s="25"/>
     </row>
     <row r="23" spans="1:27" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="92" t="s">
+      <c r="A23" s="91" t="s">
         <v>5</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -4265,26 +4300,26 @@
       <c r="F23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G23" s="81" t="s">
+      <c r="G23" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="H23" s="82" t="s">
+      <c r="H23" s="81" t="s">
         <v>109</v>
       </c>
-      <c r="I23" s="82" t="s">
+      <c r="I23" s="81" t="s">
         <v>110</v>
       </c>
-      <c r="J23" s="83" t="s">
+      <c r="J23" s="82" t="s">
         <v>37</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>36</v>
@@ -4302,13 +4337,13 @@
         <v>37</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="V23" s="1" t="s">
         <v>36</v>
@@ -4322,15 +4357,15 @@
       <c r="Y23" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="Z23" s="54" t="s">
+      <c r="Z23" s="53" t="s">
         <v>37</v>
       </c>
       <c r="AA23" s="23" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="92" t="s">
+      <c r="A24" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="22" t="s">
@@ -4348,7 +4383,7 @@
       <c r="F24" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="65" t="s">
+      <c r="G24" s="64" t="s">
         <v>47</v>
       </c>
       <c r="H24" s="1" t="s">
@@ -4357,191 +4392,191 @@
       <c r="I24" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J24" s="66" t="s">
+      <c r="J24" s="65" t="s">
         <v>39</v>
       </c>
       <c r="K24" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="O24" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="P24" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q24" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="R24" s="23" t="s">
         <v>260</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="S24" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="W24" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="X24" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="Y24" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="Z24" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="AA24" s="23" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="92" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="104" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="104"/>
+      <c r="D25" s="104"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="103" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="104"/>
+      <c r="I25" s="104"/>
+      <c r="J25" s="108"/>
+      <c r="K25" s="140" t="s">
+        <v>232</v>
+      </c>
+      <c r="L25" s="140"/>
+      <c r="M25" s="140"/>
+      <c r="N25" s="140"/>
+      <c r="O25" s="140"/>
+      <c r="P25" s="140"/>
+      <c r="Q25" s="140"/>
+      <c r="R25" s="141"/>
+      <c r="S25" s="167" t="s">
+        <v>271</v>
+      </c>
+      <c r="T25" s="140"/>
+      <c r="U25" s="140"/>
+      <c r="V25" s="140"/>
+      <c r="W25" s="140"/>
+      <c r="X25" s="140"/>
+      <c r="Y25" s="140"/>
+      <c r="Z25" s="140"/>
+      <c r="AA25" s="141"/>
+    </row>
+    <row r="26" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="94" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="104" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="104"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="104"/>
+      <c r="G26" s="103" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" s="104"/>
+      <c r="I26" s="104"/>
+      <c r="J26" s="108"/>
+      <c r="K26" s="140" t="s">
         <v>261</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="L26" s="140"/>
+      <c r="M26" s="140"/>
+      <c r="N26" s="140"/>
+      <c r="O26" s="140"/>
+      <c r="P26" s="140"/>
+      <c r="Q26" s="140"/>
+      <c r="R26" s="141"/>
+      <c r="S26" s="167" t="s">
+        <v>292</v>
+      </c>
+      <c r="T26" s="140"/>
+      <c r="U26" s="140"/>
+      <c r="V26" s="140"/>
+      <c r="W26" s="140"/>
+      <c r="X26" s="140"/>
+      <c r="Y26" s="140"/>
+      <c r="Z26" s="140"/>
+      <c r="AA26" s="141"/>
+    </row>
+    <row r="27" spans="1:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="95" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="104" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="104"/>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="109" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27" s="110"/>
+      <c r="I27" s="110"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="140" t="s">
         <v>262</v>
       </c>
-      <c r="O24" s="22" t="s">
+      <c r="L27" s="140"/>
+      <c r="M27" s="140"/>
+      <c r="N27" s="140"/>
+      <c r="O27" s="140"/>
+      <c r="P27" s="140"/>
+      <c r="Q27" s="140"/>
+      <c r="R27" s="141"/>
+      <c r="S27" s="167" t="s">
+        <v>293</v>
+      </c>
+      <c r="T27" s="140"/>
+      <c r="U27" s="140"/>
+      <c r="V27" s="140"/>
+      <c r="W27" s="140"/>
+      <c r="X27" s="140"/>
+      <c r="Y27" s="140"/>
+      <c r="Z27" s="140"/>
+      <c r="AA27" s="141"/>
+    </row>
+    <row r="28" spans="1:27" s="18" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="93" t="s">
         <v>263</v>
-      </c>
-      <c r="P24" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q24" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="R24" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="W24" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="X24" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="Y24" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="Z24" s="22" t="s">
-        <v>266</v>
-      </c>
-      <c r="AA24" s="23" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="93" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="105" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="105"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="105"/>
-      <c r="G25" s="104" t="s">
-        <v>48</v>
-      </c>
-      <c r="H25" s="105"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="109"/>
-      <c r="K25" s="141" t="s">
-        <v>238</v>
-      </c>
-      <c r="L25" s="141"/>
-      <c r="M25" s="141"/>
-      <c r="N25" s="141"/>
-      <c r="O25" s="141"/>
-      <c r="P25" s="141"/>
-      <c r="Q25" s="141"/>
-      <c r="R25" s="142"/>
-      <c r="S25" s="168" t="s">
-        <v>277</v>
-      </c>
-      <c r="T25" s="141"/>
-      <c r="U25" s="141"/>
-      <c r="V25" s="141"/>
-      <c r="W25" s="141"/>
-      <c r="X25" s="141"/>
-      <c r="Y25" s="141"/>
-      <c r="Z25" s="141"/>
-      <c r="AA25" s="142"/>
-    </row>
-    <row r="26" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="95" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="105" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="105"/>
-      <c r="D26" s="105"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="105"/>
-      <c r="G26" s="104" t="s">
-        <v>49</v>
-      </c>
-      <c r="H26" s="105"/>
-      <c r="I26" s="105"/>
-      <c r="J26" s="109"/>
-      <c r="K26" s="141" t="s">
-        <v>267</v>
-      </c>
-      <c r="L26" s="141"/>
-      <c r="M26" s="141"/>
-      <c r="N26" s="141"/>
-      <c r="O26" s="141"/>
-      <c r="P26" s="141"/>
-      <c r="Q26" s="141"/>
-      <c r="R26" s="142"/>
-      <c r="S26" s="168" t="s">
-        <v>298</v>
-      </c>
-      <c r="T26" s="141"/>
-      <c r="U26" s="141"/>
-      <c r="V26" s="141"/>
-      <c r="W26" s="141"/>
-      <c r="X26" s="141"/>
-      <c r="Y26" s="141"/>
-      <c r="Z26" s="141"/>
-      <c r="AA26" s="142"/>
-    </row>
-    <row r="27" spans="1:27" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="96" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="105" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="105"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="105"/>
-      <c r="F27" s="105"/>
-      <c r="G27" s="110" t="s">
-        <v>50</v>
-      </c>
-      <c r="H27" s="111"/>
-      <c r="I27" s="111"/>
-      <c r="J27" s="112"/>
-      <c r="K27" s="141" t="s">
-        <v>268</v>
-      </c>
-      <c r="L27" s="141"/>
-      <c r="M27" s="141"/>
-      <c r="N27" s="141"/>
-      <c r="O27" s="141"/>
-      <c r="P27" s="141"/>
-      <c r="Q27" s="141"/>
-      <c r="R27" s="142"/>
-      <c r="S27" s="168" t="s">
-        <v>299</v>
-      </c>
-      <c r="T27" s="141"/>
-      <c r="U27" s="141"/>
-      <c r="V27" s="141"/>
-      <c r="W27" s="141"/>
-      <c r="X27" s="141"/>
-      <c r="Y27" s="141"/>
-      <c r="Z27" s="141"/>
-      <c r="AA27" s="142"/>
-    </row>
-    <row r="28" spans="1:27" s="18" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="94" t="s">
-        <v>269</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
-      <c r="G28" s="99"/>
-      <c r="H28" s="100"/>
-      <c r="I28" s="100"/>
-      <c r="J28" s="101"/>
+      <c r="G28" s="98"/>
+      <c r="H28" s="99"/>
+      <c r="I28" s="99"/>
+      <c r="J28" s="100"/>
       <c r="O28" s="24"/>
       <c r="P28" s="24"/>
       <c r="Q28" s="24"/>
@@ -4719,45 +4754,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74"/>
-      <c r="B1" s="135" t="s">
+      <c r="A1" s="73"/>
+      <c r="B1" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="137" t="s">
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="136" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="115" t="s">
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="117"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="116"/>
     </row>
     <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="74" t="s">
         <v>46</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="60"/>
       <c r="G2" s="21"/>
       <c r="H2" s="21"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="60"/>
       <c r="K2" s="21"/>
       <c r="L2" s="21"/>
-      <c r="M2" s="62"/>
+      <c r="M2" s="61"/>
     </row>
     <row r="3" spans="1:16" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="75" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="14" t="s">
@@ -4769,10 +4804,10 @@
       <c r="D3" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="E3" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="63" t="s">
+      <c r="F3" s="62" t="s">
         <v>65</v>
       </c>
       <c r="G3" s="15" t="s">
@@ -4781,24 +4816,24 @@
       <c r="H3" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="64" t="s">
+      <c r="I3" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="63" t="s">
+      <c r="J3" s="62" t="s">
         <v>67</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>68</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="M3" s="64" t="s">
-        <v>305</v>
+        <v>265</v>
+      </c>
+      <c r="M3" s="63" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="76" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -4810,10 +4845,10 @@
       <c r="D4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="66" t="s">
+      <c r="E4" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="65" t="s">
+      <c r="F4" s="64" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -4822,18 +4857,18 @@
       <c r="H4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="66" t="s">
+      <c r="I4" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="118" t="s">
+      <c r="J4" s="117" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
-      <c r="M4" s="120"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="119"/>
     </row>
     <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="76" t="s">
         <v>71</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -4845,10 +4880,10 @@
       <c r="D5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="66" t="s">
+      <c r="E5" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="65" t="s">
+      <c r="F5" s="64" t="s">
         <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -4857,24 +4892,24 @@
       <c r="H5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="66" t="s">
+      <c r="I5" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="65" t="s">
+      <c r="J5" s="64" t="s">
         <v>88</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>30</v>
       </c>
       <c r="L5" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="M5" s="66" t="s">
-        <v>306</v>
+        <v>266</v>
+      </c>
+      <c r="M5" s="65" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="140" t="s">
+      <c r="A6" s="139" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -4883,460 +4918,460 @@
       <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="107" t="s">
+      <c r="D6" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="108"/>
-      <c r="F6" s="67" t="s">
+      <c r="E6" s="107"/>
+      <c r="F6" s="66" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="107" t="s">
+      <c r="H6" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="108"/>
-      <c r="J6" s="67" t="s">
+      <c r="I6" s="107"/>
+      <c r="J6" s="66" t="s">
         <v>10</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="103" t="s">
+      <c r="L6" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="M6" s="121"/>
-      <c r="P6" s="56"/>
+      <c r="M6" s="120"/>
+      <c r="P6" s="55"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="140"/>
-      <c r="B7" s="134" t="s">
+      <c r="A7" s="139"/>
+      <c r="B7" s="133" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="130" t="s">
+      <c r="C7" s="130"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="129" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="104" t="s">
+      <c r="G7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="131"/>
+      <c r="J7" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="105"/>
-      <c r="L7" s="122" t="s">
+      <c r="K7" s="104"/>
+      <c r="L7" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="M7" s="123"/>
+      <c r="M7" s="122"/>
     </row>
     <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="77" t="s">
+      <c r="A8" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="113" t="s">
+      <c r="B8" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="105"/>
-      <c r="D8" s="105" t="s">
+      <c r="C8" s="104"/>
+      <c r="D8" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="109"/>
-      <c r="F8" s="130" t="s">
+      <c r="E8" s="108"/>
+      <c r="F8" s="129" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="131"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="132"/>
-      <c r="J8" s="104" t="s">
+      <c r="G8" s="130"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="105"/>
-      <c r="L8" s="105"/>
-      <c r="M8" s="109"/>
+      <c r="K8" s="104"/>
+      <c r="L8" s="104"/>
+      <c r="M8" s="108"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="133" t="s">
+      <c r="A9" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="134" t="s">
+      <c r="B9" s="133" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="131"/>
-      <c r="D9" s="131" t="s">
+      <c r="C9" s="130"/>
+      <c r="D9" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="132"/>
-      <c r="F9" s="104" t="s">
+      <c r="E9" s="131"/>
+      <c r="F9" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="109"/>
-      <c r="J9" s="104" t="s">
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="105"/>
-      <c r="L9" s="105"/>
-      <c r="M9" s="109"/>
+      <c r="K9" s="104"/>
+      <c r="L9" s="104"/>
+      <c r="M9" s="108"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="133"/>
-      <c r="B10" s="134"/>
-      <c r="C10" s="131"/>
-      <c r="D10" s="131"/>
-      <c r="E10" s="132"/>
-      <c r="F10" s="104"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="109"/>
-      <c r="J10" s="104"/>
-      <c r="K10" s="105"/>
-      <c r="L10" s="105"/>
-      <c r="M10" s="109"/>
+      <c r="A10" s="132"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="130"/>
+      <c r="D10" s="130"/>
+      <c r="E10" s="131"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="103"/>
+      <c r="K10" s="104"/>
+      <c r="L10" s="104"/>
+      <c r="M10" s="108"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="128" t="s">
-        <v>300</v>
+      <c r="A11" s="127" t="s">
+        <v>294</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="103" t="s">
+      <c r="C11" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="103"/>
-      <c r="E11" s="68" t="s">
+      <c r="D11" s="102"/>
+      <c r="E11" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="71" t="s">
+      <c r="F11" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="103" t="s">
+      <c r="G11" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="103"/>
-      <c r="I11" s="68" t="s">
+      <c r="H11" s="102"/>
+      <c r="I11" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="67" t="s">
+      <c r="J11" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="K11" s="107" t="s">
+      <c r="K11" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="L11" s="107"/>
-      <c r="M11" s="70" t="s">
+      <c r="L11" s="106"/>
+      <c r="M11" s="69" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="128"/>
+      <c r="A12" s="127"/>
       <c r="B12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="105" t="s">
+      <c r="C12" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="105"/>
-      <c r="E12" s="66" t="s">
+      <c r="D12" s="104"/>
+      <c r="E12" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="65" t="s">
+      <c r="F12" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="105" t="s">
+      <c r="G12" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="105"/>
-      <c r="I12" s="66" t="s">
+      <c r="H12" s="104"/>
+      <c r="I12" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="J12" s="65" t="s">
+      <c r="J12" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="K12" s="105" t="s">
+      <c r="K12" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="L12" s="105"/>
-      <c r="M12" s="69" t="s">
+      <c r="L12" s="104"/>
+      <c r="M12" s="68" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="77" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="105" t="s">
+      <c r="C13" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="105"/>
-      <c r="E13" s="66" t="s">
+      <c r="D13" s="104"/>
+      <c r="E13" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="65" t="s">
+      <c r="F13" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="105" t="s">
+      <c r="G13" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="H13" s="105"/>
-      <c r="I13" s="66" t="s">
+      <c r="H13" s="104"/>
+      <c r="I13" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="65" t="s">
+      <c r="J13" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="K13" s="105" t="s">
+      <c r="K13" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="105"/>
-      <c r="M13" s="69" t="s">
+      <c r="L13" s="104"/>
+      <c r="M13" s="68" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="124" t="s">
+      <c r="A14" s="123" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="129" t="s">
+      <c r="B14" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="107"/>
-      <c r="D14" s="107" t="s">
+      <c r="C14" s="106"/>
+      <c r="D14" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="108"/>
-      <c r="F14" s="106" t="s">
+      <c r="E14" s="107"/>
+      <c r="F14" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="107"/>
-      <c r="H14" s="107" t="s">
+      <c r="G14" s="106"/>
+      <c r="H14" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="108"/>
-      <c r="J14" s="67" t="s">
+      <c r="I14" s="107"/>
+      <c r="J14" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="107" t="s">
+      <c r="K14" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="L14" s="107"/>
-      <c r="M14" s="70" t="s">
+      <c r="L14" s="106"/>
+      <c r="M14" s="69" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="124"/>
-      <c r="B15" s="113" t="s">
+      <c r="A15" s="123"/>
+      <c r="B15" s="112" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="105"/>
-      <c r="D15" s="105" t="s">
+      <c r="C15" s="104"/>
+      <c r="D15" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="109"/>
-      <c r="F15" s="104" t="s">
+      <c r="E15" s="108"/>
+      <c r="F15" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="105"/>
-      <c r="H15" s="105" t="s">
+      <c r="G15" s="104"/>
+      <c r="H15" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="I15" s="109"/>
-      <c r="J15" s="65" t="s">
+      <c r="I15" s="108"/>
+      <c r="J15" s="64" t="s">
         <v>131</v>
       </c>
-      <c r="K15" s="105" t="s">
+      <c r="K15" s="104" t="s">
         <v>132</v>
       </c>
-      <c r="L15" s="105"/>
-      <c r="M15" s="69" t="s">
+      <c r="L15" s="104"/>
+      <c r="M15" s="68" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="123" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="125" t="s">
+      <c r="B16" s="124" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="126"/>
+      <c r="C16" s="125"/>
       <c r="D16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="70" t="s">
+      <c r="E16" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="127" t="s">
+      <c r="F16" s="126" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="126"/>
+      <c r="G16" s="125"/>
       <c r="H16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I16" s="70" t="s">
+      <c r="I16" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="J16" s="102" t="s">
+      <c r="J16" s="101" t="s">
         <v>134</v>
       </c>
-      <c r="K16" s="103"/>
+      <c r="K16" s="102"/>
       <c r="L16" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="M16" s="70" t="s">
+      <c r="M16" s="69" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="113" t="s">
+      <c r="A17" s="123"/>
+      <c r="B17" s="112" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="105"/>
+      <c r="C17" s="104"/>
       <c r="D17" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="66" t="s">
+      <c r="E17" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="F17" s="104" t="s">
+      <c r="F17" s="103" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="105"/>
+      <c r="G17" s="104"/>
       <c r="H17" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="66" t="s">
+      <c r="I17" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="J17" s="104" t="s">
+      <c r="J17" s="103" t="s">
         <v>136</v>
       </c>
-      <c r="K17" s="105"/>
+      <c r="K17" s="104"/>
       <c r="L17" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="M17" s="69" t="s">
+      <c r="M17" s="68" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="128" t="s">
+      <c r="A18" s="127" t="s">
         <v>84</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="103" t="s">
+      <c r="C18" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="103"/>
-      <c r="E18" s="68" t="s">
+      <c r="D18" s="102"/>
+      <c r="E18" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="71" t="s">
+      <c r="F18" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="G18" s="103" t="s">
+      <c r="G18" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="H18" s="103"/>
-      <c r="I18" s="68" t="s">
+      <c r="H18" s="102"/>
+      <c r="I18" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="106" t="s">
-        <v>301</v>
-      </c>
-      <c r="K18" s="107"/>
-      <c r="L18" s="107"/>
-      <c r="M18" s="108"/>
+      <c r="J18" s="105" t="s">
+        <v>295</v>
+      </c>
+      <c r="K18" s="106"/>
+      <c r="L18" s="106"/>
+      <c r="M18" s="107"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="128"/>
+      <c r="A19" s="127"/>
       <c r="B19" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="105" t="s">
+      <c r="C19" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="105"/>
-      <c r="E19" s="66" t="s">
+      <c r="D19" s="104"/>
+      <c r="E19" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="F19" s="65" t="s">
+      <c r="F19" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="105" t="s">
+      <c r="G19" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="H19" s="105"/>
-      <c r="I19" s="66" t="s">
+      <c r="H19" s="104"/>
+      <c r="I19" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="J19" s="104" t="s">
-        <v>304</v>
-      </c>
-      <c r="K19" s="105"/>
+      <c r="J19" s="103" t="s">
+        <v>298</v>
+      </c>
+      <c r="K19" s="104"/>
       <c r="L19" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="M19" s="69" t="s">
-        <v>302</v>
+        <v>297</v>
+      </c>
+      <c r="M19" s="68" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="77" t="s">
+      <c r="A20" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="113" t="s">
+      <c r="B20" s="112" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="105"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="109"/>
-      <c r="F20" s="104" t="s">
+      <c r="C20" s="104"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="103" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="104" t="s">
+      <c r="G20" s="104"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="103" t="s">
         <v>139</v>
       </c>
-      <c r="K20" s="105"/>
-      <c r="L20" s="105"/>
-      <c r="M20" s="109"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="108"/>
     </row>
     <row r="21" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="79" t="s">
+      <c r="A21" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="114" t="s">
+      <c r="B21" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="111"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="112"/>
-      <c r="F21" s="110" t="s">
+      <c r="C21" s="110"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="109" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="111"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="112"/>
-      <c r="J21" s="110" t="s">
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="109" t="s">
         <v>34</v>
       </c>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="112"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="110"/>
+      <c r="M21" s="111"/>
     </row>
   </sheetData>
   <mergeCells count="62">
@@ -5432,1447 +5467,1457 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="2" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="232" t="s">
+      <c r="B1" s="231" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="234" t="s">
+      <c r="C1" s="232"/>
+      <c r="D1" s="232"/>
+      <c r="E1" s="232"/>
+      <c r="F1" s="232"/>
+      <c r="G1" s="232"/>
+      <c r="H1" s="233" t="s">
         <v>141</v>
       </c>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
-      <c r="L1" s="234"/>
-      <c r="M1" s="234"/>
-      <c r="N1" s="224" t="s">
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="233"/>
+      <c r="M1" s="233"/>
+      <c r="N1" s="223" t="s">
         <v>143</v>
       </c>
-      <c r="O1" s="224"/>
-      <c r="P1" s="224"/>
-      <c r="Q1" s="224"/>
-      <c r="R1" s="224"/>
-      <c r="S1" s="224"/>
-      <c r="T1" s="213" t="s">
+      <c r="O1" s="223"/>
+      <c r="P1" s="223"/>
+      <c r="Q1" s="223"/>
+      <c r="R1" s="223"/>
+      <c r="S1" s="223"/>
+      <c r="T1" s="212" t="s">
         <v>145</v>
       </c>
-      <c r="U1" s="214"/>
-      <c r="V1" s="214"/>
-      <c r="W1" s="214"/>
-      <c r="X1" s="214"/>
-      <c r="Y1" s="215"/>
+      <c r="U1" s="213"/>
+      <c r="V1" s="213"/>
+      <c r="W1" s="213"/>
+      <c r="X1" s="213"/>
+      <c r="Y1" s="214"/>
     </row>
     <row r="2" spans="1:26" s="3" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="217"/>
-      <c r="C2" s="218"/>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
-      <c r="F2" s="218"/>
-      <c r="G2" s="219"/>
-      <c r="H2" s="217"/>
-      <c r="I2" s="218"/>
-      <c r="J2" s="218"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="218"/>
-      <c r="M2" s="219"/>
-      <c r="N2" s="217" t="s">
-        <v>208</v>
-      </c>
-      <c r="O2" s="218"/>
-      <c r="P2" s="218"/>
-      <c r="Q2" s="218"/>
-      <c r="R2" s="218"/>
-      <c r="S2" s="219"/>
-      <c r="T2" s="217"/>
-      <c r="U2" s="218"/>
-      <c r="V2" s="218"/>
-      <c r="W2" s="218"/>
-      <c r="X2" s="218"/>
-      <c r="Y2" s="219"/>
+      <c r="B2" s="216"/>
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="217"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="216"/>
+      <c r="I2" s="217"/>
+      <c r="J2" s="217"/>
+      <c r="K2" s="217"/>
+      <c r="L2" s="217"/>
+      <c r="M2" s="218"/>
+      <c r="N2" s="216" t="s">
+        <v>203</v>
+      </c>
+      <c r="O2" s="217"/>
+      <c r="P2" s="217"/>
+      <c r="Q2" s="217"/>
+      <c r="R2" s="217"/>
+      <c r="S2" s="218"/>
+      <c r="T2" s="216"/>
+      <c r="U2" s="217"/>
+      <c r="V2" s="217"/>
+      <c r="W2" s="217"/>
+      <c r="X2" s="217"/>
+      <c r="Y2" s="218"/>
     </row>
     <row r="3" spans="1:26" s="16" customFormat="1" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="230" t="s">
+      <c r="B3" s="229" t="s">
+        <v>315</v>
+      </c>
+      <c r="C3" s="230"/>
+      <c r="D3" s="169" t="s">
+        <v>316</v>
+      </c>
+      <c r="E3" s="169"/>
+      <c r="F3" s="169" t="s">
+        <v>320</v>
+      </c>
+      <c r="G3" s="170"/>
+      <c r="H3" s="215" t="s">
+        <v>207</v>
+      </c>
+      <c r="I3" s="169"/>
+      <c r="J3" s="169" t="s">
+        <v>204</v>
+      </c>
+      <c r="K3" s="169"/>
+      <c r="L3" s="169" t="s">
+        <v>205</v>
+      </c>
+      <c r="M3" s="170"/>
+      <c r="N3" s="215" t="s">
+        <v>317</v>
+      </c>
+      <c r="O3" s="169"/>
+      <c r="P3" s="169" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q3" s="169"/>
+      <c r="R3" s="169" t="s">
+        <v>319</v>
+      </c>
+      <c r="S3" s="170"/>
+      <c r="T3" s="219" t="s">
+        <v>166</v>
+      </c>
+      <c r="U3" s="208"/>
+      <c r="V3" s="208" t="s">
+        <v>149</v>
+      </c>
+      <c r="W3" s="208"/>
+      <c r="X3" s="208" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y3" s="209"/>
+    </row>
+    <row r="4" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="211" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="225" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="226"/>
+      <c r="D4" s="226"/>
+      <c r="E4" s="226"/>
+      <c r="F4" s="226"/>
+      <c r="G4" s="227"/>
+      <c r="H4" s="171" t="s">
+        <v>210</v>
+      </c>
+      <c r="I4" s="172"/>
+      <c r="J4" s="172"/>
+      <c r="K4" s="172"/>
+      <c r="L4" s="172"/>
+      <c r="M4" s="173"/>
+      <c r="N4" s="171" t="s">
+        <v>200</v>
+      </c>
+      <c r="O4" s="175"/>
+      <c r="P4" s="175"/>
+      <c r="Q4" s="175"/>
+      <c r="R4" s="175"/>
+      <c r="S4" s="178"/>
+      <c r="T4" s="204" t="s">
+        <v>14</v>
+      </c>
+      <c r="U4" s="184"/>
+      <c r="V4" s="184"/>
+      <c r="W4" s="184"/>
+      <c r="X4" s="202" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y4" s="185"/>
+    </row>
+    <row r="5" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="211"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="226"/>
+      <c r="D5" s="226"/>
+      <c r="E5" s="226"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="227"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="172"/>
+      <c r="J5" s="172"/>
+      <c r="K5" s="172"/>
+      <c r="L5" s="172"/>
+      <c r="M5" s="173"/>
+      <c r="N5" s="174"/>
+      <c r="O5" s="175"/>
+      <c r="P5" s="175"/>
+      <c r="Q5" s="175"/>
+      <c r="R5" s="175"/>
+      <c r="S5" s="178"/>
+      <c r="T5" s="200" t="s">
+        <v>164</v>
+      </c>
+      <c r="U5" s="184"/>
+      <c r="V5" s="184"/>
+      <c r="W5" s="184"/>
+      <c r="X5" s="184" t="s">
+        <v>165</v>
+      </c>
+      <c r="Y5" s="185"/>
+    </row>
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="211" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" s="171" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" s="172"/>
+      <c r="D6" s="172"/>
+      <c r="E6" s="172"/>
+      <c r="F6" s="172"/>
+      <c r="G6" s="173"/>
+      <c r="H6" s="189" t="s">
+        <v>322</v>
+      </c>
+      <c r="I6" s="238"/>
+      <c r="J6" s="238"/>
+      <c r="K6" s="238"/>
+      <c r="L6" s="238"/>
+      <c r="M6" s="228"/>
+      <c r="N6" s="171" t="s">
         <v>321</v>
       </c>
-      <c r="C3" s="231"/>
-      <c r="D3" s="170" t="s">
+      <c r="O6" s="240"/>
+      <c r="P6" s="240"/>
+      <c r="Q6" s="240"/>
+      <c r="R6" s="240"/>
+      <c r="S6" s="173"/>
+      <c r="T6" s="189" t="s">
         <v>322</v>
       </c>
-      <c r="E3" s="170"/>
-      <c r="F3" s="170" t="s">
-        <v>326</v>
-      </c>
-      <c r="G3" s="171"/>
-      <c r="H3" s="216" t="s">
-        <v>212</v>
-      </c>
-      <c r="I3" s="170"/>
-      <c r="J3" s="170" t="s">
-        <v>209</v>
-      </c>
-      <c r="K3" s="170"/>
-      <c r="L3" s="170" t="s">
-        <v>210</v>
-      </c>
-      <c r="M3" s="171"/>
-      <c r="N3" s="216" t="s">
-        <v>323</v>
-      </c>
-      <c r="O3" s="170"/>
-      <c r="P3" s="170" t="s">
-        <v>324</v>
-      </c>
-      <c r="Q3" s="170"/>
-      <c r="R3" s="170" t="s">
-        <v>325</v>
-      </c>
-      <c r="S3" s="171"/>
-      <c r="T3" s="220" t="s">
-        <v>166</v>
-      </c>
-      <c r="U3" s="209"/>
-      <c r="V3" s="209" t="s">
-        <v>149</v>
-      </c>
-      <c r="W3" s="209"/>
-      <c r="X3" s="209" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y3" s="210"/>
-    </row>
-    <row r="4" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="212" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="226" t="s">
-        <v>223</v>
-      </c>
-      <c r="C4" s="227"/>
-      <c r="D4" s="227"/>
-      <c r="E4" s="227"/>
-      <c r="F4" s="227"/>
-      <c r="G4" s="228"/>
-      <c r="H4" s="172" t="s">
-        <v>215</v>
-      </c>
-      <c r="I4" s="173"/>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
-      <c r="L4" s="173"/>
-      <c r="M4" s="174"/>
-      <c r="N4" s="172" t="s">
-        <v>205</v>
-      </c>
-      <c r="O4" s="176"/>
-      <c r="P4" s="176"/>
-      <c r="Q4" s="176"/>
-      <c r="R4" s="176"/>
-      <c r="S4" s="179"/>
-      <c r="T4" s="205" t="s">
-        <v>14</v>
-      </c>
-      <c r="U4" s="185"/>
-      <c r="V4" s="185"/>
-      <c r="W4" s="185"/>
-      <c r="X4" s="203" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y4" s="186"/>
-    </row>
-    <row r="5" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="212"/>
-      <c r="B5" s="226"/>
-      <c r="C5" s="227"/>
-      <c r="D5" s="227"/>
-      <c r="E5" s="227"/>
-      <c r="F5" s="227"/>
-      <c r="G5" s="228"/>
-      <c r="H5" s="172"/>
-      <c r="I5" s="173"/>
-      <c r="J5" s="173"/>
-      <c r="K5" s="173"/>
-      <c r="L5" s="173"/>
-      <c r="M5" s="174"/>
-      <c r="N5" s="175"/>
-      <c r="O5" s="176"/>
-      <c r="P5" s="176"/>
-      <c r="Q5" s="176"/>
-      <c r="R5" s="176"/>
-      <c r="S5" s="179"/>
-      <c r="T5" s="201" t="s">
-        <v>164</v>
-      </c>
-      <c r="U5" s="185"/>
-      <c r="V5" s="185"/>
-      <c r="W5" s="185"/>
-      <c r="X5" s="185" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y5" s="186"/>
-    </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="212" t="s">
-        <v>204</v>
-      </c>
-      <c r="B6" s="172" t="s">
-        <v>224</v>
-      </c>
-      <c r="C6" s="173"/>
-      <c r="D6" s="173"/>
-      <c r="E6" s="173"/>
-      <c r="F6" s="173"/>
-      <c r="G6" s="174"/>
-      <c r="H6" s="190" t="s">
-        <v>329</v>
-      </c>
-      <c r="I6" s="239"/>
-      <c r="J6" s="239"/>
-      <c r="K6" s="239"/>
-      <c r="L6" s="239"/>
-      <c r="M6" s="229"/>
-      <c r="N6" s="172" t="s">
-        <v>328</v>
-      </c>
-      <c r="O6" s="241"/>
-      <c r="P6" s="241"/>
-      <c r="Q6" s="241"/>
-      <c r="R6" s="241"/>
-      <c r="S6" s="174"/>
-      <c r="T6" s="190" t="s">
-        <v>329</v>
-      </c>
-      <c r="U6" s="239"/>
-      <c r="V6" s="239"/>
-      <c r="W6" s="239"/>
-      <c r="X6" s="239"/>
-      <c r="Y6" s="229"/>
-      <c r="Z6" s="41"/>
+      <c r="U6" s="238"/>
+      <c r="V6" s="238"/>
+      <c r="W6" s="238"/>
+      <c r="X6" s="238"/>
+      <c r="Y6" s="228"/>
+      <c r="Z6" s="40"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212"/>
-      <c r="B7" s="172"/>
-      <c r="C7" s="173"/>
-      <c r="D7" s="173"/>
-      <c r="E7" s="173"/>
-      <c r="F7" s="173"/>
-      <c r="G7" s="174"/>
-      <c r="H7" s="190"/>
-      <c r="I7" s="239"/>
-      <c r="J7" s="239"/>
-      <c r="K7" s="239"/>
-      <c r="L7" s="239"/>
-      <c r="M7" s="229"/>
-      <c r="N7" s="172"/>
-      <c r="O7" s="241"/>
-      <c r="P7" s="241"/>
-      <c r="Q7" s="241"/>
-      <c r="R7" s="241"/>
-      <c r="S7" s="174"/>
-      <c r="T7" s="190"/>
-      <c r="U7" s="239"/>
-      <c r="V7" s="239"/>
-      <c r="W7" s="239"/>
-      <c r="X7" s="239"/>
-      <c r="Y7" s="229"/>
+      <c r="A7" s="211"/>
+      <c r="B7" s="171"/>
+      <c r="C7" s="172"/>
+      <c r="D7" s="172"/>
+      <c r="E7" s="172"/>
+      <c r="F7" s="172"/>
+      <c r="G7" s="173"/>
+      <c r="H7" s="189"/>
+      <c r="I7" s="238"/>
+      <c r="J7" s="238"/>
+      <c r="K7" s="238"/>
+      <c r="L7" s="238"/>
+      <c r="M7" s="228"/>
+      <c r="N7" s="171"/>
+      <c r="O7" s="240"/>
+      <c r="P7" s="240"/>
+      <c r="Q7" s="240"/>
+      <c r="R7" s="240"/>
+      <c r="S7" s="173"/>
+      <c r="T7" s="189"/>
+      <c r="U7" s="238"/>
+      <c r="V7" s="238"/>
+      <c r="W7" s="238"/>
+      <c r="X7" s="238"/>
+      <c r="Y7" s="228"/>
     </row>
     <row r="8" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="171" t="s">
+        <v>220</v>
+      </c>
+      <c r="C8" s="172"/>
+      <c r="D8" s="172"/>
+      <c r="E8" s="172"/>
+      <c r="F8" s="172"/>
+      <c r="G8" s="173"/>
+      <c r="H8" s="171" t="s">
         <v>179</v>
       </c>
-      <c r="B8" s="172" t="s">
-        <v>225</v>
-      </c>
-      <c r="C8" s="173"/>
-      <c r="D8" s="173"/>
-      <c r="E8" s="173"/>
-      <c r="F8" s="173"/>
-      <c r="G8" s="174"/>
-      <c r="H8" s="172" t="s">
-        <v>180</v>
-      </c>
-      <c r="I8" s="173"/>
-      <c r="J8" s="173"/>
-      <c r="K8" s="173"/>
-      <c r="L8" s="173"/>
-      <c r="M8" s="174"/>
-      <c r="N8" s="172" t="s">
-        <v>211</v>
-      </c>
-      <c r="O8" s="173"/>
-      <c r="P8" s="173"/>
-      <c r="Q8" s="173"/>
-      <c r="R8" s="173"/>
-      <c r="S8" s="174"/>
-      <c r="T8" s="184" t="s">
-        <v>180</v>
-      </c>
-      <c r="U8" s="185"/>
-      <c r="V8" s="185"/>
-      <c r="W8" s="185"/>
-      <c r="X8" s="185"/>
-      <c r="Y8" s="186"/>
+      <c r="I8" s="172"/>
+      <c r="J8" s="172"/>
+      <c r="K8" s="172"/>
+      <c r="L8" s="172"/>
+      <c r="M8" s="173"/>
+      <c r="N8" s="171" t="s">
+        <v>206</v>
+      </c>
+      <c r="O8" s="172"/>
+      <c r="P8" s="172"/>
+      <c r="Q8" s="172"/>
+      <c r="R8" s="172"/>
+      <c r="S8" s="173"/>
+      <c r="T8" s="183" t="s">
+        <v>179</v>
+      </c>
+      <c r="U8" s="184"/>
+      <c r="V8" s="184"/>
+      <c r="W8" s="184"/>
+      <c r="X8" s="184"/>
+      <c r="Y8" s="185"/>
     </row>
     <row r="9" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B9" s="173" t="s">
-        <v>225</v>
-      </c>
-      <c r="C9" s="173"/>
-      <c r="D9" s="173"/>
-      <c r="E9" s="173"/>
-      <c r="F9" s="173"/>
-      <c r="G9" s="174"/>
-      <c r="H9" s="172" t="s">
+      <c r="B9" s="172" t="s">
+        <v>220</v>
+      </c>
+      <c r="C9" s="172"/>
+      <c r="D9" s="172"/>
+      <c r="E9" s="172"/>
+      <c r="F9" s="172"/>
+      <c r="G9" s="173"/>
+      <c r="H9" s="171" t="s">
         <v>152</v>
       </c>
-      <c r="I9" s="173"/>
-      <c r="J9" s="173" t="s">
+      <c r="I9" s="172"/>
+      <c r="J9" s="172" t="s">
         <v>154</v>
       </c>
-      <c r="K9" s="173"/>
-      <c r="L9" s="173" t="s">
+      <c r="K9" s="172"/>
+      <c r="L9" s="172" t="s">
         <v>153</v>
       </c>
-      <c r="M9" s="174"/>
-      <c r="N9" s="172" t="s">
+      <c r="M9" s="173"/>
+      <c r="N9" s="171" t="s">
+        <v>182</v>
+      </c>
+      <c r="O9" s="172"/>
+      <c r="P9" s="172" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q9" s="172"/>
+      <c r="R9" s="172" t="s">
         <v>183</v>
       </c>
-      <c r="O9" s="173"/>
-      <c r="P9" s="173" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q9" s="173"/>
-      <c r="R9" s="173" t="s">
+      <c r="S9" s="173"/>
+      <c r="T9" s="183" t="s">
+        <v>152</v>
+      </c>
+      <c r="U9" s="184"/>
+      <c r="V9" s="184" t="s">
+        <v>154</v>
+      </c>
+      <c r="W9" s="184"/>
+      <c r="X9" s="184" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y9" s="185"/>
+    </row>
+    <row r="10" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="182" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="190" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="190"/>
+      <c r="D10" s="190"/>
+      <c r="E10" s="190"/>
+      <c r="F10" s="190"/>
+      <c r="G10" s="228"/>
+      <c r="H10" s="171" t="s">
+        <v>325</v>
+      </c>
+      <c r="I10" s="240"/>
+      <c r="J10" s="240"/>
+      <c r="K10" s="240"/>
+      <c r="L10" s="240"/>
+      <c r="M10" s="173" t="s">
+        <v>324</v>
+      </c>
+      <c r="N10" s="174" t="s">
+        <v>195</v>
+      </c>
+      <c r="O10" s="172"/>
+      <c r="P10" s="172"/>
+      <c r="Q10" s="202" t="s">
+        <v>197</v>
+      </c>
+      <c r="R10" s="140"/>
+      <c r="S10" s="141"/>
+      <c r="T10" s="189" t="s">
+        <v>326</v>
+      </c>
+      <c r="U10" s="238"/>
+      <c r="V10" s="238"/>
+      <c r="W10" s="238"/>
+      <c r="X10" s="238"/>
+      <c r="Y10" s="191" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="182"/>
+      <c r="B11" s="190"/>
+      <c r="C11" s="190"/>
+      <c r="D11" s="190"/>
+      <c r="E11" s="190"/>
+      <c r="F11" s="190"/>
+      <c r="G11" s="228"/>
+      <c r="H11" s="171"/>
+      <c r="I11" s="240"/>
+      <c r="J11" s="240"/>
+      <c r="K11" s="240"/>
+      <c r="L11" s="240"/>
+      <c r="M11" s="173"/>
+      <c r="N11" s="171" t="s">
+        <v>196</v>
+      </c>
+      <c r="O11" s="172"/>
+      <c r="P11" s="172"/>
+      <c r="Q11" s="172" t="s">
+        <v>198</v>
+      </c>
+      <c r="R11" s="172"/>
+      <c r="S11" s="173"/>
+      <c r="T11" s="189"/>
+      <c r="U11" s="238"/>
+      <c r="V11" s="238"/>
+      <c r="W11" s="238"/>
+      <c r="X11" s="238"/>
+      <c r="Y11" s="191"/>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="181" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="187" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12" s="188"/>
+      <c r="D12" s="188" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="188"/>
+      <c r="F12" s="188" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="224"/>
+      <c r="H12" s="174" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="175"/>
+      <c r="J12" s="175" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" s="175"/>
+      <c r="L12" s="175" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="178"/>
+      <c r="N12" s="174" t="s">
+        <v>14</v>
+      </c>
+      <c r="O12" s="175"/>
+      <c r="P12" s="175" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q12" s="172"/>
+      <c r="R12" s="175" t="s">
+        <v>15</v>
+      </c>
+      <c r="S12" s="178"/>
+      <c r="T12" s="204" t="s">
+        <v>14</v>
+      </c>
+      <c r="U12" s="202"/>
+      <c r="V12" s="202" t="s">
+        <v>55</v>
+      </c>
+      <c r="W12" s="202"/>
+      <c r="X12" s="202" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y12" s="203"/>
+    </row>
+    <row r="13" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="181"/>
+      <c r="B13" s="171" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" s="172"/>
+      <c r="D13" s="172" t="s">
+        <v>212</v>
+      </c>
+      <c r="E13" s="172"/>
+      <c r="F13" s="172" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="173"/>
+      <c r="H13" s="171" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="172"/>
+      <c r="J13" s="172" t="s">
+        <v>92</v>
+      </c>
+      <c r="K13" s="172"/>
+      <c r="L13" s="172" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="173"/>
+      <c r="N13" s="171" t="s">
+        <v>186</v>
+      </c>
+      <c r="O13" s="172"/>
+      <c r="P13" s="172" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q13" s="172"/>
+      <c r="R13" s="172" t="s">
+        <v>56</v>
+      </c>
+      <c r="S13" s="173"/>
+      <c r="T13" s="200" t="s">
+        <v>60</v>
+      </c>
+      <c r="U13" s="184"/>
+      <c r="V13" s="184" t="s">
+        <v>92</v>
+      </c>
+      <c r="W13" s="184"/>
+      <c r="X13" s="184" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y13" s="185"/>
+    </row>
+    <row r="14" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="181" t="s">
         <v>184</v>
       </c>
-      <c r="S9" s="174"/>
-      <c r="T9" s="184" t="s">
-        <v>152</v>
-      </c>
-      <c r="U9" s="185"/>
-      <c r="V9" s="185" t="s">
-        <v>154</v>
-      </c>
-      <c r="W9" s="185"/>
-      <c r="X9" s="185" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y9" s="186"/>
-    </row>
-    <row r="10" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="183" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="191" t="s">
-        <v>225</v>
-      </c>
-      <c r="C10" s="191"/>
-      <c r="D10" s="191"/>
-      <c r="E10" s="191"/>
-      <c r="F10" s="191"/>
-      <c r="G10" s="229"/>
-      <c r="H10" s="172" t="s">
+      <c r="B14" s="171" t="s">
+        <v>220</v>
+      </c>
+      <c r="C14" s="172"/>
+      <c r="D14" s="172"/>
+      <c r="E14" s="172"/>
+      <c r="F14" s="172"/>
+      <c r="G14" s="173"/>
+      <c r="H14" s="171" t="s">
+        <v>140</v>
+      </c>
+      <c r="I14" s="172"/>
+      <c r="J14" s="172"/>
+      <c r="K14" s="172"/>
+      <c r="L14" s="172"/>
+      <c r="M14" s="173"/>
+      <c r="N14" s="174" t="s">
+        <v>14</v>
+      </c>
+      <c r="O14" s="172"/>
+      <c r="P14" s="175" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q14" s="172"/>
+      <c r="R14" s="175" t="s">
+        <v>15</v>
+      </c>
+      <c r="S14" s="173"/>
+      <c r="T14" s="195" t="s">
+        <v>140</v>
+      </c>
+      <c r="U14" s="196"/>
+      <c r="V14" s="196"/>
+      <c r="W14" s="196"/>
+      <c r="X14" s="196"/>
+      <c r="Y14" s="197"/>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="181"/>
+      <c r="B15" s="171"/>
+      <c r="C15" s="172"/>
+      <c r="D15" s="172"/>
+      <c r="E15" s="172"/>
+      <c r="F15" s="172"/>
+      <c r="G15" s="173"/>
+      <c r="H15" s="171"/>
+      <c r="I15" s="172"/>
+      <c r="J15" s="172"/>
+      <c r="K15" s="172"/>
+      <c r="L15" s="172"/>
+      <c r="M15" s="173"/>
+      <c r="N15" s="171" t="s">
+        <v>185</v>
+      </c>
+      <c r="O15" s="172"/>
+      <c r="P15" s="172" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q15" s="172"/>
+      <c r="R15" s="172" t="s">
+        <v>56</v>
+      </c>
+      <c r="S15" s="173"/>
+      <c r="T15" s="195"/>
+      <c r="U15" s="196"/>
+      <c r="V15" s="196"/>
+      <c r="W15" s="196"/>
+      <c r="X15" s="196"/>
+      <c r="Y15" s="197"/>
+    </row>
+    <row r="16" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="236" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="204" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="202"/>
+      <c r="D16" s="202"/>
+      <c r="E16" s="202" t="s">
+        <v>170</v>
+      </c>
+      <c r="F16" s="205"/>
+      <c r="G16" s="206"/>
+      <c r="H16" s="174" t="s">
+        <v>327</v>
+      </c>
+      <c r="I16" s="239"/>
+      <c r="J16" s="239"/>
+      <c r="K16" s="175" t="s">
+        <v>329</v>
+      </c>
+      <c r="L16" s="175"/>
+      <c r="M16" s="178"/>
+      <c r="N16" s="174" t="s">
+        <v>330</v>
+      </c>
+      <c r="O16" s="175"/>
+      <c r="P16" s="175"/>
+      <c r="Q16" s="174" t="s">
+        <v>331</v>
+      </c>
+      <c r="R16" s="175"/>
+      <c r="S16" s="175"/>
+      <c r="T16" s="204" t="s">
+        <v>168</v>
+      </c>
+      <c r="U16" s="202"/>
+      <c r="V16" s="202"/>
+      <c r="W16" s="202" t="s">
+        <v>328</v>
+      </c>
+      <c r="X16" s="205"/>
+      <c r="Y16" s="206"/>
+    </row>
+    <row r="17" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="236"/>
+      <c r="B17" s="183" t="s">
+        <v>221</v>
+      </c>
+      <c r="C17" s="184"/>
+      <c r="D17" s="184"/>
+      <c r="E17" s="184" t="s">
+        <v>171</v>
+      </c>
+      <c r="F17" s="184"/>
+      <c r="G17" s="185"/>
+      <c r="H17" s="171" t="s">
+        <v>169</v>
+      </c>
+      <c r="I17" s="240"/>
+      <c r="J17" s="240"/>
+      <c r="K17" s="172" t="s">
+        <v>171</v>
+      </c>
+      <c r="L17" s="172"/>
+      <c r="M17" s="173"/>
+      <c r="N17" s="171" t="s">
+        <v>171</v>
+      </c>
+      <c r="O17" s="172"/>
+      <c r="P17" s="172"/>
+      <c r="Q17" s="171" t="s">
         <v>332</v>
       </c>
-      <c r="I10" s="241"/>
-      <c r="J10" s="241"/>
-      <c r="K10" s="241"/>
-      <c r="L10" s="241"/>
-      <c r="M10" s="174" t="s">
-        <v>331</v>
-      </c>
-      <c r="N10" s="175" t="s">
-        <v>196</v>
-      </c>
-      <c r="O10" s="173"/>
-      <c r="P10" s="173"/>
-      <c r="Q10" s="203" t="s">
-        <v>198</v>
-      </c>
-      <c r="R10" s="141"/>
-      <c r="S10" s="142"/>
-      <c r="T10" s="190" t="s">
-        <v>333</v>
-      </c>
-      <c r="U10" s="239"/>
-      <c r="V10" s="239"/>
-      <c r="W10" s="239"/>
-      <c r="X10" s="239"/>
-      <c r="Y10" s="192" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="183"/>
-      <c r="B11" s="191"/>
-      <c r="C11" s="191"/>
-      <c r="D11" s="191"/>
-      <c r="E11" s="191"/>
-      <c r="F11" s="191"/>
-      <c r="G11" s="229"/>
-      <c r="H11" s="172"/>
-      <c r="I11" s="241"/>
-      <c r="J11" s="241"/>
-      <c r="K11" s="241"/>
-      <c r="L11" s="241"/>
-      <c r="M11" s="174"/>
-      <c r="N11" s="172" t="s">
-        <v>197</v>
-      </c>
-      <c r="O11" s="173"/>
-      <c r="P11" s="173"/>
-      <c r="Q11" s="173" t="s">
-        <v>199</v>
-      </c>
-      <c r="R11" s="173"/>
-      <c r="S11" s="174"/>
-      <c r="T11" s="190"/>
-      <c r="U11" s="239"/>
-      <c r="V11" s="239"/>
-      <c r="W11" s="239"/>
-      <c r="X11" s="239"/>
-      <c r="Y11" s="192"/>
-    </row>
-    <row r="12" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="182" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" s="188" t="s">
-        <v>218</v>
-      </c>
-      <c r="C12" s="189"/>
-      <c r="D12" s="189" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="189"/>
-      <c r="F12" s="189" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="225"/>
-      <c r="H12" s="175" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="176"/>
-      <c r="J12" s="176" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="176"/>
-      <c r="L12" s="176" t="s">
-        <v>15</v>
-      </c>
-      <c r="M12" s="179"/>
-      <c r="N12" s="175" t="s">
-        <v>14</v>
-      </c>
-      <c r="O12" s="176"/>
-      <c r="P12" s="176" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q12" s="173"/>
-      <c r="R12" s="176" t="s">
-        <v>15</v>
-      </c>
-      <c r="S12" s="179"/>
-      <c r="T12" s="205" t="s">
-        <v>14</v>
-      </c>
-      <c r="U12" s="203"/>
-      <c r="V12" s="203" t="s">
-        <v>55</v>
-      </c>
-      <c r="W12" s="203"/>
-      <c r="X12" s="203" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y12" s="204"/>
-    </row>
-    <row r="13" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="182"/>
-      <c r="B13" s="172" t="s">
+      <c r="R17" s="172"/>
+      <c r="S17" s="172"/>
+      <c r="T17" s="183" t="s">
+        <v>169</v>
+      </c>
+      <c r="U17" s="184"/>
+      <c r="V17" s="184"/>
+      <c r="W17" s="184" t="s">
+        <v>171</v>
+      </c>
+      <c r="X17" s="184"/>
+      <c r="Y17" s="185"/>
+    </row>
+    <row r="18" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="236" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="174" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" s="175"/>
+      <c r="D18" s="175"/>
+      <c r="E18" s="175" t="s">
+        <v>215</v>
+      </c>
+      <c r="F18" s="175"/>
+      <c r="G18" s="178"/>
+      <c r="H18" s="204" t="s">
+        <v>208</v>
+      </c>
+      <c r="I18" s="202"/>
+      <c r="J18" s="202"/>
+      <c r="K18" s="202"/>
+      <c r="L18" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="M18" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="N18" s="187" t="s">
+        <v>194</v>
+      </c>
+      <c r="O18" s="188"/>
+      <c r="P18" s="188"/>
+      <c r="Q18" s="188"/>
+      <c r="R18" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="S18" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="T18" s="204" t="s">
+        <v>161</v>
+      </c>
+      <c r="U18" s="202"/>
+      <c r="V18" s="202"/>
+      <c r="W18" s="202"/>
+      <c r="X18" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y18" s="37" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="236"/>
+      <c r="B19" s="171" t="s">
         <v>216</v>
       </c>
-      <c r="C13" s="173"/>
-      <c r="D13" s="173" t="s">
+      <c r="C19" s="172"/>
+      <c r="D19" s="172"/>
+      <c r="E19" s="172" t="s">
         <v>217</v>
       </c>
-      <c r="E13" s="173"/>
-      <c r="F13" s="173" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="174"/>
-      <c r="H13" s="172" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13" s="173"/>
-      <c r="J13" s="173" t="s">
-        <v>92</v>
-      </c>
-      <c r="K13" s="173"/>
-      <c r="L13" s="173" t="s">
-        <v>56</v>
-      </c>
-      <c r="M13" s="174"/>
-      <c r="N13" s="172" t="s">
-        <v>187</v>
-      </c>
-      <c r="O13" s="173"/>
-      <c r="P13" s="173" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q13" s="173"/>
-      <c r="R13" s="173" t="s">
-        <v>56</v>
-      </c>
-      <c r="S13" s="174"/>
-      <c r="T13" s="201" t="s">
-        <v>60</v>
-      </c>
-      <c r="U13" s="185"/>
-      <c r="V13" s="185" t="s">
-        <v>92</v>
-      </c>
-      <c r="W13" s="185"/>
-      <c r="X13" s="185" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y13" s="186"/>
-    </row>
-    <row r="14" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="182" t="s">
-        <v>185</v>
-      </c>
-      <c r="B14" s="172" t="s">
-        <v>225</v>
-      </c>
-      <c r="C14" s="173"/>
-      <c r="D14" s="173"/>
-      <c r="E14" s="173"/>
-      <c r="F14" s="173"/>
-      <c r="G14" s="174"/>
-      <c r="H14" s="172" t="s">
-        <v>140</v>
-      </c>
-      <c r="I14" s="173"/>
-      <c r="J14" s="173"/>
-      <c r="K14" s="173"/>
-      <c r="L14" s="173"/>
-      <c r="M14" s="174"/>
-      <c r="N14" s="175" t="s">
-        <v>14</v>
-      </c>
-      <c r="O14" s="173"/>
-      <c r="P14" s="176" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q14" s="173"/>
-      <c r="R14" s="176" t="s">
-        <v>15</v>
-      </c>
-      <c r="S14" s="174"/>
-      <c r="T14" s="196" t="s">
-        <v>140</v>
-      </c>
-      <c r="U14" s="197"/>
-      <c r="V14" s="197"/>
-      <c r="W14" s="197"/>
-      <c r="X14" s="197"/>
-      <c r="Y14" s="198"/>
-    </row>
-    <row r="15" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="182"/>
-      <c r="B15" s="172"/>
-      <c r="C15" s="173"/>
-      <c r="D15" s="173"/>
-      <c r="E15" s="173"/>
-      <c r="F15" s="173"/>
-      <c r="G15" s="174"/>
-      <c r="H15" s="172"/>
-      <c r="I15" s="173"/>
-      <c r="J15" s="173"/>
-      <c r="K15" s="173"/>
-      <c r="L15" s="173"/>
-      <c r="M15" s="174"/>
-      <c r="N15" s="172" t="s">
-        <v>186</v>
-      </c>
-      <c r="O15" s="173"/>
-      <c r="P15" s="173" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q15" s="173"/>
-      <c r="R15" s="173" t="s">
-        <v>56</v>
-      </c>
-      <c r="S15" s="174"/>
-      <c r="T15" s="196"/>
-      <c r="U15" s="197"/>
-      <c r="V15" s="197"/>
-      <c r="W15" s="197"/>
-      <c r="X15" s="197"/>
-      <c r="Y15" s="198"/>
-    </row>
-    <row r="16" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="237" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="205" t="s">
-        <v>168</v>
-      </c>
-      <c r="C16" s="203"/>
-      <c r="D16" s="203"/>
-      <c r="E16" s="203" t="s">
-        <v>170</v>
-      </c>
-      <c r="F16" s="206"/>
-      <c r="G16" s="207"/>
-      <c r="H16" s="175" t="s">
-        <v>334</v>
-      </c>
-      <c r="I16" s="240"/>
-      <c r="J16" s="240"/>
-      <c r="K16" s="176" t="s">
-        <v>336</v>
-      </c>
-      <c r="L16" s="176"/>
-      <c r="M16" s="179"/>
-      <c r="N16" s="175" t="s">
-        <v>200</v>
-      </c>
-      <c r="O16" s="176"/>
-      <c r="P16" s="176"/>
-      <c r="Q16" s="176" t="s">
-        <v>202</v>
-      </c>
-      <c r="R16" s="176"/>
-      <c r="S16" s="179"/>
-      <c r="T16" s="205" t="s">
-        <v>168</v>
-      </c>
-      <c r="U16" s="203"/>
-      <c r="V16" s="203"/>
-      <c r="W16" s="203" t="s">
-        <v>335</v>
-      </c>
-      <c r="X16" s="206"/>
-      <c r="Y16" s="207"/>
-    </row>
-    <row r="17" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="237"/>
-      <c r="B17" s="184" t="s">
-        <v>226</v>
-      </c>
-      <c r="C17" s="185"/>
-      <c r="D17" s="185"/>
-      <c r="E17" s="185" t="s">
-        <v>171</v>
-      </c>
-      <c r="F17" s="185"/>
-      <c r="G17" s="186"/>
-      <c r="H17" s="172" t="s">
-        <v>169</v>
-      </c>
-      <c r="I17" s="241"/>
-      <c r="J17" s="241"/>
-      <c r="K17" s="173" t="s">
-        <v>171</v>
-      </c>
-      <c r="L17" s="173"/>
-      <c r="M17" s="174"/>
-      <c r="N17" s="172" t="s">
-        <v>201</v>
-      </c>
-      <c r="O17" s="173"/>
-      <c r="P17" s="173"/>
-      <c r="Q17" s="173" t="s">
-        <v>203</v>
-      </c>
-      <c r="R17" s="173"/>
-      <c r="S17" s="174"/>
-      <c r="T17" s="184" t="s">
-        <v>169</v>
-      </c>
-      <c r="U17" s="185"/>
-      <c r="V17" s="185"/>
-      <c r="W17" s="185" t="s">
-        <v>171</v>
-      </c>
-      <c r="X17" s="185"/>
-      <c r="Y17" s="186"/>
-    </row>
-    <row r="18" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="237" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="175" t="s">
-        <v>219</v>
-      </c>
-      <c r="C18" s="176"/>
-      <c r="D18" s="176"/>
-      <c r="E18" s="176" t="s">
-        <v>220</v>
-      </c>
-      <c r="F18" s="176"/>
-      <c r="G18" s="179"/>
-      <c r="H18" s="205" t="s">
-        <v>213</v>
-      </c>
-      <c r="I18" s="203"/>
-      <c r="J18" s="203"/>
-      <c r="K18" s="203"/>
-      <c r="L18" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="M18" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="N18" s="188" t="s">
-        <v>195</v>
-      </c>
-      <c r="O18" s="189"/>
-      <c r="P18" s="189"/>
-      <c r="Q18" s="189"/>
-      <c r="R18" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="S18" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="T18" s="205" t="s">
-        <v>161</v>
-      </c>
-      <c r="U18" s="203"/>
-      <c r="V18" s="203"/>
-      <c r="W18" s="203"/>
-      <c r="X18" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y18" s="38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="237"/>
-      <c r="B19" s="172" t="s">
-        <v>221</v>
-      </c>
-      <c r="C19" s="173"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="173" t="s">
-        <v>222</v>
-      </c>
-      <c r="F19" s="173"/>
-      <c r="G19" s="174"/>
-      <c r="H19" s="184" t="s">
-        <v>214</v>
-      </c>
-      <c r="I19" s="185"/>
-      <c r="J19" s="185"/>
-      <c r="K19" s="185"/>
+      <c r="F19" s="172"/>
+      <c r="G19" s="173"/>
+      <c r="H19" s="183" t="s">
+        <v>209</v>
+      </c>
+      <c r="I19" s="184"/>
+      <c r="J19" s="184"/>
+      <c r="K19" s="184"/>
       <c r="L19" s="27" t="s">
         <v>160</v>
       </c>
       <c r="M19" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="N19" s="50" t="s">
+      <c r="N19" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="O19" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="O19" s="52" t="s">
+      <c r="P19" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="P19" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q19" s="31"/>
-      <c r="R19" s="31" t="s">
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="S19" s="35" t="s">
         <v>188</v>
       </c>
-      <c r="S19" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="T19" s="184" t="s">
-        <v>181</v>
-      </c>
-      <c r="U19" s="185"/>
-      <c r="V19" s="185"/>
-      <c r="W19" s="185"/>
+      <c r="T19" s="183" t="s">
+        <v>180</v>
+      </c>
+      <c r="U19" s="184"/>
+      <c r="V19" s="184"/>
+      <c r="W19" s="184"/>
       <c r="X19" s="27" t="s">
         <v>160</v>
       </c>
       <c r="Y19" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="Z19" s="41"/>
+      <c r="Z19" s="40"/>
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="182" t="s">
+      <c r="A20" s="181" t="s">
         <v>84</v>
       </c>
-      <c r="B20" s="172" t="s">
+      <c r="B20" s="171" t="s">
+        <v>333</v>
+      </c>
+      <c r="C20" s="240"/>
+      <c r="D20" s="240"/>
+      <c r="E20" s="172" t="s">
+        <v>334</v>
+      </c>
+      <c r="F20" s="172"/>
+      <c r="G20" s="173"/>
+      <c r="H20" s="171" t="s">
+        <v>336</v>
+      </c>
+      <c r="I20" s="240"/>
+      <c r="J20" s="240"/>
+      <c r="K20" s="240"/>
+      <c r="L20" s="172" t="s">
+        <v>335</v>
+      </c>
+      <c r="M20" s="173" t="s">
+        <v>337</v>
+      </c>
+      <c r="N20" s="171" t="s">
+        <v>340</v>
+      </c>
+      <c r="O20" s="240"/>
+      <c r="P20" s="240"/>
+      <c r="Q20" s="240"/>
+      <c r="R20" s="172" t="s">
+        <v>338</v>
+      </c>
+      <c r="S20" s="173" t="s">
+        <v>339</v>
+      </c>
+      <c r="T20" s="189" t="s">
+        <v>336</v>
+      </c>
+      <c r="U20" s="238"/>
+      <c r="V20" s="238"/>
+      <c r="W20" s="238"/>
+      <c r="X20" s="172" t="s">
+        <v>335</v>
+      </c>
+      <c r="Y20" s="173" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z20" s="40"/>
+    </row>
+    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="181"/>
+      <c r="B21" s="171"/>
+      <c r="C21" s="240"/>
+      <c r="D21" s="240"/>
+      <c r="E21" s="172"/>
+      <c r="F21" s="172"/>
+      <c r="G21" s="173"/>
+      <c r="H21" s="171"/>
+      <c r="I21" s="240"/>
+      <c r="J21" s="240"/>
+      <c r="K21" s="240"/>
+      <c r="L21" s="172"/>
+      <c r="M21" s="173"/>
+      <c r="N21" s="171"/>
+      <c r="O21" s="240"/>
+      <c r="P21" s="240"/>
+      <c r="Q21" s="240"/>
+      <c r="R21" s="172"/>
+      <c r="S21" s="173"/>
+      <c r="T21" s="189"/>
+      <c r="U21" s="238"/>
+      <c r="V21" s="238"/>
+      <c r="W21" s="238"/>
+      <c r="X21" s="172"/>
+      <c r="Y21" s="173"/>
+    </row>
+    <row r="22" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="211" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="204" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="202"/>
+      <c r="D22" s="202"/>
+      <c r="E22" s="202"/>
+      <c r="F22" s="202" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="235"/>
+      <c r="H22" s="204" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="202"/>
+      <c r="J22" s="202" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" s="202"/>
+      <c r="L22" s="202" t="s">
+        <v>15</v>
+      </c>
+      <c r="M22" s="185"/>
+      <c r="N22" s="174" t="s">
+        <v>14</v>
+      </c>
+      <c r="O22" s="172"/>
+      <c r="P22" s="172"/>
+      <c r="Q22" s="172"/>
+      <c r="R22" s="175" t="s">
+        <v>15</v>
+      </c>
+      <c r="S22" s="173"/>
+      <c r="T22" s="204" t="s">
+        <v>14</v>
+      </c>
+      <c r="U22" s="202"/>
+      <c r="V22" s="202" t="s">
+        <v>55</v>
+      </c>
+      <c r="W22" s="202"/>
+      <c r="X22" s="202" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y22" s="185"/>
+    </row>
+    <row r="23" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="211"/>
+      <c r="B23" s="200" t="s">
+        <v>222</v>
+      </c>
+      <c r="C23" s="201"/>
+      <c r="D23" s="201"/>
+      <c r="E23" s="201"/>
+      <c r="F23" s="201" t="s">
+        <v>157</v>
+      </c>
+      <c r="G23" s="234"/>
+      <c r="H23" s="200" t="s">
+        <v>155</v>
+      </c>
+      <c r="I23" s="201"/>
+      <c r="J23" s="201" t="s">
+        <v>156</v>
+      </c>
+      <c r="K23" s="184"/>
+      <c r="L23" s="201" t="s">
+        <v>157</v>
+      </c>
+      <c r="M23" s="185"/>
+      <c r="N23" s="176" t="s">
+        <v>155</v>
+      </c>
+      <c r="O23" s="172"/>
+      <c r="P23" s="172"/>
+      <c r="Q23" s="172"/>
+      <c r="R23" s="177" t="s">
+        <v>157</v>
+      </c>
+      <c r="S23" s="173"/>
+      <c r="T23" s="200" t="s">
+        <v>155</v>
+      </c>
+      <c r="U23" s="201"/>
+      <c r="V23" s="201" t="s">
+        <v>156</v>
+      </c>
+      <c r="W23" s="184"/>
+      <c r="X23" s="201" t="s">
+        <v>157</v>
+      </c>
+      <c r="Y23" s="185"/>
+    </row>
+    <row r="24" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="211" t="s">
+        <v>223</v>
+      </c>
+      <c r="B24" s="198" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="201"/>
+      <c r="D24" s="201"/>
+      <c r="E24" s="201"/>
+      <c r="F24" s="201"/>
+      <c r="G24" s="234"/>
+      <c r="H24" s="198" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="199"/>
+      <c r="J24" s="199"/>
+      <c r="K24" s="202" t="s">
+        <v>81</v>
+      </c>
+      <c r="L24" s="202"/>
+      <c r="M24" s="235"/>
+      <c r="N24" s="179" t="s">
+        <v>227</v>
+      </c>
+      <c r="O24" s="177"/>
+      <c r="P24" s="177"/>
+      <c r="Q24" s="175" t="s">
+        <v>81</v>
+      </c>
+      <c r="R24" s="172"/>
+      <c r="S24" s="173"/>
+      <c r="T24" s="198" t="s">
+        <v>161</v>
+      </c>
+      <c r="U24" s="201"/>
+      <c r="V24" s="201"/>
+      <c r="W24" s="202" t="s">
+        <v>81</v>
+      </c>
+      <c r="X24" s="184"/>
+      <c r="Y24" s="185"/>
+    </row>
+    <row r="25" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="211"/>
+      <c r="B25" s="200" t="s">
+        <v>224</v>
+      </c>
+      <c r="C25" s="201"/>
+      <c r="D25" s="201"/>
+      <c r="E25" s="201"/>
+      <c r="F25" s="201"/>
+      <c r="G25" s="234"/>
+      <c r="H25" s="200" t="s">
+        <v>225</v>
+      </c>
+      <c r="I25" s="201"/>
+      <c r="J25" s="201"/>
+      <c r="K25" s="201" t="s">
+        <v>226</v>
+      </c>
+      <c r="L25" s="201"/>
+      <c r="M25" s="234"/>
+      <c r="N25" s="176" t="s">
         <v>228</v>
       </c>
-      <c r="C20" s="173"/>
-      <c r="D20" s="173"/>
-      <c r="E20" s="173"/>
-      <c r="F20" s="173"/>
-      <c r="G20" s="174"/>
-      <c r="H20" s="172" t="s">
-        <v>228</v>
-      </c>
-      <c r="I20" s="173"/>
-      <c r="J20" s="173"/>
-      <c r="K20" s="173"/>
-      <c r="L20" s="173"/>
-      <c r="M20" s="174"/>
-      <c r="N20" s="172" t="s">
-        <v>228</v>
-      </c>
-      <c r="O20" s="176"/>
-      <c r="P20" s="176"/>
-      <c r="Q20" s="176"/>
-      <c r="R20" s="176"/>
-      <c r="S20" s="179"/>
-      <c r="T20" s="190" t="s">
-        <v>228</v>
-      </c>
-      <c r="U20" s="191"/>
-      <c r="V20" s="191"/>
-      <c r="W20" s="191"/>
-      <c r="X20" s="191"/>
-      <c r="Y20" s="192"/>
-      <c r="Z20" s="41"/>
-    </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="182"/>
-      <c r="B21" s="172"/>
-      <c r="C21" s="173"/>
-      <c r="D21" s="173"/>
-      <c r="E21" s="173"/>
-      <c r="F21" s="173"/>
-      <c r="G21" s="174"/>
-      <c r="H21" s="172"/>
-      <c r="I21" s="173"/>
-      <c r="J21" s="173"/>
-      <c r="K21" s="173"/>
-      <c r="L21" s="173"/>
-      <c r="M21" s="174"/>
-      <c r="N21" s="175"/>
-      <c r="O21" s="176"/>
-      <c r="P21" s="176"/>
-      <c r="Q21" s="176"/>
-      <c r="R21" s="176"/>
-      <c r="S21" s="179"/>
-      <c r="T21" s="190"/>
-      <c r="U21" s="191"/>
-      <c r="V21" s="191"/>
-      <c r="W21" s="191"/>
-      <c r="X21" s="191"/>
-      <c r="Y21" s="192"/>
-    </row>
-    <row r="22" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="212" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="205" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="203"/>
-      <c r="D22" s="203"/>
-      <c r="E22" s="203"/>
-      <c r="F22" s="203" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="236"/>
-      <c r="H22" s="205" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="203"/>
-      <c r="J22" s="203" t="s">
-        <v>55</v>
-      </c>
-      <c r="K22" s="203"/>
-      <c r="L22" s="203" t="s">
-        <v>15</v>
-      </c>
-      <c r="M22" s="186"/>
-      <c r="N22" s="175" t="s">
-        <v>14</v>
-      </c>
-      <c r="O22" s="173"/>
-      <c r="P22" s="173"/>
-      <c r="Q22" s="173"/>
-      <c r="R22" s="176" t="s">
-        <v>15</v>
-      </c>
-      <c r="S22" s="174"/>
-      <c r="T22" s="205" t="s">
-        <v>14</v>
-      </c>
-      <c r="U22" s="203"/>
-      <c r="V22" s="203" t="s">
-        <v>55</v>
-      </c>
-      <c r="W22" s="203"/>
-      <c r="X22" s="203" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y22" s="186"/>
-    </row>
-    <row r="23" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="212"/>
-      <c r="B23" s="201" t="s">
-        <v>227</v>
-      </c>
-      <c r="C23" s="202"/>
-      <c r="D23" s="202"/>
-      <c r="E23" s="202"/>
-      <c r="F23" s="202" t="s">
-        <v>157</v>
-      </c>
-      <c r="G23" s="235"/>
-      <c r="H23" s="201" t="s">
-        <v>155</v>
-      </c>
-      <c r="I23" s="202"/>
-      <c r="J23" s="202" t="s">
-        <v>156</v>
-      </c>
-      <c r="K23" s="185"/>
-      <c r="L23" s="202" t="s">
-        <v>157</v>
-      </c>
-      <c r="M23" s="186"/>
-      <c r="N23" s="177" t="s">
-        <v>155</v>
-      </c>
-      <c r="O23" s="173"/>
-      <c r="P23" s="173"/>
-      <c r="Q23" s="173"/>
-      <c r="R23" s="178" t="s">
-        <v>157</v>
-      </c>
-      <c r="S23" s="174"/>
-      <c r="T23" s="201" t="s">
-        <v>155</v>
-      </c>
-      <c r="U23" s="202"/>
-      <c r="V23" s="202" t="s">
-        <v>156</v>
-      </c>
-      <c r="W23" s="185"/>
-      <c r="X23" s="202" t="s">
-        <v>157</v>
-      </c>
-      <c r="Y23" s="186"/>
-    </row>
-    <row r="24" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="212" t="s">
+      <c r="O25" s="177"/>
+      <c r="P25" s="177"/>
+      <c r="Q25" s="177" t="s">
         <v>229</v>
       </c>
-      <c r="B24" s="199" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="202"/>
-      <c r="D24" s="202"/>
-      <c r="E24" s="202"/>
-      <c r="F24" s="202"/>
-      <c r="G24" s="235"/>
-      <c r="H24" s="199" t="s">
-        <v>161</v>
-      </c>
-      <c r="I24" s="200"/>
-      <c r="J24" s="200"/>
-      <c r="K24" s="203" t="s">
-        <v>81</v>
-      </c>
-      <c r="L24" s="203"/>
-      <c r="M24" s="236"/>
-      <c r="N24" s="180" t="s">
-        <v>233</v>
-      </c>
-      <c r="O24" s="178"/>
-      <c r="P24" s="178"/>
-      <c r="Q24" s="176" t="s">
-        <v>81</v>
-      </c>
-      <c r="R24" s="173"/>
-      <c r="S24" s="174"/>
-      <c r="T24" s="199" t="s">
-        <v>161</v>
-      </c>
-      <c r="U24" s="202"/>
-      <c r="V24" s="202"/>
-      <c r="W24" s="203" t="s">
-        <v>81</v>
-      </c>
-      <c r="X24" s="185"/>
-      <c r="Y24" s="186"/>
-    </row>
-    <row r="25" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="212"/>
-      <c r="B25" s="201" t="s">
-        <v>230</v>
-      </c>
-      <c r="C25" s="202"/>
-      <c r="D25" s="202"/>
-      <c r="E25" s="202"/>
-      <c r="F25" s="202"/>
-      <c r="G25" s="235"/>
-      <c r="H25" s="201" t="s">
-        <v>231</v>
-      </c>
-      <c r="I25" s="202"/>
-      <c r="J25" s="202"/>
-      <c r="K25" s="202" t="s">
-        <v>232</v>
-      </c>
-      <c r="L25" s="202"/>
-      <c r="M25" s="235"/>
-      <c r="N25" s="177" t="s">
-        <v>234</v>
-      </c>
-      <c r="O25" s="178"/>
-      <c r="P25" s="178"/>
-      <c r="Q25" s="178" t="s">
-        <v>235</v>
-      </c>
-      <c r="R25" s="178"/>
-      <c r="S25" s="181"/>
-      <c r="T25" s="201" t="s">
-        <v>231</v>
-      </c>
-      <c r="U25" s="202"/>
-      <c r="V25" s="202"/>
-      <c r="W25" s="202" t="s">
-        <v>232</v>
-      </c>
-      <c r="X25" s="202"/>
-      <c r="Y25" s="211"/>
+      <c r="R25" s="177"/>
+      <c r="S25" s="180"/>
+      <c r="T25" s="200" t="s">
+        <v>225</v>
+      </c>
+      <c r="U25" s="201"/>
+      <c r="V25" s="201"/>
+      <c r="W25" s="201" t="s">
+        <v>226</v>
+      </c>
+      <c r="X25" s="201"/>
+      <c r="Y25" s="210"/>
     </row>
     <row r="26" spans="1:26" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="172" t="s">
+      <c r="B26" s="171" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="173"/>
-      <c r="D26" s="173"/>
-      <c r="E26" s="173"/>
-      <c r="F26" s="173"/>
-      <c r="G26" s="173"/>
-      <c r="H26" s="221" t="s">
+      <c r="C26" s="172"/>
+      <c r="D26" s="172"/>
+      <c r="E26" s="172"/>
+      <c r="F26" s="172"/>
+      <c r="G26" s="172"/>
+      <c r="H26" s="220" t="s">
         <v>34</v>
       </c>
-      <c r="I26" s="222"/>
-      <c r="J26" s="222"/>
-      <c r="K26" s="222"/>
-      <c r="L26" s="222"/>
-      <c r="M26" s="223"/>
-      <c r="N26" s="221" t="s">
+      <c r="I26" s="221"/>
+      <c r="J26" s="221"/>
+      <c r="K26" s="221"/>
+      <c r="L26" s="221"/>
+      <c r="M26" s="222"/>
+      <c r="N26" s="220" t="s">
         <v>140</v>
       </c>
-      <c r="O26" s="222"/>
-      <c r="P26" s="222"/>
-      <c r="Q26" s="222"/>
-      <c r="R26" s="222"/>
-      <c r="S26" s="223"/>
-      <c r="T26" s="193" t="s">
+      <c r="O26" s="221"/>
+      <c r="P26" s="221"/>
+      <c r="Q26" s="221"/>
+      <c r="R26" s="221"/>
+      <c r="S26" s="222"/>
+      <c r="T26" s="192" t="s">
         <v>140</v>
       </c>
-      <c r="U26" s="194"/>
-      <c r="V26" s="194"/>
-      <c r="W26" s="194"/>
-      <c r="X26" s="194"/>
-      <c r="Y26" s="195"/>
+      <c r="U26" s="193"/>
+      <c r="V26" s="193"/>
+      <c r="W26" s="193"/>
+      <c r="X26" s="193"/>
+      <c r="Y26" s="194"/>
     </row>
     <row r="27" spans="1:26" s="18" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="42" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="44"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="45"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="44"/>
-      <c r="O27" s="46"/>
-      <c r="P27" s="46"/>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="46"/>
-      <c r="S27" s="47"/>
-      <c r="T27" s="48"/>
-      <c r="U27" s="48"/>
-      <c r="V27" s="48"/>
-      <c r="W27" s="48"/>
-      <c r="X27" s="48"/>
-      <c r="Y27" s="49"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
+      <c r="L27" s="44"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="45"/>
+      <c r="P27" s="45"/>
+      <c r="Q27" s="45"/>
+      <c r="R27" s="45"/>
+      <c r="S27" s="46"/>
+      <c r="T27" s="47"/>
+      <c r="U27" s="47"/>
+      <c r="V27" s="47"/>
+      <c r="W27" s="47"/>
+      <c r="X27" s="47"/>
+      <c r="Y27" s="48"/>
     </row>
     <row r="28" spans="1:26" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="216" t="s">
-        <v>225</v>
-      </c>
-      <c r="C28" s="170"/>
-      <c r="D28" s="170"/>
-      <c r="E28" s="170"/>
-      <c r="F28" s="170"/>
-      <c r="G28" s="171"/>
-      <c r="H28" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="I28" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="J28" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="N28" s="169" t="s">
-        <v>206</v>
-      </c>
-      <c r="O28" s="170"/>
-      <c r="P28" s="170"/>
-      <c r="Q28" s="170"/>
-      <c r="R28" s="170"/>
-      <c r="S28" s="171"/>
-      <c r="T28" s="208" t="s">
+      <c r="B28" s="215" t="s">
+        <v>220</v>
+      </c>
+      <c r="C28" s="169"/>
+      <c r="D28" s="169"/>
+      <c r="E28" s="169"/>
+      <c r="F28" s="169"/>
+      <c r="G28" s="170"/>
+      <c r="H28" s="207" t="s">
         <v>147</v>
       </c>
-      <c r="U28" s="209"/>
-      <c r="V28" s="209"/>
-      <c r="W28" s="209"/>
-      <c r="X28" s="209"/>
-      <c r="Y28" s="210"/>
+      <c r="I28" s="208"/>
+      <c r="J28" s="208"/>
+      <c r="K28" s="208"/>
+      <c r="L28" s="208"/>
+      <c r="M28" s="209"/>
+      <c r="N28" s="168" t="s">
+        <v>201</v>
+      </c>
+      <c r="O28" s="169"/>
+      <c r="P28" s="169"/>
+      <c r="Q28" s="169"/>
+      <c r="R28" s="169"/>
+      <c r="S28" s="170"/>
+      <c r="T28" s="207" t="s">
+        <v>147</v>
+      </c>
+      <c r="U28" s="208"/>
+      <c r="V28" s="208"/>
+      <c r="W28" s="208"/>
+      <c r="X28" s="208"/>
+      <c r="Y28" s="209"/>
     </row>
     <row r="29" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="212" t="s">
+      <c r="A29" s="211" t="s">
+        <v>173</v>
+      </c>
+      <c r="B29" s="171"/>
+      <c r="C29" s="172"/>
+      <c r="D29" s="172"/>
+      <c r="E29" s="172"/>
+      <c r="F29" s="172"/>
+      <c r="G29" s="173"/>
+      <c r="H29" s="198" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="199"/>
+      <c r="J29" s="199" t="s">
+        <v>176</v>
+      </c>
+      <c r="K29" s="202"/>
+      <c r="L29" s="202" t="s">
+        <v>15</v>
+      </c>
+      <c r="M29" s="203"/>
+      <c r="N29" s="171" t="s">
+        <v>202</v>
+      </c>
+      <c r="O29" s="172"/>
+      <c r="P29" s="172"/>
+      <c r="Q29" s="172"/>
+      <c r="R29" s="172"/>
+      <c r="S29" s="173"/>
+      <c r="T29" s="198" t="s">
+        <v>14</v>
+      </c>
+      <c r="U29" s="199"/>
+      <c r="V29" s="199" t="s">
+        <v>176</v>
+      </c>
+      <c r="W29" s="202"/>
+      <c r="X29" s="202" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y29" s="203"/>
+    </row>
+    <row r="30" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="211"/>
+      <c r="B30" s="171"/>
+      <c r="C30" s="172"/>
+      <c r="D30" s="172"/>
+      <c r="E30" s="172"/>
+      <c r="F30" s="172"/>
+      <c r="G30" s="173"/>
+      <c r="H30" s="200" t="s">
         <v>174</v>
       </c>
-      <c r="B29" s="172"/>
-      <c r="C29" s="173"/>
-      <c r="D29" s="173"/>
-      <c r="E29" s="173"/>
-      <c r="F29" s="173"/>
-      <c r="G29" s="174"/>
-      <c r="H29" s="199" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="200"/>
-      <c r="J29" s="200" t="s">
+      <c r="I30" s="201"/>
+      <c r="J30" s="184" t="s">
         <v>177</v>
       </c>
-      <c r="K29" s="203"/>
-      <c r="L29" s="203" t="s">
-        <v>15</v>
-      </c>
-      <c r="M29" s="204"/>
-      <c r="N29" s="172" t="s">
-        <v>207</v>
-      </c>
-      <c r="O29" s="173"/>
-      <c r="P29" s="173"/>
-      <c r="Q29" s="173"/>
-      <c r="R29" s="173"/>
-      <c r="S29" s="174"/>
-      <c r="T29" s="199" t="s">
-        <v>14</v>
-      </c>
-      <c r="U29" s="200"/>
-      <c r="V29" s="200" t="s">
+      <c r="K30" s="184"/>
+      <c r="L30" s="201" t="s">
+        <v>175</v>
+      </c>
+      <c r="M30" s="185"/>
+      <c r="N30" s="171"/>
+      <c r="O30" s="172"/>
+      <c r="P30" s="172"/>
+      <c r="Q30" s="172"/>
+      <c r="R30" s="172"/>
+      <c r="S30" s="173"/>
+      <c r="T30" s="200" t="s">
+        <v>174</v>
+      </c>
+      <c r="U30" s="201"/>
+      <c r="V30" s="184" t="s">
         <v>177</v>
       </c>
-      <c r="W29" s="203"/>
-      <c r="X29" s="203" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y29" s="204"/>
-    </row>
-    <row r="30" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="212"/>
-      <c r="B30" s="172"/>
-      <c r="C30" s="173"/>
-      <c r="D30" s="173"/>
-      <c r="E30" s="173"/>
-      <c r="F30" s="173"/>
-      <c r="G30" s="174"/>
-      <c r="H30" s="201" t="s">
+      <c r="W30" s="184"/>
+      <c r="X30" s="201" t="s">
         <v>175</v>
       </c>
-      <c r="I30" s="202"/>
-      <c r="J30" s="185" t="s">
-        <v>178</v>
-      </c>
-      <c r="K30" s="185"/>
-      <c r="L30" s="202" t="s">
-        <v>176</v>
-      </c>
-      <c r="M30" s="186"/>
-      <c r="N30" s="172"/>
-      <c r="O30" s="173"/>
-      <c r="P30" s="173"/>
-      <c r="Q30" s="173"/>
-      <c r="R30" s="173"/>
-      <c r="S30" s="174"/>
-      <c r="T30" s="201" t="s">
-        <v>175</v>
-      </c>
-      <c r="U30" s="202"/>
-      <c r="V30" s="185" t="s">
-        <v>178</v>
-      </c>
-      <c r="W30" s="185"/>
-      <c r="X30" s="202" t="s">
-        <v>176</v>
-      </c>
-      <c r="Y30" s="186"/>
+      <c r="Y30" s="185"/>
     </row>
     <row r="31" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B31" s="172"/>
-      <c r="C31" s="173"/>
-      <c r="D31" s="173"/>
-      <c r="E31" s="173"/>
-      <c r="F31" s="173"/>
-      <c r="G31" s="174"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="52"/>
-      <c r="M31" s="51"/>
-      <c r="N31" s="172" t="s">
-        <v>327</v>
-      </c>
-      <c r="O31" s="173"/>
-      <c r="P31" s="173"/>
-      <c r="Q31" s="173"/>
-      <c r="R31" s="173"/>
-      <c r="S31" s="174"/>
-      <c r="T31" s="184" t="s">
-        <v>173</v>
-      </c>
-      <c r="U31" s="185"/>
-      <c r="V31" s="185"/>
-      <c r="W31" s="185"/>
-      <c r="X31" s="185"/>
-      <c r="Y31" s="186"/>
+      <c r="B31" s="171"/>
+      <c r="C31" s="172"/>
+      <c r="D31" s="172"/>
+      <c r="E31" s="172"/>
+      <c r="F31" s="172"/>
+      <c r="G31" s="173"/>
+      <c r="H31" s="183" t="s">
+        <v>322</v>
+      </c>
+      <c r="I31" s="184"/>
+      <c r="J31" s="184"/>
+      <c r="K31" s="184"/>
+      <c r="L31" s="184"/>
+      <c r="M31" s="185"/>
+      <c r="N31" s="171" t="s">
+        <v>219</v>
+      </c>
+      <c r="O31" s="172"/>
+      <c r="P31" s="172"/>
+      <c r="Q31" s="172"/>
+      <c r="R31" s="172"/>
+      <c r="S31" s="173"/>
+      <c r="T31" s="183" t="s">
+        <v>322</v>
+      </c>
+      <c r="U31" s="184"/>
+      <c r="V31" s="184"/>
+      <c r="W31" s="184"/>
+      <c r="X31" s="184"/>
+      <c r="Y31" s="185"/>
     </row>
     <row r="32" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B32" s="172"/>
-      <c r="C32" s="173"/>
-      <c r="D32" s="173"/>
-      <c r="E32" s="173"/>
-      <c r="F32" s="173"/>
-      <c r="G32" s="174"/>
-      <c r="H32" s="172" t="s">
-        <v>330</v>
-      </c>
-      <c r="I32" s="241"/>
-      <c r="J32" s="241"/>
-      <c r="K32" s="241"/>
-      <c r="L32" s="241"/>
-      <c r="M32" s="174"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="52"/>
-      <c r="P32" s="52"/>
-      <c r="Q32" s="52"/>
-      <c r="R32" s="52"/>
-      <c r="S32" s="51"/>
-      <c r="T32" s="172" t="s">
-        <v>330</v>
-      </c>
-      <c r="U32" s="241"/>
-      <c r="V32" s="241"/>
-      <c r="W32" s="241"/>
-      <c r="X32" s="241"/>
-      <c r="Y32" s="174"/>
+      <c r="B32" s="171"/>
+      <c r="C32" s="172"/>
+      <c r="D32" s="172"/>
+      <c r="E32" s="172"/>
+      <c r="F32" s="172"/>
+      <c r="G32" s="173"/>
+      <c r="H32" s="171" t="s">
+        <v>323</v>
+      </c>
+      <c r="I32" s="240"/>
+      <c r="J32" s="240"/>
+      <c r="K32" s="240"/>
+      <c r="L32" s="240"/>
+      <c r="M32" s="173"/>
+      <c r="N32" s="49"/>
+      <c r="O32" s="51"/>
+      <c r="P32" s="51"/>
+      <c r="Q32" s="51"/>
+      <c r="R32" s="51"/>
+      <c r="S32" s="50"/>
+      <c r="T32" s="171" t="s">
+        <v>323</v>
+      </c>
+      <c r="U32" s="240"/>
+      <c r="V32" s="240"/>
+      <c r="W32" s="240"/>
+      <c r="X32" s="240"/>
+      <c r="Y32" s="173"/>
     </row>
     <row r="33" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="32"/>
-      <c r="B33" s="39"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
-      <c r="N33" s="39"/>
-      <c r="O33" s="32"/>
-      <c r="P33" s="32"/>
-      <c r="Q33" s="32"/>
-      <c r="R33" s="32"/>
-      <c r="S33" s="40"/>
-      <c r="T33" s="32"/>
-      <c r="U33" s="32"/>
-      <c r="V33" s="32"/>
-      <c r="W33" s="32"/>
-      <c r="X33" s="32"/>
-      <c r="Y33" s="33"/>
+      <c r="A33" s="31"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="31"/>
+      <c r="S33" s="39"/>
+      <c r="T33" s="31"/>
+      <c r="U33" s="31"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="31"/>
+      <c r="Y33" s="32"/>
     </row>
     <row r="34" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="32"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="32"/>
-      <c r="P34" s="32"/>
-      <c r="Q34" s="32"/>
-      <c r="R34" s="32"/>
-      <c r="S34" s="40"/>
-      <c r="T34" s="32"/>
-      <c r="U34" s="32"/>
-      <c r="V34" s="32"/>
-      <c r="W34" s="32"/>
-      <c r="X34" s="32"/>
-      <c r="Y34" s="33"/>
+      <c r="A34" s="31"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
+      <c r="M34" s="31"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="31"/>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="31"/>
+      <c r="S34" s="39"/>
+      <c r="T34" s="31"/>
+      <c r="U34" s="31"/>
+      <c r="V34" s="31"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="31"/>
+      <c r="Y34" s="32"/>
     </row>
     <row r="35" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="32"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
-      <c r="M35" s="32"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="32"/>
-      <c r="P35" s="32"/>
-      <c r="Q35" s="32"/>
-      <c r="R35" s="32"/>
-      <c r="S35" s="40"/>
-      <c r="T35" s="32"/>
-      <c r="U35" s="32"/>
-      <c r="V35" s="32"/>
-      <c r="W35" s="32"/>
-      <c r="X35" s="32"/>
-      <c r="Y35" s="33"/>
+      <c r="A35" s="31"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="31"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="31"/>
+      <c r="M35" s="31"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="31"/>
+      <c r="P35" s="31"/>
+      <c r="Q35" s="31"/>
+      <c r="R35" s="31"/>
+      <c r="S35" s="39"/>
+      <c r="T35" s="31"/>
+      <c r="U35" s="31"/>
+      <c r="V35" s="31"/>
+      <c r="W35" s="31"/>
+      <c r="X35" s="31"/>
+      <c r="Y35" s="32"/>
     </row>
     <row r="36" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="32"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="39"/>
-      <c r="O36" s="32"/>
-      <c r="P36" s="32"/>
-      <c r="Q36" s="32"/>
-      <c r="R36" s="32"/>
-      <c r="S36" s="40"/>
-      <c r="T36" s="32"/>
-      <c r="U36" s="32"/>
-      <c r="V36" s="32"/>
-      <c r="W36" s="32"/>
-      <c r="X36" s="32"/>
-      <c r="Y36" s="33"/>
+      <c r="A36" s="31"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="31"/>
+      <c r="M36" s="31"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="31"/>
+      <c r="P36" s="31"/>
+      <c r="Q36" s="31"/>
+      <c r="R36" s="31"/>
+      <c r="S36" s="39"/>
+      <c r="T36" s="31"/>
+      <c r="U36" s="31"/>
+      <c r="V36" s="31"/>
+      <c r="W36" s="31"/>
+      <c r="X36" s="31"/>
+      <c r="Y36" s="32"/>
     </row>
     <row r="37" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="42" t="s">
+      <c r="A37" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="B37" s="39"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="184" t="s">
+      <c r="B37" s="38"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="183" t="s">
         <v>163</v>
       </c>
-      <c r="I37" s="185"/>
-      <c r="J37" s="185"/>
-      <c r="K37" s="185"/>
-      <c r="L37" s="185"/>
-      <c r="M37" s="186"/>
-      <c r="N37" s="184"/>
-      <c r="O37" s="185"/>
-      <c r="P37" s="185"/>
-      <c r="Q37" s="185"/>
-      <c r="R37" s="185"/>
-      <c r="S37" s="187"/>
-      <c r="T37" s="184" t="s">
+      <c r="I37" s="184"/>
+      <c r="J37" s="184"/>
+      <c r="K37" s="184"/>
+      <c r="L37" s="184"/>
+      <c r="M37" s="185"/>
+      <c r="N37" s="183"/>
+      <c r="O37" s="184"/>
+      <c r="P37" s="184"/>
+      <c r="Q37" s="184"/>
+      <c r="R37" s="184"/>
+      <c r="S37" s="186"/>
+      <c r="T37" s="183" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="185"/>
-      <c r="V37" s="185"/>
-      <c r="W37" s="185"/>
-      <c r="X37" s="185"/>
-      <c r="Y37" s="186"/>
+      <c r="U37" s="184"/>
+      <c r="V37" s="184"/>
+      <c r="W37" s="184"/>
+      <c r="X37" s="184"/>
+      <c r="Y37" s="185"/>
     </row>
     <row r="38" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="42" t="s">
+      <c r="A38" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="N38" s="183" t="s">
         <v>190</v>
       </c>
-      <c r="N38" s="184" t="s">
-        <v>191</v>
-      </c>
-      <c r="O38" s="141"/>
-      <c r="P38" s="141"/>
-      <c r="Q38" s="141"/>
-      <c r="R38" s="141"/>
-      <c r="S38" s="142"/>
+      <c r="O38" s="140"/>
+      <c r="P38" s="140"/>
+      <c r="Q38" s="140"/>
+      <c r="R38" s="140"/>
+      <c r="S38" s="141"/>
     </row>
   </sheetData>
-  <mergeCells count="201">
+  <mergeCells count="210">
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
@@ -6888,9 +6933,11 @@
     <mergeCell ref="K17:M17"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="H17:J17"/>
+    <mergeCell ref="B20:D21"/>
+    <mergeCell ref="E20:G21"/>
+    <mergeCell ref="H20:K21"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="L29:M29"/>
-    <mergeCell ref="H20:M21"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="H24:J24"/>
@@ -6906,6 +6953,10 @@
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="A20:A21"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="H31:M31"/>
     <mergeCell ref="H37:M37"/>
     <mergeCell ref="H30:I30"/>
     <mergeCell ref="J30:K30"/>
@@ -6963,7 +7014,6 @@
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="H18:K18"/>
     <mergeCell ref="H19:K19"/>
-    <mergeCell ref="B20:G21"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="T1:Y1"/>
@@ -7025,6 +7075,9 @@
     <mergeCell ref="W24:Y24"/>
     <mergeCell ref="T25:V25"/>
     <mergeCell ref="W25:Y25"/>
+    <mergeCell ref="T20:W21"/>
+    <mergeCell ref="X20:X21"/>
+    <mergeCell ref="Y20:Y21"/>
     <mergeCell ref="N37:S37"/>
     <mergeCell ref="N8:S8"/>
     <mergeCell ref="N31:S31"/>
@@ -7041,7 +7094,6 @@
     <mergeCell ref="N13:O13"/>
     <mergeCell ref="P13:Q13"/>
     <mergeCell ref="R13:S13"/>
-    <mergeCell ref="T20:Y21"/>
     <mergeCell ref="T8:Y8"/>
     <mergeCell ref="T26:Y26"/>
     <mergeCell ref="N9:O9"/>
@@ -7068,12 +7120,14 @@
     <mergeCell ref="N23:O23"/>
     <mergeCell ref="P23:Q23"/>
     <mergeCell ref="R23:S23"/>
-    <mergeCell ref="N20:S21"/>
     <mergeCell ref="N24:P24"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="N25:P25"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="N26:S26"/>
+    <mergeCell ref="N20:Q21"/>
+    <mergeCell ref="R20:R21"/>
+    <mergeCell ref="S20:S21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
